--- a/Results/Ammonia/ammonia human toxicity carcinogenic results.xlsx
+++ b/Results/Ammonia/ammonia human toxicity carcinogenic results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.28436720455942e-10</v>
+        <v>5.284367204559038e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.926114744142165e-10</v>
+        <v>5.926114744142163e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.585943347064928e-10</v>
+        <v>5.585943347064861e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.343447495192588e-10</v>
+        <v>6.343447495192536e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.066447845926837e-10</v>
+        <v>5.066447845926805e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.121567712966113e-10</v>
+        <v>5.121567712966022e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.860394716706372e-10</v>
+        <v>6.860394716706393e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.59864370867917e-10</v>
+        <v>4.598643708679132e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>8.393878823567948e-10</v>
+        <v>8.393878823567995e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>8.022166380551597e-10</v>
+        <v>8.022166380551693e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>7.429603391250157e-10</v>
+        <v>7.429603391250164e-10</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.253917226741511e-10</v>
+        <v>6.253917226741898e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.780295579900914e-10</v>
+        <v>6.78029557990091e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.600792261933245e-10</v>
+        <v>6.600792261933239e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>7.210064073653396e-10</v>
+        <v>7.210064073653387e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.933064424387645e-10</v>
+        <v>5.933064424387659e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.066664087596831e-10</v>
+        <v>6.066664087596759e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>8.061261093720258e-10</v>
+        <v>8.061261093720312e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.464686932860131e-10</v>
+        <v>5.464686932860122e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.359188724956241e-10</v>
+        <v>9.359188724956165e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.925984597615809e-10</v>
+        <v>8.925984597615586e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.721349234643193e-10</v>
+        <v>8.721349234643191e-10</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.40294464175214e-09</v>
+        <v>5.238148682585777e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3481085383757e-09</v>
+        <v>4.805965590888624e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.420872065537595e-09</v>
+        <v>5.417422920440475e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.354537322313475e-09</v>
+        <v>4.817280652896407e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.354537322313476e-09</v>
+        <v>4.817280652896415e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.392997733984119e-09</v>
+        <v>5.140897547850366e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.496613800409956e-09</v>
+        <v>6.174840269164101e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.36170260619303e-09</v>
+        <v>4.829819866862337e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.40126657772281e-09</v>
+        <v>5.221368042292651e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.376930718305326e-09</v>
+        <v>4.978009448117732e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.530462602377835e-09</v>
+        <v>6.513328288842883e-10</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.333150468370464e-08</v>
+        <v>2.623241424265882e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>8.875721817684346e-09</v>
+        <v>1.805456489068287e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.544838495702745e-08</v>
+        <v>3.010584547568573e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>8.875721866511813e-09</v>
+        <v>1.805456537895793e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>8.875721866511813e-09</v>
+        <v>1.805456537895793e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.279084160061845e-08</v>
+        <v>2.520110264442818e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.608261330126103e-08</v>
+        <v>4.944619915619199e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>8.87571316680387e-09</v>
+        <v>1.805447838187824e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.40075628136302e-08</v>
+        <v>2.740844929726664e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.086524338035574e-08</v>
+        <v>2.1677439642838e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>3.103100473883916e-08</v>
+        <v>2.382028058665222e-09</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.125881458520822e-09</v>
+        <v>6.250762265323134e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.928160819469869e-09</v>
+        <v>5.826857600082564e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>2.00334430022016e-09</v>
+        <v>6.442576720652636e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.90516914415247e-09</v>
+        <v>5.786392654081804e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.937116691322105e-09</v>
+        <v>5.842620336795681e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>4.115934550752792e-09</v>
+        <v>9.933266319395286e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>4.203657213936648e-09</v>
+        <v>1.09392366511547e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.084639422961691e-09</v>
+        <v>5.842433449599645e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>2.040673365291324e-09</v>
+        <v>6.346723982315479e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.950456228003841e-09</v>
+        <v>5.987414339717543e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>2.112372443122874e-09</v>
+        <v>7.537489603004613e-10</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.570572542174978e-09</v>
+        <v>1.433317373804779e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>6.529339157496351e-09</v>
+        <v>1.392493143112888e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>6.588302688911023e-09</v>
+        <v>1.451210076829721e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.529057078796269e-09</v>
+        <v>1.392443537495806e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>6.529057078796269e-09</v>
+        <v>1.392443537495806e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>6.560625634406963e-09</v>
+        <v>1.423592260331227e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>6.664241700832807e-09</v>
+        <v>1.526986532462596e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>6.529330506615878e-09</v>
+        <v>1.392484492232418e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>6.568894478145659e-09</v>
+        <v>1.431639309775453e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>6.54455861872816e-09</v>
+        <v>1.407303450357958e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>6.698090502800679e-09</v>
+        <v>1.560835334430474e-09</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.447799691713731e-09</v>
+        <v>1.41170935224068e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.005025346066805e-08</v>
+        <v>2.0121740571133e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.086411925780528e-08</v>
+        <v>2.203753788877379e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>9.053802400120217e-09</v>
+        <v>1.836798711641034e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>6.521993012386328e-09</v>
+        <v>1.391200261814394e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.008084645634592e-08</v>
+        <v>2.043151121635338e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.018446252277174e-08</v>
+        <v>2.146545393766707e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.004955132855483e-08</v>
+        <v>2.012043353536529e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.008983125324912e-08</v>
+        <v>2.051324178835832e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>6.354115290444248e-09</v>
+        <v>1.373785424761607e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.402372283822085e-08</v>
+        <v>2.850146618478161e-09</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.269351023787537e-09</v>
+        <v>1.204302387809534e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>6.4878363114968e-09</v>
+        <v>1.38518864225655e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>6.546998440896089e-09</v>
+        <v>1.44394052921849e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>7.941524869985935e-09</v>
+        <v>1.641037867398152e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>6.487835302707071e-09</v>
+        <v>1.385188504943418e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>6.519122788407429e-09</v>
+        <v>1.416287759474884e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>6.622738854833269e-09</v>
+        <v>1.519682031606256e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>6.487827660616333e-09</v>
+        <v>1.385179991376081e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>6.527391632146122e-09</v>
+        <v>1.424334808919111e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.916844762846574e-09</v>
+        <v>1.271539121470013e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>6.656587656801135e-09</v>
+        <v>1.553530833574134e-09</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.093295746377209e-10</v>
+        <v>4.093295746377199e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.261816913297902e-10</v>
+        <v>5.261816913297872e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.229314033691714e-10</v>
+        <v>4.229314033691703e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.593089295989374e-10</v>
+        <v>5.593089295989362e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.578991886892068e-10</v>
+        <v>4.578991886892052e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.224466923333719e-10</v>
+        <v>4.224466923333715e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.22216348996766e-10</v>
+        <v>4.222163489967646e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.212324366522061e-10</v>
+        <v>4.212324366522055e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.91572380939046e-10</v>
+        <v>7.915723809390419e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.088829107843293e-10</v>
+        <v>7.088829107843277e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.399743566215788e-10</v>
+        <v>4.399743566215779e-10</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.805322291423083e-10</v>
+        <v>4.805322291423071e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.979862977476135e-10</v>
+        <v>5.979862977476112e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.961771497938104e-10</v>
+        <v>4.9617714979381e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.323075897920997e-10</v>
+        <v>6.323075897920957e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.308978488823684e-10</v>
+        <v>5.30897848882364e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.95619631695054e-10</v>
+        <v>4.956196316950514e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.946356195757141e-10</v>
+        <v>4.946356195757136e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.944575057191525e-10</v>
+        <v>4.944575057191495e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.82760857292002e-10</v>
+        <v>8.827608572919956e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.811702258441493e-10</v>
+        <v>7.811702258441497e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.157862565132444e-10</v>
+        <v>5.157862565132433e-10</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.15771162296868e-09</v>
+        <v>4.252029257873916e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.157005773405209e-09</v>
+        <v>4.309355339678307e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.165797333791152e-09</v>
+        <v>4.332886366098647e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.161988371182768e-09</v>
+        <v>4.318124985401497e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.161988371182769e-09</v>
+        <v>4.318124985401517e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.165266567138631e-09</v>
+        <v>4.329577941776593e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.165392660204345e-09</v>
+        <v>4.328839630230569e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.164464493598598e-09</v>
+        <v>4.322469382619546e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.236807220396002e-09</v>
+        <v>5.042985232147126e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.162004259782563e-09</v>
+        <v>4.294955626012759e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.175966891582478e-09</v>
+        <v>4.434581944011897e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.421399976819725e-09</v>
+        <v>1.351612071045329e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>6.722273070599792e-09</v>
+        <v>1.41042257296662e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>7.121975075540254e-09</v>
+        <v>1.481575913477449e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.722273103813654e-09</v>
+        <v>1.410422606180481e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.722273103813645e-09</v>
+        <v>1.410422606180481e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>7.211125295377306e-09</v>
+        <v>1.497028924581889e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>7.783841531642768e-09</v>
+        <v>1.597730958084374e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>6.722271455972635e-09</v>
+        <v>1.410420958339424e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.429264917626013e-08</v>
+        <v>2.802126694995776e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>6.678811370026819e-09</v>
+        <v>1.400453608743029e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>7.959330871199057e-09</v>
+        <v>1.844888546091611e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.485960091109527e-09</v>
+        <v>8.349746539597908e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.69595095301679e-09</v>
+        <v>5.257898850654919e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.700225993822817e-09</v>
+        <v>8.431330430785954e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.676386797284733e-09</v>
+        <v>5.223466210435261e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.699378387838673e-09</v>
+        <v>5.263931409590932e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>3.493515035279478e-09</v>
+        <v>5.269862061485351e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.483261792734217e-09</v>
+        <v>8.40828928137823e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>1.698716837237106e-09</v>
+        <v>5.26275350232831e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>3.558860324593549e-09</v>
+        <v>9.129798673389989e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.695632407391246e-09</v>
+        <v>5.234141160714944e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.710943769070512e-09</v>
+        <v>5.376141243288915e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.405289237154976e-09</v>
+        <v>1.172776581833368e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.412043722412077e-09</v>
+        <v>1.179822208935117e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.413206100755128e-09</v>
+        <v>1.180832575544877e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.412420994065789e-09</v>
+        <v>1.179888636114031e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.412420994065792e-09</v>
+        <v>1.179888636114031e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.412844181324925e-09</v>
+        <v>1.180531450223643e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.412970274390646e-09</v>
+        <v>1.180457619069037e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4120421077849e-09</v>
+        <v>1.179820594307935e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.484384834582305e-09</v>
+        <v>1.251872179260691e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.409581873968863e-09</v>
+        <v>1.177069218647257e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.423544505768779e-09</v>
+        <v>1.191031850447171e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.059084853392191e-09</v>
+        <v>1.111844610621282e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>7.880624733385344e-09</v>
+        <v>1.61429246451219e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>8.464261125453715e-09</v>
+        <v>1.717818256982112e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>7.110950347952017e-09</v>
+        <v>1.478829800778161e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.155353811245134e-09</v>
+        <v>1.134644812182752e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>7.880299657523814e-09</v>
+        <v>1.614803611681492e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>7.88042575058939e-09</v>
+        <v>1.614729780526866e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>7.879497583983782e-09</v>
+        <v>1.614092755765789e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>7.952393275913881e-09</v>
+        <v>1.686241662581377e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.011112313745153e-09</v>
+        <v>1.106938576427894e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.083010298042844e-08</v>
+        <v>2.142586136831176e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.833011693882721e-09</v>
+        <v>8.960557357168953e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>4.725343699883936e-09</v>
+        <v>1.058963005625052e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>4.726676111054859e-09</v>
+        <v>1.060003298012354e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>5.747281709514746e-09</v>
+        <v>1.238824121713691e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>4.725343111491454e-09</v>
+        <v>1.058962929436191e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.726144158796784e-09</v>
+        <v>1.059672246913576e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>4.726270251862497e-09</v>
+        <v>1.059598415758969e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.725342085256759e-09</v>
+        <v>1.058961390997867e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>4.797684812054157e-09</v>
+        <v>1.131012975950628e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.209775256651473e-09</v>
+        <v>9.659032551436137e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>4.736844483240641e-09</v>
+        <v>1.070172647137103e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.389720014398935e-10</v>
+        <v>5.389720014398946e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.847853717982478e-10</v>
+        <v>4.847853717982487e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>6.099653077409812e-10</v>
+        <v>6.099653077409803e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.072998656582284e-10</v>
+        <v>5.072998656582287e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.072998656582284e-10</v>
+        <v>5.072998656582287e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.705577624802075e-10</v>
+        <v>5.705577624802077e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.560051192752234e-10</v>
+        <v>6.560051192752225e-10</v>
       </c>
       <c r="I2" t="n">
         <v>5.538804734189542e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.330358028097913e-10</v>
+        <v>6.330358028097919e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.48031336785886e-10</v>
+        <v>7.480313367858875e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.858783951742047e-10</v>
+        <v>5.858783951742054e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.190931558517401e-10</v>
+        <v>6.190931558517398e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.700895820338244e-10</v>
+        <v>5.700895820338258e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>7.007501643170866e-10</v>
+        <v>7.007501643170863e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.896682613568041e-10</v>
+        <v>5.896682613568047e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.896682613568041e-10</v>
+        <v>5.896682613568047e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.554233240187898e-10</v>
+        <v>6.554233240187899e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>7.531265859306737e-10</v>
+        <v>7.531265859306751e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.361989209030835e-10</v>
+        <v>6.361989209030844e-10</v>
       </c>
       <c r="J3" t="n">
         <v>7.201949575266693e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.311551448832993e-10</v>
+        <v>8.311551448833006e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.730526774404073e-10</v>
+        <v>6.730526774404072e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.27681559312793e-09</v>
+        <v>4.535477419274288e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.266986882280371e-09</v>
+        <v>4.661771984239933e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.319018105482357e-09</v>
+        <v>4.957502542818563e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.279101782396377e-09</v>
+        <v>4.612784783360238e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.279101782396379e-09</v>
+        <v>4.612784783360236e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.295350868229837e-09</v>
+        <v>4.722817010914561e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3463884321556e-09</v>
+        <v>5.23120580955105e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.285394752881249e-09</v>
+        <v>4.62382930113282e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.304669080617386e-09</v>
+        <v>4.814012294168926e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.288698851616329e-09</v>
+        <v>4.654310004158358e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.304740238043077e-09</v>
+        <v>4.814723868425648e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.98285349558299e-09</v>
+        <v>1.105810409225161e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>8.442552897379065e-09</v>
+        <v>1.729076810238209e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.106504922995322e-08</v>
+        <v>2.211051722894207e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.895101079374764e-09</v>
+        <v>1.625694348294713e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>7.895101079374764e-09</v>
+        <v>1.625694348294713e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>8.958412419896379e-09</v>
+        <v>1.820980526876716e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.528274349811864e-08</v>
+        <v>2.975919059273844e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.89509730386252e-09</v>
+        <v>1.625690572782488e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.008246155360081e-08</v>
+        <v>2.026292696290823e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>8.151083397162479e-09</v>
+        <v>1.67321067388748e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.08959137166569e-08</v>
+        <v>2.169518909931743e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.722801736107656e-09</v>
+        <v>5.440892584241356e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.802927892748986e-09</v>
+        <v>5.60502815755355e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.839287955612401e-09</v>
+        <v>5.873178983146246e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.775155759202529e-09</v>
+        <v>5.485839777808321e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.800262980569184e-09</v>
+        <v>5.530028487174208e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>3.74133701120957e-09</v>
+        <v>9.027752599232143e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.839464509384274e-09</v>
+        <v>9.619019681697701e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>3.731380895860961e-09</v>
+        <v>8.928764889450397e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>3.780446396009671e-09</v>
+        <v>9.171380345648484e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.803562321660036e-09</v>
+        <v>5.560469706525133e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.82031306952998e-09</v>
+        <v>5.72213204692575e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.037125703589828e-09</v>
+        <v>1.291362316828938e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>6.052046200384743e-09</v>
+        <v>1.308347633846975e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>6.079150949081196e-09</v>
+        <v>1.333533630215636e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.045674772783452e-09</v>
+        <v>1.30019532009839e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>6.045674772783452e-09</v>
+        <v>1.30019532009839e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>6.055660978691742e-09</v>
+        <v>1.310096275992966e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>6.106698542617504e-09</v>
+        <v>1.360935155856616e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>6.045704863343134e-09</v>
+        <v>1.300197505014791e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>6.064979191079289e-09</v>
+        <v>1.319215804318403e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>6.049008962078235e-09</v>
+        <v>1.303245575317344e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>6.065050348504964e-09</v>
+        <v>1.319286961744075e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.919024236423263e-09</v>
+        <v>1.270576458720251e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.292156435550453e-09</v>
+        <v>1.878607032147319e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.001475957332203e-08</v>
+        <v>2.026200744328733e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>8.367474055390788e-09</v>
+        <v>1.708831991623039e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>6.034115906719479e-09</v>
+        <v>1.298160959682151e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>9.294921464004531e-09</v>
+        <v>1.88020611831881e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>9.345959027931763e-09</v>
+        <v>1.931044998182725e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>9.284965348655879e-09</v>
+        <v>1.870307347340637e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>9.304899494690601e-09</v>
+        <v>1.889441774664161e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.868542772931364e-09</v>
+        <v>1.271483526199601e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.281135613167163e-08</v>
+        <v>2.506636773147629e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.586518061705062e-09</v>
+        <v>1.036055373240628e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>5.694229670291606e-09</v>
+        <v>1.245371924891821e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.72151295960309e-09</v>
+        <v>1.270589344408558e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.948949986253887e-09</v>
+        <v>1.459171756807758e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.687891271924834e-09</v>
+        <v>1.237225424288482e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>5.697844448598605e-09</v>
+        <v>1.247120567037813e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.74888201252436e-09</v>
+        <v>1.297959446901462e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>5.687888333249992e-09</v>
+        <v>1.23722179605964e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.707162660986145e-09</v>
+        <v>1.25624009536325e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.315173029586805e-09</v>
+        <v>1.128832487962099e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>5.707233818411823e-09</v>
+        <v>1.256311252788922e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.149780496693277e-10</v>
+        <v>5.149780496693276e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.709510100817748e-10</v>
+        <v>4.709510100817741e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.781979249684829e-10</v>
+        <v>5.781979249684824e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.038549218750748e-10</v>
+        <v>5.03854921875075e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.038549218750748e-10</v>
+        <v>5.03854921875075e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.435847998395196e-10</v>
+        <v>5.435847998395189e-10</v>
       </c>
       <c r="H2" t="n">
         <v>5.901065836191968e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.401314435714194e-10</v>
+        <v>5.401314435714195e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.060949385964317e-10</v>
+        <v>6.060949385964315e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.277174827548938e-10</v>
+        <v>7.277174827548928e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.377140985452332e-10</v>
+        <v>5.377140985452326e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.934123119650295e-10</v>
+        <v>5.934123119650292e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.546313565101166e-10</v>
+        <v>5.546313565101145e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.661282645167722e-10</v>
+        <v>6.661282645167725e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.860757471800712e-10</v>
+        <v>5.860757471800709e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.860757471800713e-10</v>
+        <v>5.860757471800708e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.263160005311948e-10</v>
+        <v>6.263160005311945e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.792413510120687e-10</v>
+        <v>6.792413510120681e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.223016713682926e-10</v>
+        <v>6.223016713682924e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.895324189762062e-10</v>
+        <v>6.895324189762059e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.08261629692317e-10</v>
+        <v>8.082616296923162e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.195718812233604e-10</v>
+        <v>6.195718812233602e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.246058818531602e-09</v>
+        <v>4.414013407440042e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.236697503310614e-09</v>
+        <v>4.543111378998156e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.283640355543592e-09</v>
+        <v>4.789828777559915e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.257097962672515e-09</v>
+        <v>4.556924029226429e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.257097962672515e-09</v>
+        <v>4.556924029226431e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.26285207884931e-09</v>
+        <v>4.583694872237288e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.290730222976866e-09</v>
+        <v>4.860727451892722e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.260917454408946e-09</v>
+        <v>4.563630113282891e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.265859481542673e-09</v>
+        <v>4.612020037550733e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.254408867256436e-09</v>
+        <v>4.497513894688357e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.259619553612243e-09</v>
+        <v>4.549620758246489e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.919436261908675e-09</v>
+        <v>9.119157682288361e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>7.224179771356023e-09</v>
+        <v>1.508108011365694e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>9.283835155774421e-09</v>
+        <v>1.887017154967034e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.261699944019304e-09</v>
+        <v>1.51250234591324e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>7.261699944019304e-09</v>
+        <v>1.51250234591324e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>7.520117440632106e-09</v>
+        <v>1.559648184930075e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.100640604941159e-08</v>
+        <v>2.196031681376191e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.261697975407262e-09</v>
+        <v>1.512500377301201e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>7.955369943335537e-09</v>
+        <v>1.638555838651009e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>6.617426316022008e-09</v>
+        <v>1.393642455337005e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>7.897542591356603e-09</v>
+        <v>1.623236524137241e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.55919669336942e-09</v>
+        <v>8.485136045094786e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.735045068903328e-09</v>
+        <v>5.420203089688721e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.765325419437794e-09</v>
+        <v>8.92483802805671e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.715772226603459e-09</v>
+        <v>5.364190729370633e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.73871740532778e-09</v>
+        <v>5.404574243706612e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.739838438760535e-09</v>
+        <v>5.423190861132188e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.656218571133573e-09</v>
+        <v>9.023986922089395e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>1.737903814320174e-09</v>
+        <v>5.403126102177764e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>1.797674572744484e-09</v>
+        <v>5.54801459299415e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.731233843135786e-09</v>
+        <v>5.336725847688724e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.737142024925054e-09</v>
+        <v>5.390060303202956e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.775564200725569e-09</v>
+        <v>1.238594283690473e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.790741013645273e-09</v>
+        <v>1.255822791375642e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.812978079277295e-09</v>
+        <v>1.276146312813614e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.790929330934105e-09</v>
+        <v>1.253646719412885e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.790929330934105e-09</v>
+        <v>1.253646719412885e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.792357461043281e-09</v>
+        <v>1.2555624301702e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.820235605170842e-09</v>
+        <v>1.283265688135738e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.790422836602919e-09</v>
+        <v>1.253555954274756e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.795364863736643e-09</v>
+        <v>1.258394946701541e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.78391424945041e-09</v>
+        <v>1.246944332415303e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.789124935806213e-09</v>
+        <v>1.252155018771117e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.668857898604671e-09</v>
+        <v>1.219813974618956e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.889111084060286e-09</v>
+        <v>1.801135920815157e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.574512984332714e-09</v>
+        <v>1.938176452516083e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>8.012412967072691e-09</v>
+        <v>1.644627837254706e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.785673555721209e-09</v>
+        <v>1.252721702980426e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.889405396023866e-09</v>
+        <v>1.800642863773204e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.917283540155374e-09</v>
+        <v>1.828346121739429e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.887470771583514e-09</v>
+        <v>1.798636387877765e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.893042428644647e-09</v>
+        <v>1.803586195171173e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.617696567528198e-09</v>
+        <v>1.217690020555515e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.223276206541608e-08</v>
+        <v>2.386235147437319e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.238520349193772e-09</v>
+        <v>9.68074567286712e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>5.25257425026141e-09</v>
+        <v>1.161105441533317e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.274980203867674e-09</v>
+        <v>1.181458687254591e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.404941205763581e-09</v>
+        <v>1.361712808797304e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.252257299727225e-09</v>
+        <v>1.158840442434191e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>5.254190697659421e-09</v>
+        <v>1.160845080327873e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.282068841786975e-09</v>
+        <v>1.188548338293409e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>5.252256073219062e-09</v>
+        <v>1.15883860443243e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.257198100352788e-09</v>
+        <v>1.163677596859214e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.666994695429502e-09</v>
+        <v>1.050366491972802e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>5.250958172422356e-09</v>
+        <v>1.157437668928786e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.974366259749465e-10</v>
+        <v>4.974366259749458e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.565256858822801e-10</v>
+        <v>4.565256858822791e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.495405483278608e-10</v>
+        <v>5.495405483278585e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.985323463629799e-10</v>
+        <v>4.985323463629766e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.985323463629799e-10</v>
+        <v>4.985323463629766e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.216852280647237e-10</v>
+        <v>5.216852280647206e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.47476623217489e-10</v>
+        <v>5.474766232174875e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.26312749964428e-10</v>
+        <v>5.263127499644259e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.756647463532845e-10</v>
+        <v>5.756647463532831e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.15452419937934e-10</v>
+        <v>7.154524199379255e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.217841145179644e-10</v>
+        <v>5.217841145179636e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.744530268564107e-10</v>
+        <v>5.744530268564075e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.379622790930613e-10</v>
+        <v>5.379622790930611e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.343833308572627e-10</v>
+        <v>6.343833308572575e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.798947634901251e-10</v>
+        <v>5.798947634901241e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.79894763490125e-10</v>
+        <v>5.798947634901243e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.023439423424475e-10</v>
+        <v>6.023439423424406e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.314385676547832e-10</v>
+        <v>6.314385676547804e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.076249773090804e-10</v>
+        <v>6.076249773090653e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.545902759776642e-10</v>
+        <v>6.545902759776635e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.942063693952471e-10</v>
+        <v>7.942063693952515e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.024656645802937e-10</v>
+        <v>6.024656645802919e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.239293947530072e-09</v>
+        <v>4.364471474550997e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.224783326814261e-09</v>
+        <v>4.456884567851688e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.270267521538403e-09</v>
+        <v>4.674207214634314e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.253824007554757e-09</v>
+        <v>4.531770160268974e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.253824007554756e-09</v>
+        <v>4.531770160268974e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.253507853504102e-09</v>
+        <v>4.50826562454879e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.269056073425249e-09</v>
+        <v>4.662092733502734e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.256441456307281e-09</v>
+        <v>4.536369671219549e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.24684948763406e-09</v>
+        <v>4.440026875590854e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.246170444464197e-09</v>
+        <v>4.433236443892259e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25381087001514e-09</v>
+        <v>4.509640699401647e-10</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.543689994797159e-09</v>
+        <v>8.420208495764615e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>6.534416690817623e-09</v>
+        <v>1.380183923786099e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>8.311873849562963e-09</v>
+        <v>1.706743428480341e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.098885292632312e-09</v>
+        <v>1.481907796626238e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>7.098885292632312e-09</v>
+        <v>1.481907796626238e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>6.899340389005521e-09</v>
+        <v>1.44449308331879e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>9.041855390062503e-09</v>
+        <v>1.834221945665701e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.09888441898856e-09</v>
+        <v>1.481906922981955e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>6.386790717653951e-09</v>
+        <v>1.348632339140751e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>6.115209602088394e-09</v>
+        <v>1.300274531487607e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>7.577819946119333e-09</v>
+        <v>1.563989661303458e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.552196047356286e-09</v>
+        <v>5.20784560409406e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.726424653170977e-09</v>
+        <v>5.339773297454535e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.75327758680909e-09</v>
+        <v>5.524304924903684e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.714180484810833e-09</v>
+        <v>5.341997555849353e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.736646529938906e-09</v>
+        <v>5.381537795060459e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.732697702431941e-09</v>
+        <v>8.57897329818538e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.640633368975526e-09</v>
+        <v>8.83606875105407e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>1.735631305235134e-09</v>
+        <v>8.607077344856127e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7804526627218e-09</v>
+        <v>8.5649252324018e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.725145036808524e-09</v>
+        <v>5.276231721850386e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.733485522773909e-09</v>
+        <v>5.353868083682516e-10</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.753313974996675e-09</v>
+        <v>1.230914667984315e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.765138355774298e-09</v>
+        <v>1.244790937552114e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.784120254390986e-09</v>
+        <v>1.261858798140739e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.771296007257363e-09</v>
+        <v>1.248252083666356e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.771296007257363e-09</v>
+        <v>1.248252083666356e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.767527880970709e-09</v>
+        <v>1.245294082984095e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.783076100891854e-09</v>
+        <v>1.26067679387949e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.770461483773906e-09</v>
+        <v>1.24810448765117e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.760869515100656e-09</v>
+        <v>1.238470208088302e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.760190471930797e-09</v>
+        <v>1.237791164918442e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.76783089748174e-09</v>
+        <v>1.245431590469383e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.640931493896743e-09</v>
+        <v>1.211135351417904e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.842597095211892e-09</v>
+        <v>1.786423672756598e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.521208527212533e-09</v>
+        <v>1.919586330593363e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>7.975757996614975e-09</v>
+        <v>1.636237391690956e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.759738252447738e-09</v>
+        <v>1.246217918830887e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.843353202112045e-09</v>
+        <v>1.786639336571634e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.858901422038825e-09</v>
+        <v>1.802022047468024e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.846286804915249e-09</v>
+        <v>1.789449741238709e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.83732141080859e-09</v>
+        <v>1.779925738798961e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.588585394040147e-09</v>
+        <v>1.207588671373344e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.217400586203815e-08</v>
+        <v>2.372918378121905e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.108824495535648e-09</v>
+        <v>9.41484521167484e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>5.084614453675944e-09</v>
+        <v>1.125018731431801e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.103764888364972e-09</v>
+        <v>1.142116254368992e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.202334523451401e-09</v>
+        <v>1.324114862105438e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.089937742499423e-09</v>
+        <v>1.128333029718746e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>5.087003978872369e-09</v>
+        <v>1.125521876863779e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.102552198793508e-09</v>
+        <v>1.140904587759174e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>5.089937581675489e-09</v>
+        <v>1.128332281530857e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.080345613002335e-09</v>
+        <v>1.118698001967986e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.498481538815873e-09</v>
+        <v>9.04389270996277e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>5.087306995383382e-09</v>
+        <v>1.125659384349066e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.11447377602773e-10</v>
+        <v>5.114473776027679e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.276911279237048e-10</v>
+        <v>4.276911279237052e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.694162497974824e-10</v>
+        <v>5.694162497974773e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.921976778918206e-10</v>
+        <v>4.921976778918172e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.921976778918209e-10</v>
+        <v>4.921976778918172e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.471178677330695e-10</v>
+        <v>5.471178677330659e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.208225188525051e-10</v>
+        <v>6.208225188524982e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.350869077386842e-10</v>
+        <v>5.350869077386785e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.266694658238793e-10</v>
+        <v>6.266694658238757e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.309649093384503e-10</v>
+        <v>7.309649093384334e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.848538221649025e-10</v>
+        <v>5.848538221649001e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.880371830122358e-10</v>
+        <v>5.88037183012233e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.045539070853372e-10</v>
+        <v>5.045539070853358e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.547133942518538e-10</v>
+        <v>6.547133942518483e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.723463630280188e-10</v>
+        <v>5.723463630280176e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.72346363028019e-10</v>
+        <v>5.723463630280176e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.290656357818484e-10</v>
+        <v>6.290656357818445e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>7.132698818660324e-10</v>
+        <v>7.132698818660242e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.151815486377714e-10</v>
+        <v>6.151815486377686e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>7.131708187818135e-10</v>
+        <v>7.131708187818122e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.116418052389973e-10</v>
+        <v>8.116418052389892e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.72475897945773e-10</v>
+        <v>6.72475897945769e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.253275929947463e-09</v>
+        <v>4.387973739987862e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.222657554653555e-09</v>
+        <v>4.317199373326574e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.287735968117736e-09</v>
+        <v>4.732574121690605e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.26388121121089e-09</v>
+        <v>4.522695896514784e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.263881211210888e-09</v>
+        <v>4.522695896514784e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.274245623195679e-09</v>
+        <v>4.599606262046529e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.31829903065834e-09</v>
+        <v>5.038204747096596e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.267080902789346e-09</v>
+        <v>4.528301573070315e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.292501726150562e-09</v>
+        <v>4.78023170201884e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.269450939741154e-09</v>
+        <v>4.54972383792476e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.296947794636e-09</v>
+        <v>4.824692386873248e-10</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.753389386737635e-09</v>
+        <v>8.788173400095599e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.273293616863387e-09</v>
+        <v>1.144631880418601e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>9.121144106853573e-09</v>
+        <v>1.85193723711605e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.198405905262198e-09</v>
+        <v>1.496745930144903e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>7.198405905262198e-09</v>
+        <v>1.496745930144903e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>7.972324635408212e-09</v>
+        <v>1.638822525966249e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.343330514454873e-08</v>
+        <v>2.636061539200618e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.198402776549572e-09</v>
+        <v>1.496742801432283e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>9.987842150055929e-09</v>
+        <v>2.008403076516699e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>7.370877802432933e-09</v>
+        <v>1.528823505807444e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.128321627084564e-08</v>
+        <v>2.240052480976573e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.684942419482451e-09</v>
+        <v>5.278516662771611e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.747308413871078e-09</v>
+        <v>5.240584880545953e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.797566331968647e-09</v>
+        <v>5.629875557206104e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.749886824468184e-09</v>
+        <v>5.378065771212734e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.773884781542233e-09</v>
+        <v>5.420302175434187e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.780235922973664e-09</v>
+        <v>5.490149184830297e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.795125337527478e-09</v>
+        <v>9.397419023565417e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>3.698747392324321e-09</v>
+        <v>5.418844495854059e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>3.753527634163554e-09</v>
+        <v>9.111637276651505e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.776088455366086e-09</v>
+        <v>5.441405860592973e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.804581475183694e-09</v>
+        <v>5.718127659795997e-10</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.002837348124489e-09</v>
+        <v>1.274720179068407e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.998239289179227e-09</v>
+        <v>1.272222318054821e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>6.037120488500765e-09</v>
+        <v>1.309149083227104e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.017423493053659e-09</v>
+        <v>1.288893026722473e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>6.017423493053659e-09</v>
+        <v>1.288893026722473e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>6.023807041372708e-09</v>
+        <v>1.295883431274276e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>6.067860448835365e-09</v>
+        <v>1.339743279779277e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>6.01664232096638e-09</v>
+        <v>1.288752962376652e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>6.04206314432759e-09</v>
+        <v>1.313945975271501e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>6.019012357918179e-09</v>
+        <v>1.290895188862096e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>6.046509212813027e-09</v>
+        <v>1.318392043756944e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.871539433828444e-09</v>
+        <v>1.251611746277518e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.209253507267666e-09</v>
+        <v>1.83736081737613e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.939403683441497e-09</v>
+        <v>1.995950921815163e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>8.313793074336559e-09</v>
+        <v>1.693054070838274e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.991811928393623e-09</v>
+        <v>1.28438539136673e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>9.233199439603967e-09</v>
+        <v>1.86073649030226e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>9.277252847067931e-09</v>
+        <v>1.9045963388075e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>9.22603471919763e-09</v>
+        <v>1.853606021404639e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>9.252112084408086e-09</v>
+        <v>1.878914585664329e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.825659405912963e-09</v>
+        <v>1.256865069493572e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.274553198691311e-08</v>
+        <v>2.497420045609871e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.516699932737462e-09</v>
+        <v>1.013159995377582e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>5.591460191099284e-09</v>
+        <v>1.200629197180691e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.630519571068493e-09</v>
+        <v>1.237587322146785e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.855423121585102e-09</v>
+        <v>1.436380960544824e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.60986555018611e-09</v>
+        <v>1.217162829166464e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>5.617027943292754e-09</v>
+        <v>1.224290310400138e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.661081350755433e-09</v>
+        <v>1.268150158905147e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>5.609863222886439e-09</v>
+        <v>1.217159841502515e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.635284046247652e-09</v>
+        <v>1.242352854397369e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.25312814108237e-09</v>
+        <v>9.800995683830694e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>5.639730114733092e-09</v>
+        <v>1.24679892288281e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.91793619840434e-10</v>
+        <v>4.917936198404364e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.286845360995041e-10</v>
+        <v>4.286845360995054e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.198207892578654e-10</v>
+        <v>5.198207892578709e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.91037809695832e-10</v>
+        <v>4.910378096958311e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.910378096958319e-10</v>
+        <v>4.910378096958311e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.073984909329203e-10</v>
+        <v>5.073984909329215e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.139510019800093e-10</v>
+        <v>5.139510019800104e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.208606748781932e-10</v>
+        <v>5.208606748781955e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.840392949943636e-10</v>
+        <v>5.840392949943643e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.034159807378279e-10</v>
+        <v>7.034159807378303e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.255306014834515e-10</v>
+        <v>5.255306014834524e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.665634866379926e-10</v>
+        <v>5.665634866379923e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.046173067320475e-10</v>
+        <v>5.046173067320485e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.988005372786926e-10</v>
+        <v>5.988005372786945e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.701825230401233e-10</v>
+        <v>5.701825230401235e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.701825230401232e-10</v>
+        <v>5.701825230401235e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.845123209336603e-10</v>
+        <v>5.845123209336626e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.914500249141714e-10</v>
+        <v>5.91450024914172e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.999250158767294e-10</v>
+        <v>5.999250158767314e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.641494000781062e-10</v>
+        <v>6.641494000781055e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.794808142381246e-10</v>
+        <v>7.794808142381283e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.053750635322512e-10</v>
+        <v>6.053750635322505e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.212732275132651e-09</v>
+        <v>4.308243747884409e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.187922709905563e-09</v>
+        <v>4.27632412197304e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.229393239739405e-09</v>
+        <v>4.474853393951946e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.228768545163194e-09</v>
+        <v>4.479133533846301e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.228768545163197e-09</v>
+        <v>4.479133533846301e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.221810096951648e-09</v>
+        <v>4.400658535638998e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.225923560234017e-09</v>
+        <v>4.440156598898079e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.22999797398829e-09</v>
+        <v>4.481300373931399e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.233866724386458e-09</v>
+        <v>4.519588240422498e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.217857216492526e-09</v>
+        <v>4.35949316148317e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23282597612344e-09</v>
+        <v>4.509180757792305e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.559640947912874e-09</v>
+        <v>8.438802989595744e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.320204009554126e-09</v>
+        <v>1.154913916994601e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>7.005361404468431e-09</v>
+        <v>1.46405573087911e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.118506065006922e-09</v>
+        <v>1.484507151260217e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>7.118506065006922e-09</v>
+        <v>1.484507151260217e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>6.422513284623248e-09</v>
+        <v>1.355389609634349e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>7.329605820546909e-09</v>
+        <v>1.518263731883953e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.118506434590009e-09</v>
+        <v>1.484507520843323e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>7.71062319519247e-09</v>
+        <v>1.591867956727394e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.962443594349648e-09</v>
+        <v>1.270996514126382e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>8.182592471278485e-09</v>
+        <v>1.6740769722987e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.690030566839856e-09</v>
+        <v>5.148288736737216e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.684098901255662e-09</v>
+        <v>5.149594214017299e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>3.561205002032321e-09</v>
+        <v>5.317706314005481e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.687584274654655e-09</v>
+        <v>5.286649213375669e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.708438166155837e-09</v>
+        <v>5.323352062218856e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.699108388658847e-09</v>
+        <v>8.442901616261279e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.572637884239433e-09</v>
+        <v>8.570373786767565e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>1.707296265695495e-09</v>
+        <v>8.523543454553671e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>1.764963087729213e-09</v>
+        <v>5.454317834840825e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.695022400716898e-09</v>
+        <v>5.199303881167426e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.710888589441466e-09</v>
+        <v>5.350570952672839e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.680005546819626e-09</v>
+        <v>1.217064466345027e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.678944669453796e-09</v>
+        <v>1.218052272794819e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.696499911285955e-09</v>
+        <v>1.233696109327224e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.698336666373992e-09</v>
+        <v>1.234557338455213e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.698336666373992e-09</v>
+        <v>1.234557338455213e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.689083368638631e-09</v>
+        <v>1.226305945120478e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.693196831920993e-09</v>
+        <v>1.230255751446395e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.697271245675272e-09</v>
+        <v>1.234370128949722e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.701139996073441e-09</v>
+        <v>1.238198915598836e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.685130488179501e-09</v>
+        <v>1.222189407704898e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.700099247810411e-09</v>
+        <v>1.237158167335816e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.50906705084713e-09</v>
+        <v>1.186979291216885e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.62125675030744e-09</v>
+        <v>1.735899196219051e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.282310926064464e-09</v>
+        <v>1.864798844508544e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>7.788401600028252e-09</v>
+        <v>1.60240876478513e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.625694499918834e-09</v>
+        <v>1.221772317228387e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.629556345409707e-09</v>
+        <v>1.743829186227937e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.633669808696069e-09</v>
+        <v>1.747778992554549e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.637744222446344e-09</v>
+        <v>1.75189337005718e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.642224454774411e-09</v>
+        <v>1.755829777525368e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.456395926662809e-09</v>
+        <v>1.1819321250961e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.189070168026425e-08</v>
+        <v>2.326704189543869e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.105745432692431e-09</v>
+        <v>9.399946877599734e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>5.070840503285536e-09</v>
+        <v>1.11102594012914e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.088563591226687e-09</v>
+        <v>1.126699317576564e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.204090462778134e-09</v>
+        <v>1.323570006140021e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.089166028640048e-09</v>
+        <v>1.127343306794993e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>5.080979202470364e-09</v>
+        <v>1.119279612454805e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.085092665752737e-09</v>
+        <v>1.123229418780714e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>5.089167079507008e-09</v>
+        <v>1.127343796284044e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.093035829905177e-09</v>
+        <v>1.131172582933152e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.517232295426283e-09</v>
+        <v>9.010479671436139e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>5.091995081642161e-09</v>
+        <v>1.130131834670134e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.775083224639017e-10</v>
+        <v>4.775083224639015e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.31578310719305e-10</v>
+        <v>4.315783107193047e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.028124536940867e-10</v>
+        <v>5.028124536940863e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.896135908995475e-10</v>
+        <v>4.896135908995472e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.896135908995475e-10</v>
+        <v>4.896135908995471e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.903614304928043e-10</v>
+        <v>4.903614304928039e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.922656147641844e-10</v>
+        <v>4.92265614764184e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.050974447421619e-10</v>
+        <v>5.05097444742162e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.787679023241749e-10</v>
+        <v>5.787679023241743e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>6.980673074767826e-10</v>
+        <v>6.980673074767818e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.060294016555713e-10</v>
+        <v>5.060294016555712e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.514234713445886e-10</v>
+        <v>5.514234713445884e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.06915806021658e-10</v>
+        <v>5.069158060216575e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.805284639942939e-10</v>
+        <v>5.805284639942936e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.676818998357261e-10</v>
+        <v>5.676818998357251e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.676818998357261e-10</v>
+        <v>5.676818998357251e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.662072080911337e-10</v>
+        <v>5.662072080911332e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.677592980188839e-10</v>
+        <v>5.677592980188837e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.83208413867704e-10</v>
+        <v>5.832084138677035e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.575642691721479e-10</v>
+        <v>6.57564269172147e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.726058346299166e-10</v>
+        <v>7.726058346299159e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.842358704666289e-10</v>
+        <v>5.842358704666286e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.216590010419069e-09</v>
+        <v>4.331192243321224e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.191403866396497e-09</v>
+        <v>4.30624233365265e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.231632244208421e-09</v>
+        <v>4.481614581214725e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.233575927414321e-09</v>
+        <v>4.496524099720083e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.23357592741432e-09</v>
+        <v>4.496524099720085e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.224019461483947e-09</v>
+        <v>4.407226852666505e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.225383454835138e-09</v>
+        <v>4.419126687481894e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.232900482163942e-09</v>
+        <v>4.49533975372949e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.235907847545044e-09</v>
+        <v>4.524370614580942e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.219057083189786e-09</v>
+        <v>4.355862971028365e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.233583829667186e-09</v>
+        <v>4.501130435802384e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.796613619003091e-09</v>
+        <v>8.872033769824062e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.643658579825653e-09</v>
+        <v>1.214221058682809e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>7.081007797000142e-09</v>
+        <v>1.477651549834414e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.263657460741859e-09</v>
+        <v>1.510946754086918e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>7.263657460741859e-09</v>
+        <v>1.510946754086918e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>6.498996226758027e-09</v>
+        <v>1.369118590924206e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>7.125907654584081e-09</v>
+        <v>1.480404922276825e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.263657999290797e-09</v>
+        <v>1.51094729263585e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>7.771060314180448e-09</v>
+        <v>1.602623889353522e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.942510020831728e-09</v>
+        <v>1.266914009623183e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>8.11253929750704e-09</v>
+        <v>1.660809199359768e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.529638699330788e-09</v>
+        <v>8.402157913746895e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.702866916709674e-09</v>
+        <v>5.20641729732615e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.723975626327736e-09</v>
+        <v>5.348138929049354e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.703610350184182e-09</v>
+        <v>5.323784679312441e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.725425509232341e-09</v>
+        <v>5.362179359029161e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>3.537068150395663e-09</v>
+        <v>8.478192523091245e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.597721078258553e-09</v>
+        <v>8.59444088208274e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>1.724170270829541e-09</v>
+        <v>5.359974577095417e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>3.579877075976166e-09</v>
+        <v>8.649756434265892e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.710116984198957e-09</v>
+        <v>5.220128392121449e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.725542422883155e-09</v>
+        <v>5.366977555170805e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.645171300726993e-09</v>
+        <v>1.212549527202894e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.645028442744877e-09</v>
+        <v>1.214462154555274e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.660047715027355e-09</v>
+        <v>1.227562576762338e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.663176854176686e-09</v>
+        <v>1.22926216885779e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.663176854176686e-09</v>
+        <v>1.22926216885779e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.652600751791876e-09</v>
+        <v>1.22015298813733e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.653964745143065e-09</v>
+        <v>1.221342971618962e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.661481772471872e-09</v>
+        <v>1.22896427824368e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.66448913785297e-09</v>
+        <v>1.231867364328868e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.647638373497708e-09</v>
+        <v>1.215016599973608e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.662165119975119e-09</v>
+        <v>1.22954334645101e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.443566954608214e-09</v>
+        <v>1.177067162478251e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.510220690334355e-09</v>
+        <v>1.718735987398563e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.158390579233236e-09</v>
+        <v>1.843270917526296e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>7.688296049048789e-09</v>
+        <v>1.585683145223976e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.558122974668802e-09</v>
+        <v>1.210772686164589e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.51536169190478e-09</v>
+        <v>1.723998910867059e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.516725685261714e-09</v>
+        <v>1.725188894349699e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.524242712584777e-09</v>
+        <v>1.732810200973409e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.527852313831761e-09</v>
+        <v>1.735819280570418e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.38911186891381e-09</v>
+        <v>1.169515935413392e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.172591183989712e-08</v>
+        <v>2.296762763374446e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.975846626464792e-09</v>
+        <v>9.187483861247383e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>4.90357289804095e-09</v>
+        <v>1.083965979394488e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>4.91875924395124e-09</v>
+        <v>1.097095806559892e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>5.990767285515393e-09</v>
+        <v>1.286918084460988e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>4.920025018078413e-09</v>
+        <v>1.09846744641322e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.911145207087944e-09</v>
+        <v>1.089656812976542e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>4.912509200439138e-09</v>
+        <v>1.090846796458172e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.920026227767945e-09</v>
+        <v>1.098468103082896e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>4.923033593149043e-09</v>
+        <v>1.101371189168085e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.368572338590486e-09</v>
+        <v>9.860621396576521e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>4.920709575271182e-09</v>
+        <v>1.099047171290224e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.047346571266744e-10</v>
+        <v>5.04734657126671e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.283444257460834e-10</v>
+        <v>4.283444257460832e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.325576742357331e-10</v>
+        <v>5.325576742357334e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.911510139154417e-10</v>
+        <v>4.91151013915438e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.911510139154417e-10</v>
+        <v>4.911510139154382e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.246078694676631e-10</v>
+        <v>5.246078694676628e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.976900517805387e-10</v>
+        <v>5.97690051780537e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.302791594325035e-10</v>
+        <v>5.30279159432503e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.730309649756407e-10</v>
+        <v>5.730309649756375e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.139454964219062e-10</v>
+        <v>7.139454964219084e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.695608097312605e-10</v>
+        <v>5.695608097312596e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.804766314620435e-10</v>
+        <v>5.804766314620377e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.046546366973015e-10</v>
+        <v>5.046546366973011e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.124788646580924e-10</v>
+        <v>6.124788646580888e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.70738454897357e-10</v>
+        <v>5.707384548973585e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.70738454897357e-10</v>
+        <v>5.707384548973534e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.033349423777153e-10</v>
+        <v>6.033349423777099e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.867996508853747e-10</v>
+        <v>6.86799650885373e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.09801772918744e-10</v>
+        <v>6.098017729187411e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.515019350373998e-10</v>
+        <v>6.515019350373972e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.918131087549362e-10</v>
+        <v>7.918131087549332e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.550456404393005e-10</v>
+        <v>6.550456404392994e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.249488825663297e-09</v>
+        <v>4.37643741634083e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.220757067860599e-09</v>
+        <v>4.318685569679565e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.266028430373391e-09</v>
+        <v>4.54183346344175e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.262595230850533e-09</v>
+        <v>4.524907294847926e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.262595230850533e-09</v>
+        <v>4.524907294847925e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.261096778838232e-09</v>
+        <v>4.494212982861852e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.304751133054901e-09</v>
+        <v>4.929060490256867e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.26461274822461e-09</v>
+        <v>4.528452234258481e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.26028905939865e-09</v>
+        <v>4.484439753694317e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.257901219640122e-09</v>
+        <v>4.460561356109005e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28805769365123e-09</v>
+        <v>4.76212609622025e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7390028937781e-09</v>
+        <v>8.757982152481036e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.376929143507764e-09</v>
+        <v>1.163354838318224e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>7.365100842615037e-09</v>
+        <v>1.527620085082178e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.291162415721818e-09</v>
+        <v>1.513518548272854e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>7.291162415721818e-09</v>
+        <v>1.513518548272854e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>7.015892626110269e-09</v>
+        <v>1.462265361917842e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.234125512527269e-08</v>
+        <v>2.435330741130778e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.291161700776598e-09</v>
+        <v>1.513517833327636e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>7.066962176203784e-09</v>
+        <v>1.470418438389461e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>6.596587011909381e-09</v>
+        <v>1.385664829958924e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.069113173492236e-08</v>
+        <v>2.131153631918268e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.674052921855341e-09</v>
+        <v>5.259330246840166e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.741960036184638e-09</v>
+        <v>5.236002788959306e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.769277852904902e-09</v>
+        <v>5.427552442297814e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.74486813012443e-09</v>
+        <v>5.373707592970663e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.767289138455872e-09</v>
+        <v>5.413168567420191e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>3.685660875030272e-09</v>
+        <v>8.7614457690374e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.773752736079983e-09</v>
+        <v>9.274503288034791e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>1.766256404635646e-09</v>
+        <v>8.795685020434023e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>3.713898557876429e-09</v>
+        <v>8.802792447615792e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.759921372921924e-09</v>
+        <v>5.344116821097362e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.791166139690612e-09</v>
+        <v>5.647596956451531e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.984592386944518e-09</v>
+        <v>1.271021963903829e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.981219551112482e-09</v>
+        <v>1.269709949480357e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>6.000955520045511e-09</v>
+        <v>1.287530509610893e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.000655783002768e-09</v>
+        <v>1.286389382145018e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>6.000655783002768e-09</v>
+        <v>1.286389382145018e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.996200340119455e-09</v>
+        <v>1.282799520555931e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>6.039854694336117e-09</v>
+        <v>1.326284271295433e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.999716309505834e-09</v>
+        <v>1.286223445695596e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.995392620679867e-09</v>
+        <v>1.281822197639181e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.99300478092133e-09</v>
+        <v>1.27943435788065e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>6.023161254932459e-09</v>
+        <v>1.309590831891774e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.826081106259333e-09</v>
+        <v>1.243123978654407e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.137621455821407e-09</v>
+        <v>1.825236681698947e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.842766399926512e-09</v>
+        <v>1.963689220806108e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>8.249770621678552e-09</v>
+        <v>1.682233591607036e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.946892573426964e-09</v>
+        <v>1.276927057310951e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>9.150832808797564e-09</v>
+        <v>1.838014832034795e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>9.194487163015513e-09</v>
+        <v>1.881499582774516e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>9.154348778183948e-09</v>
+        <v>1.841438757174456e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>9.150676217511833e-09</v>
+        <v>1.837152107672495e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.772950154080804e-09</v>
+        <v>1.240704743766581e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.263864941084224e-08</v>
+        <v>2.473916741022878e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.46839711038155e-09</v>
+        <v>1.004171596674707e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>5.531606215702014e-09</v>
+        <v>1.1905780028769e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.551519916169903e-09</v>
+        <v>1.208429843757395e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.780916794629395e-09</v>
+        <v>1.423715319447194e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.550102906434492e-09</v>
+        <v>1.207092076298684e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>5.546587004708984e-09</v>
+        <v>1.203667573952474e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.590241358925648e-09</v>
+        <v>1.24715232469198e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>5.550102974095372e-09</v>
+        <v>1.207091499092138e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.545779285269388e-09</v>
+        <v>1.20269025103572e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.900337879465358e-09</v>
+        <v>1.091537714405476e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>5.573547919521991e-09</v>
+        <v>1.230458885288318e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.677817347136501e-10</v>
+        <v>4.677817347136489e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.257708463414893e-10</v>
+        <v>4.257708463414894e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.947158255779233e-10</v>
+        <v>4.947158255779217e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.851615522498563e-10</v>
+        <v>4.851615522498565e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.851615522498562e-10</v>
+        <v>4.851615522498566e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.817549774714075e-10</v>
+        <v>4.817549774714055e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.855552918537946e-10</v>
+        <v>4.855552918537951e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.958380660681801e-10</v>
+        <v>4.958380660681824e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.709443733060276e-10</v>
+        <v>5.709443733060268e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>6.995852098232193e-10</v>
+        <v>6.995852098232185e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.962457405706059e-10</v>
+        <v>4.962457405706072e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.407262312754594e-10</v>
+        <v>5.407262312754614e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.997717214664931e-10</v>
+        <v>4.997717214664924e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.717060151494886e-10</v>
+        <v>5.7170601514949e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.623290817936453e-10</v>
+        <v>5.62329081793644e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.623290817936453e-10</v>
+        <v>5.623290817936445e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.567983549953987e-10</v>
+        <v>5.567983549953989e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.605261336957701e-10</v>
+        <v>5.605261336957696e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.729304062980161e-10</v>
+        <v>5.729304062980168e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.489327972073152e-10</v>
+        <v>6.489327972073157e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.740638456065198e-10</v>
+        <v>7.740638456065263e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.734728966212976e-10</v>
+        <v>5.734728966212987e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.198634218326687e-09</v>
+        <v>4.280897144433458e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.172796460152915e-09</v>
+        <v>4.243331323392012e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.214645394051249e-09</v>
+        <v>4.441008901679125e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.214954653270451e-09</v>
+        <v>4.4473363437775e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.214954653270451e-09</v>
+        <v>4.447336343777499e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.206718887139447e-09</v>
+        <v>4.363571727503271e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.209220054717415e-09</v>
+        <v>4.386755508340828e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.215143879407976e-09</v>
+        <v>4.447672732459751e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.21859599169396e-09</v>
+        <v>4.480514878106109e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.204705705362885e-09</v>
+        <v>4.341612014795619e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.215594075235955e-09</v>
+        <v>4.450495713526098e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.614413997645567e-09</v>
+        <v>8.532669532995992e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.336812791828303e-09</v>
+        <v>1.157200002742956e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>6.992697709939577e-09</v>
+        <v>1.461038092253877e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.110208121249405e-09</v>
+        <v>1.482298239119888e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>7.110208121249405e-09</v>
+        <v>1.482298239119888e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>6.379853729283547e-09</v>
+        <v>1.346828900034188e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>7.113085080039295e-09</v>
+        <v>1.477755789660366e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.110208527885566e-09</v>
+        <v>1.482298645756054e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>7.647242501726273e-09</v>
+        <v>1.579493267445463e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>6.097078324375178e-09</v>
+        <v>1.295218777759979e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>7.905809405234075e-09</v>
+        <v>1.622527463051992e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.495356720863097e-09</v>
+        <v>5.130399146328557e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.674801839466907e-09</v>
+        <v>5.126860786197146e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.699012461929584e-09</v>
+        <v>5.293496326842396e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.678157786277261e-09</v>
+        <v>5.262573853452036e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.699007366740903e-09</v>
+        <v>5.299269114869204e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.689390481740735e-09</v>
+        <v>5.213073729398367e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.554540799599937e-09</v>
+        <v>8.514519996967351e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>1.697815474009227e-09</v>
+        <v>8.489904315020601e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>1.754773161467592e-09</v>
+        <v>8.572485302882018e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.68796115869634e-09</v>
+        <v>5.192141608053807e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.698912643517891e-09</v>
+        <v>5.301136389093072e-10</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.614734186582836e-09</v>
+        <v>1.205323304644908e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.61320927896919e-09</v>
+        <v>1.205845784216158e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.630579978306328e-09</v>
+        <v>1.221305372785449e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.632611770012058e-09</v>
+        <v>1.222241282711269e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.632611770012058e-09</v>
+        <v>1.222241282711269e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.622818855395551e-09</v>
+        <v>1.21359076295189e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.625320022973591e-09</v>
+        <v>1.215909141035647e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.631243847664121e-09</v>
+        <v>1.222000863447538e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.634695959950108e-09</v>
+        <v>1.225285078012171e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.620805673619046e-09</v>
+        <v>1.211394791681125e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.631694043492108e-09</v>
+        <v>1.222283161554172e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.380595132930332e-09</v>
+        <v>1.164114831425364e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.413103031632988e-09</v>
+        <v>1.698627082014802e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.057216850900553e-09</v>
+        <v>1.824393459094121e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>7.601667227231968e-09</v>
+        <v>1.568795041304132e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.494126560994346e-09</v>
+        <v>1.19786788605622e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.420601606589099e-09</v>
+        <v>1.706000524493773e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.423102774170978e-09</v>
+        <v>1.708318902578203e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.429026598857643e-09</v>
+        <v>1.714410624989422e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.433074571047366e-09</v>
+        <v>1.717799710896546e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.33034711581643e-09</v>
+        <v>1.160274085784859e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.159657264540428e-08</v>
+        <v>2.272101789802165e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.0328777669572e-09</v>
+        <v>9.269165762993719e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>4.978288296244806e-09</v>
+        <v>1.094099691862175e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>4.995825614115373e-09</v>
+        <v>1.109588605293188e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.089066182304794e-09</v>
+        <v>1.302577258839477e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>4.996321811983681e-09</v>
+        <v>1.110254250705086e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.987897872671212e-09</v>
+        <v>1.1018446705979e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>4.990399040249213e-09</v>
+        <v>1.104163048681663e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.996322864939745e-09</v>
+        <v>1.110254771093557e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>4.999774977225742e-09</v>
+        <v>1.113538985658188e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>3.793523628494143e-09</v>
+        <v>1.003084963692981e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>4.996773060767755e-09</v>
+        <v>1.110537069200191e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.663525240755996e-10</v>
+        <v>4.663525240755982e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.270766998941488e-10</v>
+        <v>4.270766998941485e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.895183909702819e-10</v>
+        <v>4.895183909702799e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.822952138174018e-10</v>
+        <v>4.822952138174029e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.822952138174018e-10</v>
+        <v>4.822952138174029e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.789241576027764e-10</v>
+        <v>4.789241576027746e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.816373112727682e-10</v>
+        <v>4.816373112727661e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.941138986837909e-10</v>
+        <v>4.9411389868379e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.714570813661908e-10</v>
+        <v>5.71457081366189e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>6.927000112738446e-10</v>
+        <v>6.927000112738341e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.939387572221583e-10</v>
+        <v>4.939387572221567e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.388328143818703e-10</v>
+        <v>5.388328143818683e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.008174858267195e-10</v>
+        <v>5.008174858267189e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.654783601056238e-10</v>
+        <v>5.65478360105623e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.589544744778687e-10</v>
+        <v>5.589544744778694e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.589544744778687e-10</v>
+        <v>5.589544744778692e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.532927971441628e-10</v>
+        <v>5.532927971441619e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.557389993526263e-10</v>
+        <v>5.557389993526242e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.708087656496491e-10</v>
+        <v>5.708087656496478e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.497629226607096e-10</v>
+        <v>6.497629226607086e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.662305406911229e-10</v>
+        <v>7.66230540691118e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.705699539138653e-10</v>
+        <v>5.705699539138641e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.199923103672276e-09</v>
+        <v>4.291576763177681e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.172592269389898e-09</v>
+        <v>4.257133719738417e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.213694229920119e-09</v>
+        <v>4.429288025656078e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.217417636334411e-09</v>
+        <v>4.458645469994861e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.217417636334414e-09</v>
+        <v>4.458645469994862e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.207135139782478e-09</v>
+        <v>4.365849966969355e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.209029913844371e-09</v>
+        <v>4.382644864898645e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.216001125007683e-09</v>
+        <v>4.456156862397848e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.222978219406558e-09</v>
+        <v>4.522127920520504e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2040795146799e-09</v>
+        <v>4.333140873253921e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.216361113971141e-09</v>
+        <v>4.455956866166312e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.759672621910503e-09</v>
+        <v>8.79673589086529e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.547463630947368e-09</v>
+        <v>1.195690727435751e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>6.924081532909068e-09</v>
+        <v>1.447956962445814e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.23239971743125e-09</v>
+        <v>1.504501387536189e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>7.23239971743125e-09</v>
+        <v>1.504501387536189e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>6.44246615166796e-09</v>
+        <v>1.358003249795926e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>7.114639280899486e-09</v>
+        <v>1.477651729459535e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.232400257761885e-09</v>
+        <v>1.504501927866862e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>8.09100754659805e-09</v>
+        <v>1.660985947087887e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>6.058165916958024e-09</v>
+        <v>1.287633289497122e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>8.00896793946711e-09</v>
+        <v>1.641094481425986e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.51095540104367e-09</v>
+        <v>5.162898819139159e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.688921336149951e-09</v>
+        <v>5.165872872312004e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.710015483066483e-09</v>
+        <v>5.302813426460382e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.69070960274622e-09</v>
+        <v>5.291639326365982e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.71237840089008e-09</v>
+        <v>5.329776410892511e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>3.518167437153879e-09</v>
+        <v>8.433266788303277e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.576533707713781e-09</v>
+        <v>8.549451519530505e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>1.711070477668401e-09</v>
+        <v>8.523573683731764e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>3.564472748498339e-09</v>
+        <v>5.488350600023175e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.699533050700514e-09</v>
+        <v>5.205139091925195e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.712261854883266e-09</v>
+        <v>5.328742165442364e-10</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.573894997535595e-09</v>
+        <v>1.198976725466366e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.573055621671822e-09</v>
+        <v>1.20019491777885e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.587501679008974e-09</v>
+        <v>1.212718909434057e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.591887478685647e-09</v>
+        <v>1.215771235081481e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.591887478685647e-09</v>
+        <v>1.215771235081481e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.581107033645795e-09</v>
+        <v>1.206404045845532e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.583001807707689e-09</v>
+        <v>1.208083535638462e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.589973018871003e-09</v>
+        <v>1.215434735388383e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.596950113269881e-09</v>
+        <v>1.222031841200648e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.578051408543221e-09</v>
+        <v>1.203133136473991e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.590333007834462e-09</v>
+        <v>1.215414735765229e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.301840463071563e-09</v>
+        <v>1.151095127660149e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.281431889013774e-09</v>
+        <v>1.676869138248125e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>8.910888349324888e-09</v>
+        <v>1.79763496024023e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>7.483624101143055e-09</v>
+        <v>1.548716878829887e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.413550372211073e-09</v>
+        <v>1.18438390451203e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.286861221893425e-09</v>
+        <v>1.682616780396709e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.288755995960739e-09</v>
+        <v>1.684296270190588e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.29572720711863e-09</v>
+        <v>1.691647469939558e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.303289526519744e-09</v>
+        <v>1.698347575351658e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.250682548221791e-09</v>
+        <v>1.145516217369621e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.140665740753422e-08</v>
+        <v>2.239087824565507e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.897429604172704e-09</v>
+        <v>9.039188178332934e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>4.804293878663993e-09</v>
+        <v>1.064892851742615e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>4.818905617061976e-09</v>
+        <v>1.077446003264373e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>5.868681835164731e-09</v>
+        <v>1.264487041557816e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>4.821210108309788e-09</v>
+        <v>1.080132018630306e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.812345290637974e-09</v>
+        <v>1.071101979809301e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>4.814240064699845e-09</v>
+        <v>1.072781469602227e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.821211275863185e-09</v>
+        <v>1.08013266935215e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>4.828188370262026e-09</v>
+        <v>1.086729775164415e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.262025571444922e-09</v>
+        <v>9.715125903997415e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>4.821571264826618e-09</v>
+        <v>1.080112669728993e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.031890439112045e-10</v>
+        <v>5.031890439112046e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.586176531734813e-10</v>
+        <v>5.586176531734821e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.491215099508764e-10</v>
+        <v>5.491215099508771e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.979510701044294e-10</v>
+        <v>5.979510701044299e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.776007321046641e-10</v>
+        <v>4.77600732104664e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.013083485144371e-10</v>
+        <v>5.01308348514437e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.561194242981233e-10</v>
+        <v>6.561194242981243e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.344513152083399e-10</v>
+        <v>4.344513152083405e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>8.240240129609414e-10</v>
+        <v>8.2402401296094e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.749649674986682e-10</v>
+        <v>7.749649674986683e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>7.275894007165382e-10</v>
+        <v>7.275894007165386e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.948796102683813e-10</v>
+        <v>5.948796102683812e-10</v>
       </c>
       <c r="C3" t="n">
         <v>6.38769202025452e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.477114610956791e-10</v>
+        <v>6.477114610956794e-10</v>
       </c>
       <c r="E3" t="n">
         <v>6.793229796515203e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.589726416517538e-10</v>
+        <v>5.589726416517537e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.927164209772213e-10</v>
+        <v>5.927164209772217e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>7.701673319667939e-10</v>
+        <v>7.701673319667929e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.156815705067606e-10</v>
+        <v>5.15681570506761e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.195842505678849e-10</v>
+        <v>9.195842505678853e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.609301202807315e-10</v>
+        <v>8.609301202807312e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.529832637280576e-10</v>
+        <v>8.529832637280575e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.314989260760199e-09</v>
+        <v>4.966894305854873e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.259736620941654e-09</v>
+        <v>4.533152641711422e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.342294165497099e-09</v>
+        <v>5.239943353223848e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.265720443419241e-09</v>
+        <v>4.543684588508022e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.265720443419244e-09</v>
+        <v>4.543684588508021e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.313546488554476e-09</v>
+        <v>4.955142758510297e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.40588512289238e-09</v>
+        <v>5.875852927176676e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.273281789799861e-09</v>
+        <v>4.556904513248323e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.33030381533143e-09</v>
+        <v>5.120039851567183e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.292330447393505e-09</v>
+        <v>4.740306172187925e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.448379128471484e-09</v>
+        <v>6.300792982967693e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.13366414583615e-08</v>
+        <v>2.260500207805924e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>7.134717225647597e-09</v>
+        <v>1.487311844996569e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.416198531051733e-08</v>
+        <v>2.780259964620139e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.134717276532668e-09</v>
+        <v>1.487311895881658e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>7.134717276532661e-09</v>
+        <v>1.487311895881658e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.161215977276175e-08</v>
+        <v>2.308070204049993e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.273431045256206e-08</v>
+        <v>4.341388130399167e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.134706591482025e-09</v>
+        <v>1.487301210831004e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.366588370221762e-08</v>
+        <v>2.683066033484554e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>9.32951647554593e-09</v>
+        <v>1.888575350508746e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>9.784906941272003e-09</v>
+        <v>2.097308185399344e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.857328815149544e-09</v>
+        <v>9.441411897334472e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.812199919728162e-09</v>
+        <v>5.505488042306985e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.898760091627787e-09</v>
+        <v>6.219323377906988e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.790979495413694e-09</v>
+        <v>5.468140515009005e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.821668384040281e-09</v>
+        <v>5.522152958699128e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.862340772910547e-09</v>
+        <v>9.429660349989883e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>1.959267000153581e-09</v>
+        <v>1.032368044570475e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>3.815621344189209e-09</v>
+        <v>9.031422104727934e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>3.859104551383171e-09</v>
+        <v>9.570729122901728e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.838623792006634e-09</v>
+        <v>5.70178245349718e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>2.003153194419934e-09</v>
+        <v>7.277195333746235e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.079201570849369e-09</v>
+        <v>1.335190792617673e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>6.037504734054596e-09</v>
+        <v>1.294202447522585e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>6.106322823373421e-09</v>
+        <v>1.362463374565287e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>6.037138244328345e-09</v>
+        <v>1.294137987260426e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>6.037138244328344e-09</v>
+        <v>1.294137987260426e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>6.077758798643643e-09</v>
+        <v>1.334015637883217e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>6.17009743298155e-09</v>
+        <v>1.426086654749854e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>6.037494099889021e-09</v>
+        <v>1.294191813357019e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>6.094516125420598e-09</v>
+        <v>1.350505347188905e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>6.056542757482667e-09</v>
+        <v>1.31253197925098e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>6.212591438560647e-09</v>
+        <v>1.468580660328956e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.905914933929276e-09</v>
+        <v>1.304692344684998e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>9.177045848111536e-09</v>
+        <v>1.846761680602509e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.932343216622452e-09</v>
+        <v>2.035842960128341e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>8.271058116773307e-09</v>
+        <v>1.68730788268031e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.969103746773024e-09</v>
+        <v>1.282163915755573e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>9.216769176105781e-09</v>
+        <v>1.886481461322958e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>9.309107810443518e-09</v>
+        <v>1.978552478189572e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>9.176504477351174e-09</v>
+        <v>1.846657636796762e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>9.234177464614913e-09</v>
+        <v>1.903085739892893e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.821728502947779e-09</v>
+        <v>1.271204670676776e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.281157301774068e-08</v>
+        <v>2.630001411971366e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.668243830363302e-09</v>
+        <v>1.08686223163772e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>5.725950576471192e-09</v>
+        <v>1.239368916085024e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.794953566403725e-09</v>
+        <v>1.307662385635563e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.99463898358511e-09</v>
+        <v>1.462658116456471e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.725949670678026e-09</v>
+        <v>1.23936879859474e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>5.766204641060242e-09</v>
+        <v>1.279182106445657e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.858543275398148e-09</v>
+        <v>1.371253123312296e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>5.725939942305638e-09</v>
+        <v>1.239358281919461e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.782961967837197e-09</v>
+        <v>1.295671815751346e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>5.107990371347099e-09</v>
+        <v>1.145586760195725e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>5.901037280977243e-09</v>
+        <v>1.413747128891397e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.817456643711797e-10</v>
+        <v>4.817456643711823e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.615723267403297e-10</v>
+        <v>5.615723267403332e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.364480935190401e-10</v>
+        <v>5.364480935190332e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.992950209260669e-10</v>
+        <v>5.992950209260673e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.83857286961005e-10</v>
+        <v>4.838572869610053e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.952419643662242e-10</v>
+        <v>4.952419643662165e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.25297352400257e-10</v>
+        <v>6.252973524002592e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.42261076241108e-10</v>
+        <v>4.422610762411091e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.970458700048992e-10</v>
+        <v>7.970458700048995e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.700745882446922e-10</v>
+        <v>7.700745882446932e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>7.024585160804792e-10</v>
+        <v>7.024585160804868e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.681441997077426e-10</v>
+        <v>5.68144199707747e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.408191031714331e-10</v>
+        <v>6.408191031714307e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.310633248018339e-10</v>
+        <v>6.310633248018349e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.797693596021587e-10</v>
+        <v>6.797693596021588e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.643316256370946e-10</v>
+        <v>5.64331625637095e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.836677404521618e-10</v>
+        <v>5.836677404521644e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>7.325865523077007e-10</v>
+        <v>7.325865523077078e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.227574670046403e-10</v>
+        <v>5.227574670046441e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.882818442922516e-10</v>
+        <v>8.882818442922502e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.538398669872401e-10</v>
+        <v>8.538398669872398e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.220073017494139e-10</v>
+        <v>8.220073017494182e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.252358260553272e-09</v>
+        <v>4.756996620618107e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.217450973079544e-09</v>
+        <v>4.502368401800058e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.284876536743122e-09</v>
+        <v>5.082179382516599e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.22289172294006e-09</v>
+        <v>4.511944475739686e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.222891722940062e-09</v>
+        <v>4.511944475739686e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.260071573677046e-09</v>
+        <v>4.836681394231812e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.337684524440668e-09</v>
+        <v>5.610259259491993e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.228135711032734e-09</v>
+        <v>4.521101542436259e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.271502838481242e-09</v>
+        <v>4.948442399897816e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.241936922613635e-09</v>
+        <v>4.652783241221673e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.383560212043922e-09</v>
+        <v>6.069016135524663e-10</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.690022630019162e-09</v>
+        <v>1.960728583041016e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>7.187263361158576e-09</v>
+        <v>1.500923814788661e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.257236407742262e-08</v>
+        <v>2.494815734646686e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.187263404148443e-09</v>
+        <v>1.500923857778591e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>7.187263404148443e-09</v>
+        <v>1.500923857778591e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.059136258003691e-08</v>
+        <v>2.125975347643491e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9531896987917e-08</v>
+        <v>3.763207302169692e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.187254623529967e-09</v>
+        <v>1.500915077160088e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.205956568879778e-08</v>
+        <v>2.393543291357194e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>8.572526451977425e-09</v>
+        <v>1.7554620742992e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.516568501938874e-08</v>
+        <v>2.185591835159489e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.769476107011145e-09</v>
+        <v>8.923274007539733e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.73751490292094e-09</v>
+        <v>5.417680913361204e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.808001797716291e-09</v>
+        <v>6.002879836840252e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.717644641265053e-09</v>
+        <v>5.382709607273361e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.74512629105496e-09</v>
+        <v>5.431077310641497e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.777189420134909e-09</v>
+        <v>9.002958781153444e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.690569452323181e-09</v>
+        <v>9.751336710126361e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>1.745253557490617e-09</v>
+        <v>8.687378929357893e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>1.843506047320329e-09</v>
+        <v>9.093829058487707e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.756798841965356e-09</v>
+        <v>5.558940214370589e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.905647939809051e-09</v>
+        <v>6.987890531412296e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.648297284807113e-09</v>
+        <v>1.249384926138193e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.624083472915143e-09</v>
+        <v>1.22580415594858e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.68064476003509e-09</v>
+        <v>1.281873141358913e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.624117431881386e-09</v>
+        <v>1.22581016815031e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.624117431881386e-09</v>
+        <v>1.22581016815031e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.656010597930892e-09</v>
+        <v>1.257353403499568e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.733623548694506e-09</v>
+        <v>1.334711190025581e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.624074735286557e-09</v>
+        <v>1.225795418320008e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.667441862735071e-09</v>
+        <v>1.268529504066165e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.637875946867466e-09</v>
+        <v>1.238963588198549e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.779499236297787e-09</v>
+        <v>1.380586877628847e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.433646201449848e-09</v>
+        <v>1.211606335672019e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.429258250948987e-09</v>
+        <v>1.719514914208147e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.111156810069427e-09</v>
+        <v>1.885643258893364e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>7.603458976060972e-09</v>
+        <v>1.574174278038266e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.50525174834187e-09</v>
+        <v>1.20488980796071e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.460345447018032e-09</v>
+        <v>1.750916334264477e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.537958397781439e-09</v>
+        <v>1.82827412079046e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.428409584373714e-09</v>
+        <v>1.719358349084921e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.472370029458016e-09</v>
+        <v>1.762196858734412e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.367145649834167e-09</v>
+        <v>1.191315056178874e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.173741733568475e-08</v>
+        <v>2.429180457439045e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.206126050201134e-09</v>
+        <v>9.955627902229021e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>5.156458511224774e-09</v>
+        <v>1.143502163137033e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.213191763283316e-09</v>
+        <v>1.199601414376398e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.281064295026136e-09</v>
+        <v>1.341432815437262e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.156457716914628e-09</v>
+        <v>1.14350205876215e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>5.188385636240527e-09</v>
+        <v>1.175051410688021e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.265998587004118e-09</v>
+        <v>1.252409197214034e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>5.156449773596183e-09</v>
+        <v>1.143493425508461e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.199816901044727e-09</v>
+        <v>1.186227511254618e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>3.943122970004196e-09</v>
+        <v>9.406870658868547e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>5.311874274607374e-09</v>
+        <v>1.298284884817302e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.679869852871983e-10</v>
+        <v>4.679869852871992e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.835222769645446e-10</v>
+        <v>5.835222769645452e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.196459079935594e-10</v>
+        <v>5.196459079935584e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.201891770237739e-10</v>
+        <v>6.201891770237749e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.079623769207751e-10</v>
+        <v>5.07962376920775e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.872732074681762e-10</v>
+        <v>4.872732074681643e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.922620390175636e-10</v>
+        <v>5.922620390175598e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.66643583367668e-10</v>
+        <v>4.666435833676671e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.847230307688903e-10</v>
+        <v>7.847230307688896e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.649701676970341e-10</v>
+        <v>7.649701676970351e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>6.800454884492743e-10</v>
+        <v>6.80045488449277e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.509841308297146e-10</v>
+        <v>5.509841308297152e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.651143072935172e-10</v>
+        <v>6.651143072935207e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.104025930556297e-10</v>
+        <v>6.104025930556292e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>7.029921542197189e-10</v>
+        <v>7.029921542197194e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.907653541167197e-10</v>
+        <v>5.907653541167223e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.731672814667261e-10</v>
+        <v>5.731672814667366e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.932416972757807e-10</v>
+        <v>6.932416972757751e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.495882280038225e-10</v>
+        <v>5.495882280038258e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.738621756526715e-10</v>
+        <v>8.738621756526676e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.469808324830727e-10</v>
+        <v>8.469808324830747e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>7.948935271204033e-10</v>
+        <v>7.948935271203985e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.242855029890821e-09</v>
+        <v>4.67699211615628e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.234177706305002e-09</v>
+        <v>4.655387841652202e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.273564070465514e-09</v>
+        <v>4.984082521903177e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.239406795708115e-09</v>
+        <v>4.664591296382819e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.239406795708115e-09</v>
+        <v>4.664591296382815e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.254069096681251e-09</v>
+        <v>4.791199170636601e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.316727878205836e-09</v>
+        <v>5.415720599306408e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.241687618327334e-09</v>
+        <v>4.668569670033937e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.267162517017504e-09</v>
+        <v>4.920066987423095e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.238950948018377e-09</v>
+        <v>4.637951297431827e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.368915358606624e-09</v>
+        <v>5.937595403314275e-10</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.900976447952398e-09</v>
+        <v>1.815528573891112e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>8.446666200416188e-09</v>
+        <v>1.734936752250425e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.154519475051074e-08</v>
+        <v>2.306215242082475e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>8.446666231657802e-09</v>
+        <v>1.734936783492013e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>8.446666231657802e-09</v>
+        <v>1.734936783492013e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.011059407277719e-08</v>
+        <v>2.037868304410119e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.709092259306154e-08</v>
+        <v>3.317830314701786e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>8.44666187800038e-09</v>
+        <v>1.734932429834609e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.185852031093545e-08</v>
+        <v>2.35608566037116e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>8.292681993569929e-09</v>
+        <v>1.705251787033316e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.354570471626931e-08</v>
+        <v>4.496874446130652e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.765619905943319e-09</v>
+        <v>5.59705829302317e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.760365222516161e-09</v>
+        <v>5.581477865165738e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>3.635878216531127e-09</v>
+        <v>9.141755396449865e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.740279788504066e-09</v>
+        <v>5.546127758927038e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.76537514839828e-09</v>
+        <v>5.590295592101558e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.776833972733751e-09</v>
+        <v>5.711265347503494e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.669564396334764e-09</v>
+        <v>9.55671284877493e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>3.608719584436638e-09</v>
+        <v>8.834545907812575e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>3.62245050548518e-09</v>
+        <v>5.936841558617628e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.75954122095821e-09</v>
+        <v>5.554190172841195e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.896427973696353e-09</v>
+        <v>6.866017600841458e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.611727442613731e-09</v>
+        <v>1.236620752088378e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.610564353466006e-09</v>
+        <v>1.235782829891916e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.642265805515547e-09</v>
+        <v>1.267299753392806e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.61114693891236e-09</v>
+        <v>1.235885390673013e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.61114693891236e-09</v>
+        <v>1.235885390673013e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.622941509404159e-09</v>
+        <v>1.248041457536386e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.685600290928746e-09</v>
+        <v>1.310493600403391e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.610560031050248e-09</v>
+        <v>1.235778507476146e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.636034929740412e-09</v>
+        <v>1.260928239215059e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.607823360741283e-09</v>
+        <v>1.232716670215933e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.737787771329538e-09</v>
+        <v>1.362681080804183e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.362963171001337e-09</v>
+        <v>1.192838240521835e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.339059924088075e-09</v>
+        <v>1.715998047719295e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>8.986649095444202e-09</v>
+        <v>1.855911209230793e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>7.524988404444009e-09</v>
+        <v>1.572721486781405e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.456581008785721e-09</v>
+        <v>1.208681787118136e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.350081074815513e-09</v>
+        <v>1.728018018447987e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.412739856339977e-09</v>
+        <v>1.790470161314963e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.337699596461591e-09</v>
+        <v>1.715755068387738e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.363759345900812e-09</v>
+        <v>1.741007733857926e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.303780147495683e-09</v>
+        <v>1.179205064974663e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.157350773588806e-08</v>
+        <v>2.389767789001098e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.070912001399376e-09</v>
+        <v>9.654372359040866e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>5.007697172692315e-09</v>
+        <v>1.129678206650681e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.039570462845899e-09</v>
+        <v>1.161225373657723e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.090069673621684e-09</v>
+        <v>1.320175791525118e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.007696416613277e-09</v>
+        <v>1.129678099323872e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>5.020074328630458e-09</v>
+        <v>1.141936834295158e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.082733110155051e-09</v>
+        <v>1.204388977162158e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>5.007692850276549e-09</v>
+        <v>1.129673884234911e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.033167748966717e-09</v>
+        <v>1.154823615973828e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.461505762334166e-09</v>
+        <v>1.030964773989495e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>5.13492059055584e-09</v>
+        <v>1.256576457562947e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.072801639675392e-10</v>
+        <v>4.072801639675406e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.042462261176087e-10</v>
+        <v>5.042462261176091e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.267208780642097e-10</v>
+        <v>4.267208780642102e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.372912378161304e-10</v>
+        <v>5.372912378161296e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.360282480049952e-10</v>
+        <v>4.360282480049937e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.204635140895676e-10</v>
+        <v>4.204635140895649e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.798294937453543e-10</v>
+        <v>4.798294937453539e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>3.999783541971268e-10</v>
+        <v>3.999783541971259e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.146588325288405e-10</v>
+        <v>7.146588325288369e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.096103517949006e-10</v>
+        <v>7.096103517948999e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.752821129012556e-10</v>
+        <v>4.752821129012557e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.795009534432818e-10</v>
+        <v>4.795009534432801e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.741950785947335e-10</v>
+        <v>5.741950785947334e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.018618017862467e-10</v>
+        <v>5.018618017862441e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.084226256088173e-10</v>
+        <v>6.084226256088165e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.071596357976811e-10</v>
+        <v>5.071596357976805e-10</v>
       </c>
       <c r="G3" t="n">
         <v>4.946645370063591e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6226942914623e-10</v>
+        <v>5.622694291462297e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.711002760747917e-10</v>
+        <v>4.711002760747897e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>7.957732574643462e-10</v>
+        <v>7.957732574643447e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.833437546358541e-10</v>
+        <v>7.833437546358514e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.577215220124362e-10</v>
+        <v>5.577215220124367e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.177926318106322e-09</v>
+        <v>4.275338103591454e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.163681418440473e-09</v>
+        <v>4.214740837733477e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.189482998863858e-09</v>
+        <v>4.390904911166807e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.169029356836581e-09</v>
+        <v>4.224153513886398e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.169029356836581e-09</v>
+        <v>4.224153513886401e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.185478498631173e-09</v>
+        <v>4.353206351815984e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.221060365124679e-09</v>
+        <v>4.706678573775008e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.172986300072221e-09</v>
+        <v>4.231082488173238e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.213123640254403e-09</v>
+        <v>4.627311325072254e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.183912614727279e-09</v>
+        <v>4.335201069801023e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.218380120391895e-09</v>
+        <v>4.679876126447165e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.837660630722119e-09</v>
+        <v>1.423647043981981e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>6.11115509577262e-09</v>
+        <v>1.292229446265529e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>7.86300381000656e-09</v>
+        <v>1.613630147513432e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.111155132741888e-09</v>
+        <v>1.292229483234796e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.111155132741888e-09</v>
+        <v>1.292229483234796e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>7.668657841541354e-09</v>
+        <v>1.576360193350951e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.168282854247317e-08</v>
+        <v>2.311939046613711e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>6.111150855342599e-09</v>
+        <v>1.292225205835511e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.080675756818192e-08</v>
+        <v>2.151210694673264e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>7.345339415665247e-09</v>
+        <v>1.51793121806919e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.024156263501023e-08</v>
+        <v>2.383390811555883e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.755113513939294e-09</v>
+        <v>5.291187562752979e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.744810997274488e-09</v>
+        <v>5.237528890939246e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.767751553937768e-09</v>
+        <v>8.78252715023732e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.724479346361879e-09</v>
+        <v>5.201745490153733e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.750233115442359e-09</v>
+        <v>5.247072123489765e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>3.683014915842936e-09</v>
+        <v>5.369055810977522e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.705225314786064e-09</v>
+        <v>9.078808861488226e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>3.670522717283986e-09</v>
+        <v>5.246931947334779e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>3.701118629287132e-09</v>
+        <v>9.006182482042496e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.760763308283768e-09</v>
+        <v>5.350458284959157e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.79708060795978e-09</v>
+        <v>5.698388979047723e-10</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.722443982202748e-09</v>
+        <v>1.227368914906126e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.717508204598667e-09</v>
+        <v>1.222947593794323e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.733819378904835e-09</v>
+        <v>1.238893689670076e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.717745375888009e-09</v>
+        <v>1.2229893664037e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.717745375888009e-09</v>
+        <v>1.2229893664037e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.729996162727598e-09</v>
+        <v>1.235155739728579e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.765578029221103e-09</v>
+        <v>1.270502961924482e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.717503964168646e-09</v>
+        <v>1.222943353364304e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.757641304350824e-09</v>
+        <v>1.262566237054207e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.728430278823706e-09</v>
+        <v>1.233355211527083e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.762897784488321e-09</v>
+        <v>1.267822717191697e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.378158887649249e-09</v>
+        <v>1.166774738593046e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.394965070298708e-09</v>
+        <v>1.694179999603223e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.036770248612931e-09</v>
+        <v>1.820213039588764e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>7.568673645128013e-09</v>
+        <v>1.548752740024759e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.469224091849819e-09</v>
+        <v>1.179249620649988e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.406405152064648e-09</v>
+        <v>1.70620371929948e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.441987018557965e-09</v>
+        <v>1.74155094149535e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.393912953505696e-09</v>
+        <v>1.693991332935204e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.434643947028022e-09</v>
+        <v>1.733718699612408e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.328034240803934e-09</v>
+        <v>1.162885509217452e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.159467433114707e-08</v>
+        <v>2.294215383842027e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.269115077735805e-09</v>
+        <v>9.715830291059461e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>5.272234209450257e-09</v>
+        <v>1.14457937107285e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.288727908046842e-09</v>
+        <v>1.16055759122354e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.43550842914253e-09</v>
+        <v>1.349315663091984e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.272233502771144e-09</v>
+        <v>1.144579277160003e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>5.284722167579193e-09</v>
+        <v>1.156787517007106e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.320304034072694e-09</v>
+        <v>1.192134739203008e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>5.272229969020239e-09</v>
+        <v>1.144575130642832e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.312367309202413e-09</v>
+        <v>1.184198014332732e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.013834894236169e-09</v>
+        <v>1.052190589853189e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>5.317623789339909e-09</v>
+        <v>1.189454494470224e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.268103441221252e-10</v>
+        <v>4.268103441221272e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.046361644717953e-10</v>
+        <v>5.046361644717949e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.014816940029779e-10</v>
+        <v>4.014816940029808e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.352034340197483e-10</v>
+        <v>5.352034340197469e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.41509310145441e-10</v>
+        <v>4.415093101454405e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.136121627065388e-10</v>
+        <v>4.136121627065401e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.136446331031833e-10</v>
+        <v>4.13644633103183e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.08086964192586e-10</v>
+        <v>4.080869641925882e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.046951121277287e-10</v>
+        <v>7.046951121277286e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.057404131809467e-10</v>
+        <v>7.057404131809448e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.171235278696789e-10</v>
+        <v>4.171235278696786e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.997837245606277e-10</v>
+        <v>4.997837245606299e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.736277235165032e-10</v>
+        <v>5.73627723516503e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.706505301095422e-10</v>
+        <v>4.706505301095448e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.053722891979729e-10</v>
+        <v>6.053722891979762e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.116781653236655e-10</v>
+        <v>5.116781653236668e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.846030819376595e-10</v>
+        <v>4.846030819376639e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.839159480782692e-10</v>
+        <v>4.839159480782689e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.782999985817418e-10</v>
+        <v>4.782999985817424e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>7.849092071617887e-10</v>
+        <v>7.849092071617877e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.776961555446044e-10</v>
+        <v>7.776961555446031e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.886486807601875e-10</v>
+        <v>4.886486807601876e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.140104458180626e-09</v>
+        <v>4.313430800215613e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.120623257476851e-09</v>
+        <v>4.187686620515196e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.125047648950739e-09</v>
+        <v>4.162862707916762e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.125474144471975e-09</v>
+        <v>4.196224465977831e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.125474144471975e-09</v>
+        <v>4.196224465977832e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.131980603966052e-09</v>
+        <v>4.23448375771986e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.132298117444457e-09</v>
+        <v>4.235367392853954e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.128415194843629e-09</v>
+        <v>4.201382296140032e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.168760204793477e-09</v>
+        <v>4.599988266344139e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.136077068558857e-09</v>
+        <v>4.273156903997937e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.134387150963907e-09</v>
+        <v>4.256257728048422e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.627392653402529e-09</v>
+        <v>1.573105796193857e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>6.280989673024742e-09</v>
+        <v>1.32699314626664e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>6.280456478834236e-09</v>
+        <v>1.323638219934589e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.280989707539e-09</v>
+        <v>1.326993180780897e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.280989707538999e-09</v>
+        <v>1.326993180780897e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>6.948531161520791e-09</v>
+        <v>1.447161268354518e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>7.393211458559372e-09</v>
+        <v>1.525457481350748e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>6.280987472288533e-09</v>
+        <v>1.326990945530431e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.046827047658612e-08</v>
+        <v>2.096712625601213e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>7.145457067597922e-09</v>
+        <v>1.484966564499678e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>8.305099979266987e-09</v>
+        <v>1.687671223747659e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.685165196814733e-09</v>
+        <v>8.405735298999203e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.669719137860304e-09</v>
+        <v>5.154095364753491e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.668451687301131e-09</v>
+        <v>5.119255964195136e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.650580261448889e-09</v>
+        <v>5.120411226849392e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.673652079004256e-09</v>
+        <v>5.16101762552681e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.67704134260016e-09</v>
+        <v>5.193790652517787e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.444598165528184e-09</v>
+        <v>5.194998618665696e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>1.673475933477739e-09</v>
+        <v>5.160689190937952e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>1.766545624616121e-09</v>
+        <v>8.676799747536748e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.681492744479311e-09</v>
+        <v>5.233088488416443e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.679561252807602e-09</v>
+        <v>5.215764142094144e-10</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.317446349885516e-09</v>
+        <v>1.166555248977801e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.305759287284724e-09</v>
+        <v>1.15535259930645e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.302221651556854e-09</v>
+        <v>1.15146889126669e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.306041488352149e-09</v>
+        <v>1.155402295133794e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.30604148835215e-09</v>
+        <v>1.155402295133794e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.309322495670938e-09</v>
+        <v>1.158660544728226e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.309640009149347e-09</v>
+        <v>1.158748908241635e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.305757086548513e-09</v>
+        <v>1.155350398570241e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.346102096498362e-09</v>
+        <v>1.195210995590651e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.313418960263753e-09</v>
+        <v>1.162527859356032e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.311729042668799e-09</v>
+        <v>1.160837941761081e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.923147650383081e-09</v>
+        <v>1.097158678241402e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>7.636527343412575e-09</v>
+        <v>1.565567774962157e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>8.19699147057476e-09</v>
+        <v>1.660948376653174e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>6.891372052137019e-09</v>
+        <v>1.434420472848039e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>4.998077310241018e-09</v>
+        <v>1.101200600079933e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>7.639074720801996e-09</v>
+        <v>1.568696934129465e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>7.639392234280349e-09</v>
+        <v>1.568785297642864e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>7.635509311679581e-09</v>
+        <v>1.565386787971479e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>7.67638967602283e-09</v>
+        <v>1.60534160736462e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>4.868519616280668e-09</v>
+        <v>1.084225575239298e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.048698024031841e-08</v>
+        <v>2.071682147611906e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.840447591526823e-09</v>
+        <v>9.066034689152452e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>4.714986008732566e-09</v>
+        <v>1.051376502844673e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>4.711617439630787e-09</v>
+        <v>1.047522550530944e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>5.73767176715269e-09</v>
+        <v>1.231369223791054e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>4.714985440658412e-09</v>
+        <v>1.051376431303369e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.718549217118788e-09</v>
+        <v>1.054684448266447e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7188667305972e-09</v>
+        <v>1.054772811779858e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.714983807996373e-09</v>
+        <v>1.051374302108464e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>4.755328817946207e-09</v>
+        <v>1.091234899128875e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.188330991215876e-09</v>
+        <v>9.64512377876571e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>4.720955764116646e-09</v>
+        <v>1.056861845299303e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.51060380869719e-10</v>
+        <v>4.510603808697196e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.116217618820845e-10</v>
+        <v>5.116217618820855e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.214657450403637e-10</v>
+        <v>4.214657450403642e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.419550040537892e-10</v>
+        <v>5.4195500405379e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.491114623832955e-10</v>
+        <v>4.491114623832958e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.183523339988219e-10</v>
+        <v>4.183523339988228e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.058714160895526e-10</v>
+        <v>4.058714160895533e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.160574259833036e-10</v>
+        <v>4.160574259833042e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>8.118149176503299e-10</v>
+        <v>8.118149176503326e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.06810395338968e-10</v>
+        <v>7.068103953389684e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.304532178606849e-10</v>
+        <v>4.304532178606853e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.270570062814738e-10</v>
+        <v>5.270570062814747e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.811958651608866e-10</v>
+        <v>5.81195865160888e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.930170445673717e-10</v>
+        <v>4.930170445673729e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.127020074456222e-10</v>
+        <v>6.127020074456233e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.198584657751282e-10</v>
+        <v>5.198584657751292e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.894359769284431e-10</v>
+        <v>4.894359769284452e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.743574449884753e-10</v>
+        <v>4.743574449884758e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.86904359359447e-10</v>
+        <v>4.869043593594481e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.077572626632984e-10</v>
+        <v>9.077572626633004e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.784873868371953e-10</v>
+        <v>7.784873868371961e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.033609141577931e-10</v>
+        <v>5.033609141577932e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.15666961379396e-09</v>
+        <v>4.46331967305679e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.127524487281258e-09</v>
+        <v>4.240831144037748e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.139076856824494e-09</v>
+        <v>4.287392103362232e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.132424789811394e-09</v>
+        <v>4.249455963140226e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.132424789811393e-09</v>
+        <v>4.249455963140229e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.136949815378374e-09</v>
+        <v>4.268397993092369e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.12982972707038e-09</v>
+        <v>4.19492080582095e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.135315843190506e-09</v>
+        <v>4.254529367543115e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.235606503152092e-09</v>
+        <v>5.252688566638101e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.139574293538937e-09</v>
+        <v>4.292366470506528e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.144458886748006e-09</v>
+        <v>4.341212402597232e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.847926788476837e-09</v>
+        <v>1.799993222714913e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>6.700730578918389e-09</v>
+        <v>1.404967381216826e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>7.281906701563436e-09</v>
+        <v>1.509877257152018e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.700730613711625e-09</v>
+        <v>1.404967416010067e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.700730613711625e-09</v>
+        <v>1.404967416010067e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>7.230060342834407e-09</v>
+        <v>1.499227246330688e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>7.09547652004601e-09</v>
+        <v>1.469445910456525e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>6.700728811585812e-09</v>
+        <v>1.404965613884268e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.650559939159159e-08</v>
+        <v>3.212787590466567e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>7.190433062091443e-09</v>
+        <v>1.494187784545349e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>8.783412099980569e-09</v>
+        <v>1.779353388153896e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.705977947324273e-09</v>
+        <v>5.430102334831531e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.680591691464531e-09</v>
+        <v>5.214229418125878e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>3.466348540636634e-09</v>
+        <v>5.252921549697313e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.66104063101603e-09</v>
+        <v>5.179819838619111e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.684576252986056e-09</v>
+        <v>5.221242533061909e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.686258148908668e-09</v>
+        <v>8.379643514070911e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.446803311014368e-09</v>
+        <v>8.272794291465998e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>1.684624176720822e-09</v>
+        <v>5.221312029317863e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>1.839457778078138e-09</v>
+        <v>9.337002375485961e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.688334673746099e-09</v>
+        <v>5.25818473443774e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.693722016724711e-09</v>
+        <v>5.307915506118056e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.323667747424687e-09</v>
+        <v>1.179723634850729e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.302315744153829e-09</v>
+        <v>1.158846371631958e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.30590743857063e-09</v>
+        <v>1.162101388749746e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.302588056997332e-09</v>
+        <v>1.158894327361773e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.302588056997332e-09</v>
+        <v>1.158894327361773e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.303947949009119e-09</v>
+        <v>1.160231466854287e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.296827860701116e-09</v>
+        <v>1.152883748127146e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.302313976821242e-09</v>
+        <v>1.158844604299363e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.402604636782829e-09</v>
+        <v>1.25866052420886e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.306572427169636e-09</v>
+        <v>1.162628314595703e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.311457020378735e-09</v>
+        <v>1.167512907804774e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.908055275999483e-09</v>
+        <v>1.106575840276249e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>7.591946004142556e-09</v>
+        <v>1.561821295207199e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>8.15544511065405e-09</v>
+        <v>1.66362001631889e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>6.85221018463999e-09</v>
+        <v>1.431627820349043e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>4.972685940913682e-09</v>
+        <v>1.100831555245667e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>7.5925761493955e-09</v>
+        <v>1.563030027939691e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>7.585456061087594e-09</v>
+        <v>1.555682309212562e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>7.590942177207653e-09</v>
+        <v>1.561643165384767e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>7.691764298264623e-09</v>
+        <v>1.661552622446544e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>4.840727296881996e-09</v>
+        <v>1.080639572109342e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.042489072769e-08</v>
+        <v>2.067477235415012e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.761854002105481e-09</v>
+        <v>9.048444171640152e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>4.600543410945066e-09</v>
+        <v>1.035334441656477e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>4.604303836060411e-09</v>
+        <v>1.038619155377048e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>5.59301335486288e-09</v>
+        <v>1.210009179509138e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>4.600542877537891e-09</v>
+        <v>1.035334376446434e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.602175615800327e-09</v>
+        <v>1.036719536878807e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>4.595055527492316e-09</v>
+        <v>1.029371818151664e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.600541643612458e-09</v>
+        <v>1.035332674323883e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>4.700832303574025e-09</v>
+        <v>1.135148594233381e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.106489217945521e-09</v>
+        <v>9.478554526193033e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>4.609684687169938e-09</v>
+        <v>1.044000977829294e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.509519447523738e-10</v>
+        <v>4.509519447523739e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.269630094841244e-10</v>
+        <v>5.269630094841247e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.308921991043555e-10</v>
+        <v>5.308921991043552e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.621779775387283e-10</v>
+        <v>5.621779775387284e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.543094267438896e-10</v>
+        <v>4.543094267438893e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.765414478326579e-10</v>
+        <v>4.765414478326569e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.41920564336046e-10</v>
+        <v>6.419205643360481e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.162047699725543e-10</v>
+        <v>4.162047699725546e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.397854020885392e-10</v>
+        <v>7.397854020885398e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.441711802176056e-10</v>
+        <v>7.441711802176062e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>6.714670997875894e-10</v>
+        <v>6.714670997875892e-10</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.313351177538502e-10</v>
+        <v>5.313351177538503e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.009295347934857e-10</v>
+        <v>6.009295347934853e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.232829698324297e-10</v>
+        <v>6.2328296983243e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.373481400813316e-10</v>
+        <v>6.373481400813322e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.294795892864928e-10</v>
+        <v>5.294795892864925e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.607683471457695e-10</v>
+        <v>5.607683471457692e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>7.50331412148377e-10</v>
+        <v>7.503314121483779e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.913421901671218e-10</v>
+        <v>4.913421901671222e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.239175279068596e-10</v>
+        <v>8.239175279068606e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.237900544663306e-10</v>
+        <v>8.237900544663304e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>7.849711577721077e-10</v>
+        <v>7.849711577721075e-10</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.23284402150578e-09</v>
+        <v>4.577637651878236e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.198876953673069e-09</v>
+        <v>4.347856337620459e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.280365115362115e-09</v>
+        <v>5.052848590441588e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.204554112903006e-09</v>
+        <v>4.357848514527102e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.204554112903007e-09</v>
+        <v>4.357848514527099e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.24770465216736e-09</v>
+        <v>4.729138214004868e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.346349168319608e-09</v>
+        <v>5.712689120016522e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.211161513266719e-09</v>
+        <v>4.369397139491413e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.247680822565295e-09</v>
+        <v>4.726005662473381e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.229819243894909e-09</v>
+        <v>4.547389875769523e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.363930472803428e-09</v>
+        <v>5.888502164854713e-10</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.890130224480007e-09</v>
+        <v>1.805446129608731e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>6.628247812811582e-09</v>
+        <v>1.39035489979257e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.328830371298632e-08</v>
+        <v>2.618682040774357e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.628247858529549e-09</v>
+        <v>1.390354945510541e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.628247858529548e-09</v>
+        <v>1.390354945510541e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.053786850900438e-08</v>
+        <v>2.107982651343984e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.106076150018403e-08</v>
+        <v>4.041005463608673e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>6.628238101294997e-09</v>
+        <v>1.390345188275991e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.095963033087338e-08</v>
+        <v>2.181903670447525e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>8.649639675689521e-09</v>
+        <v>1.760627376496713e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.513592325761517e-08</v>
+        <v>4.772720923941607e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.803494194383444e-09</v>
+        <v>5.58198195070077e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.772861782242064e-09</v>
+        <v>5.358069630427928e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.859355934856656e-09</v>
+        <v>6.07187242723028e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.752247150875006e-09</v>
+        <v>5.321788256134609e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.781501689544282e-09</v>
+        <v>5.373276243913533e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>3.77131119165729e-09</v>
+        <v>9.170685699440167e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.859224870360314e-09</v>
+        <v>1.01353503316435e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.781811686144382e-09</v>
+        <v>8.810944624926707e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>3.762143571348787e-09</v>
+        <v>9.15146007635253e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.798539679815994e-09</v>
+        <v>5.548337837566883e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.939781681090579e-09</v>
+        <v>6.902000285948351e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.855803425570316e-09</v>
+        <v>1.271404615894384e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.834130628847841e-09</v>
+        <v>1.250590276172281e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.903142532645382e-09</v>
+        <v>1.318893680077388e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.833990400757934e-09</v>
+        <v>1.250565633700203e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.833990400757933e-09</v>
+        <v>1.250565633700203e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.870664056231901e-09</v>
+        <v>1.286554672107048e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.969308572384154e-09</v>
+        <v>1.384909762708212e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.83412091733126e-09</v>
+        <v>1.250580564655702e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.870640226629837e-09</v>
+        <v>1.286241416953898e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.852778647959454e-09</v>
+        <v>1.268379838283513e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.986889876867968e-09</v>
+        <v>1.402491067192032e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.575524586725199e-09</v>
+        <v>1.222075540524941e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.680922664854525e-09</v>
+        <v>1.75162567179541e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.397679608159418e-09</v>
+        <v>1.933932202035211e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>7.825767857803306e-09</v>
+        <v>1.601118464240683e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.652977577777385e-09</v>
+        <v>1.218707377028254e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.716747549097037e-09</v>
+        <v>1.787465364137078e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.815392065249187e-09</v>
+        <v>1.885820454738223e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.680204410196389e-09</v>
+        <v>1.751491256685732e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.717338139698156e-09</v>
+        <v>1.787260246939103e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.514426023692334e-09</v>
+        <v>1.208829776735181e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2098720247761e-08</v>
+        <v>2.478173206640514e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.451947272819527e-09</v>
+        <v>1.024325934349066e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>5.48030258950086e-09</v>
+        <v>1.18831654158465e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.549497682674855e-09</v>
+        <v>1.25665218681984e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>6.692012770176548e-09</v>
+        <v>1.401577569899605e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.480301730547658e-09</v>
+        <v>1.188316428080499e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>5.516836016884912e-09</v>
+        <v>1.224280937519417e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.615480533037169e-09</v>
+        <v>1.32263602812058e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>5.480292877984274e-09</v>
+        <v>1.18830683006807e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.516812187282851e-09</v>
+        <v>1.223967682366267e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.865877505910271e-09</v>
+        <v>1.099029480665595e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>5.633061837520982e-09</v>
+        <v>1.3402173326044e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.125812402835445e-10</v>
+        <v>4.12581240283544e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.17128052511151e-10</v>
+        <v>5.171280525111502e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.973948945895398e-10</v>
+        <v>4.973948945895414e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.509358257162299e-10</v>
+        <v>5.509358257162292e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.473891241766593e-10</v>
+        <v>4.473891241766595e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.478826354581444e-10</v>
+        <v>4.478826354581442e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.482556035498232e-10</v>
+        <v>4.482556035498235e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.10626202976994e-10</v>
+        <v>4.106262029769939e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.278526458622087e-10</v>
+        <v>7.278526458622082e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.075736361755959e-10</v>
+        <v>7.075736361755958e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.777930288747424e-10</v>
+        <v>5.77793028874742e-10</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.852925319112179e-10</v>
+        <v>4.852925319112176e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.883466827597736e-10</v>
+        <v>5.883466827597728e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.828458034586729e-10</v>
+        <v>5.828458034586744e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.233604340734253e-10</v>
+        <v>6.233604340734245e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.198137325338564e-10</v>
+        <v>5.198137325338558e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.258964490239883e-10</v>
+        <v>5.258964490239887e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.256148204695881e-10</v>
+        <v>5.25614820469588e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.831765918913986e-10</v>
+        <v>4.831765918913982e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.098355319480017e-10</v>
+        <v>8.098355319480014e-10</v>
       </c>
       <c r="K3" t="n">
         <v>7.804711326038433e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.753211759385696e-10</v>
+        <v>6.753211759385699e-10</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.162206169459154e-09</v>
+        <v>4.271487386801892e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.150576684425129e-09</v>
+        <v>4.241670281305923e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.212624293084675e-09</v>
+        <v>4.775668623057117e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.155712929878699e-09</v>
+        <v>4.250710399260322e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.155712929878699e-09</v>
+        <v>4.250710399260323e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.182879849092156e-09</v>
+        <v>4.480790975693557e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.183433461162837e-09</v>
+        <v>4.483760303838724e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.160273521343906e-09</v>
+        <v>4.258682871569491e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.198899296633644e-09</v>
+        <v>4.638418658546784e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.162943090865585e-09</v>
+        <v>4.278856600866221e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.260430958292469e-09</v>
+        <v>5.253735275135057e-10</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.518359876829451e-09</v>
+        <v>1.369831786069333e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>6.088092322766174e-09</v>
+        <v>1.293169775769833e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.065249962901885e-08</v>
+        <v>2.138984912427588e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.088092362329888e-09</v>
+        <v>1.293169815333557e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.088092362329887e-09</v>
+        <v>1.293169815333557e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>8.40884072946754e-09</v>
+        <v>1.719848205624215e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>9.012997616401114e-09</v>
+        <v>1.826379314238954e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>6.088085788467506e-09</v>
+        <v>1.293163241471174e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.035228422813578e-08</v>
+        <v>2.074837605069708e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>6.506920906722404e-09</v>
+        <v>1.368425750581005e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.747020613148207e-08</v>
+        <v>1.737968435087287e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.694084234404885e-09</v>
+        <v>8.390256423356989e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.685958020143815e-09</v>
+        <v>5.183941427065008e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.750950346494356e-09</v>
+        <v>5.723122471924039e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.666702273272852e-09</v>
+        <v>5.150051638760872e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.692113972111555e-09</v>
+        <v>5.194776228474632e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>3.523089541633676e-09</v>
+        <v>5.416896364925654e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>3.510522242987225e-09</v>
+        <v>8.579436537656807e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>3.500483213885428e-09</v>
+        <v>8.377451908124574e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>3.530332151543895e-09</v>
+        <v>5.668615907476419e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.691981744445356e-09</v>
+        <v>5.209964626121306e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.795470118713255e-09</v>
+        <v>6.1954041923731e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.430456110325558e-09</v>
+        <v>1.178360724202157e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.428529996508965e-09</v>
+        <v>1.177086806977574e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.480705107537804e-09</v>
+        <v>1.228749081579107e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.428639424638069e-09</v>
+        <v>1.177106098928703e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.428639424638069e-09</v>
+        <v>1.177106098928703e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.451129789958564e-09</v>
+        <v>1.199291083091324e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.451683402029238e-09</v>
+        <v>1.199588015905841e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.42852346221031e-09</v>
+        <v>1.177080272678917e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.467149237500052e-09</v>
+        <v>1.215053851376646e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.431193031731993e-09</v>
+        <v>1.179097645608591e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.528680899158878e-09</v>
+        <v>1.276585513035473e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.115676871154307e-09</v>
+        <v>1.122959578408213e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>7.964069921349854e-09</v>
+        <v>1.623341831332293e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>8.606387857857154e-09</v>
+        <v>1.778869242654425e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>7.184635703961234e-09</v>
+        <v>1.486161442414931e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.204239869141113e-09</v>
+        <v>1.13761177737524e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>7.985792966540828e-09</v>
+        <v>1.645391799752557e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>7.986346578611335e-09</v>
+        <v>1.645688732567047e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>7.963186638792583e-09</v>
+        <v>1.623180989340152e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.002372411527042e-09</v>
+        <v>1.661253127587616e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>5.063483936753777e-09</v>
+        <v>1.114380845243099e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.103982494582914e-08</v>
+        <v>2.2465468599936e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.972548428742296e-09</v>
+        <v>9.217689736338696e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>4.894713074822129e-09</v>
+        <v>1.083135029269777e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>4.947058526016267e-09</v>
+        <v>1.134827283740239e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>5.961094524328802e-09</v>
+        <v>1.27081819596648e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>4.894712450149889e-09</v>
+        <v>1.083134951927974e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.917312868271738e-09</v>
+        <v>1.105339305383526e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>4.917866480342394e-09</v>
+        <v>1.105636238198044e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.894706540523475e-09</v>
+        <v>1.08312849497112e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>4.933332315813217e-09</v>
+        <v>1.121102073668851e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.361954805076198e-09</v>
+        <v>8.803530555711634e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>4.994863977472042e-09</v>
+        <v>1.182633735327676e-09</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia human toxicity carcinogenic results.xlsx
+++ b/Results/Ammonia/ammonia human toxicity carcinogenic results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.284367204559038e-10</v>
+        <v>5.458331570201232e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.926114744142163e-10</v>
+        <v>6.500517131178855e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.585943347064861e-10</v>
+        <v>5.474202923602853e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.343447495192536e-10</v>
+        <v>6.864379671662867e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.066447845926805e-10</v>
+        <v>5.801619304409469e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.121567712966022e-10</v>
+        <v>5.449763756304533e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.860394716706393e-10</v>
+        <v>5.526548885404812e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.598643708679132e-10</v>
+        <v>5.422266824126871e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>8.393878823567995e-10</v>
+        <v>8.068605038159237e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>8.022166380551693e-10</v>
+        <v>8.078412891299867e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>7.429603391250164e-10</v>
+        <v>5.571483221741775e-10</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.253917226741898e-10</v>
+        <v>5.015801141282879e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.78029557990091e-10</v>
+        <v>6.556599065993364e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.600792261933239e-10</v>
+        <v>5.129518675344799e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>7.210064073653387e-10</v>
+        <v>7.145321654875356e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.933064424387659e-10</v>
+        <v>5.390927137599746e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.066664087596759e-10</v>
+        <v>4.956196857060929e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>8.061261093720312e-10</v>
+        <v>5.600262093597187e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.464686932860122e-10</v>
+        <v>4.758449901555856e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.359188724956165e-10</v>
+        <v>9.318932021821864e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.925984597615586e-10</v>
+        <v>9.215521948879172e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.721349234643191e-10</v>
+        <v>5.832757602236174e-10</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.238148682585777e-10</v>
+        <v>5.238148682585903e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.805965590888624e-10</v>
+        <v>4.805965590888617e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.417422920440475e-10</v>
+        <v>5.417422920440489e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.817280652896407e-10</v>
+        <v>4.81728065289641e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.817280652896415e-10</v>
+        <v>4.81728065289641e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.140897547850366e-10</v>
+        <v>5.140897547850402e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>6.174840269164101e-10</v>
+        <v>6.174840269164069e-10</v>
       </c>
       <c r="I4" t="n">
         <v>4.829819866862337e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.221368042292651e-10</v>
+        <v>5.22136804229265e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.978009448117732e-10</v>
+        <v>4.978009448117728e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>6.513328288842883e-10</v>
+        <v>6.513328288842879e-10</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.623241424265882e-09</v>
+        <v>2.623241424266033e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.805456489068287e-09</v>
+        <v>1.805456489068291e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>3.010584547568573e-09</v>
+        <v>3.010584547568585e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.805456537895793e-09</v>
+        <v>1.805456537895784e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.805456537895793e-09</v>
+        <v>1.805456537895784e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.520110264442818e-09</v>
+        <v>2.520110264442807e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.944619915619199e-09</v>
+        <v>4.944619915619117e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.805447838187824e-09</v>
+        <v>1.805447838187818e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.740844929726664e-09</v>
+        <v>2.740844929726696e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1677439642838e-09</v>
+        <v>2.167743964283841e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.382028058665222e-09</v>
+        <v>5.843428216767569e-09</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.250762265323134e-10</v>
+        <v>6.250762265323212e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.826857600082564e-10</v>
+        <v>5.82685760008254e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>6.442576720652636e-10</v>
+        <v>6.442574047926907e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.786392654081804e-10</v>
+        <v>5.786392654081811e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.842620336795681e-10</v>
+        <v>5.842620336795677e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.933266319395286e-10</v>
+        <v>9.933266319395284e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09392366511547e-09</v>
+        <v>1.093923665115467e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>5.842433449599645e-10</v>
+        <v>9.622188638407242e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>6.346723982315479e-10</v>
+        <v>9.987606572510656e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.987414339717543e-10</v>
+        <v>5.987414339717548e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>7.537489603004613e-10</v>
+        <v>7.537489603004618e-10</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.433317373804779e-09</v>
+        <v>1.433317373804776e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.392493143112888e-09</v>
+        <v>1.392493143112889e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.451210076829721e-09</v>
+        <v>1.451210076829724e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.392443537495806e-09</v>
+        <v>1.392443537495807e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.392443537495806e-09</v>
+        <v>1.392443537495808e-09</v>
       </c>
       <c r="G7" t="n">
         <v>1.423592260331227e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.526986532462596e-09</v>
+        <v>1.526986532462593e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.392484492232418e-09</v>
+        <v>1.392484492232421e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.431639309775453e-09</v>
+        <v>1.431639309775451e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.407303450357958e-09</v>
+        <v>1.40730345035796e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.560835334430474e-09</v>
+        <v>1.560835334430475e-09</v>
       </c>
     </row>
     <row r="8">
@@ -758,34 +758,34 @@
         <v>1.41170935224068e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0121740571133e-09</v>
+        <v>2.012174057114199e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>2.203753788877379e-09</v>
+        <v>2.203753788877377e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.836798711641034e-09</v>
+        <v>1.836798711641032e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.391200261814394e-09</v>
+        <v>1.391200261814392e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>2.043151121635338e-09</v>
+        <v>2.043151121635336e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>2.146545393766707e-09</v>
+        <v>2.146545393766702e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>2.012043353536529e-09</v>
+        <v>2.012043353536532e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>2.051324178835832e-09</v>
+        <v>2.05132417883583e-09</v>
       </c>
       <c r="K8" t="n">
         <v>1.373785424761607e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.850146618478161e-09</v>
+        <v>2.850146618478154e-09</v>
       </c>
     </row>
     <row r="9">
@@ -795,34 +795,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.204302387809534e-09</v>
+        <v>1.204302387809527e-09</v>
       </c>
       <c r="C9" t="n">
         <v>1.38518864225655e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.44394052921849e-09</v>
+        <v>1.443940529218488e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.641037867398152e-09</v>
+        <v>1.641037867398149e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.385188504943418e-09</v>
+        <v>1.38518850494342e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.416287759474884e-09</v>
+        <v>1.416287759474886e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.519682031606256e-09</v>
+        <v>1.519682031606253e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.385179991376081e-09</v>
+        <v>1.385179991376079e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.424334808919111e-09</v>
+        <v>1.42433480891911e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.271539121470013e-09</v>
+        <v>1.120825813275108e-09</v>
       </c>
       <c r="L9" t="n">
         <v>1.553530833574134e-09</v>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.093295746377199e-10</v>
+        <v>5.09547564390489e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.261816913297872e-10</v>
+        <v>5.950518875789506e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.229314033691703e-10</v>
+        <v>5.102634016212172e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.593089295989362e-10</v>
+        <v>6.240783036714361e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.578991886892052e-10</v>
+        <v>5.396856036039103e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.224466923333715e-10</v>
+        <v>5.102378922421174e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.222163489967646e-10</v>
+        <v>5.087069772761523e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.212324366522055e-10</v>
+        <v>5.101768301253612e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.915723809390419e-10</v>
+        <v>7.239662578104578e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.088829107843277e-10</v>
+        <v>7.532560271631229e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.399743566215779e-10</v>
+        <v>5.110318704585669e-10</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.805322291423071e-10</v>
+        <v>4.398023516595449e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.979862977476112e-10</v>
+        <v>5.859538487426847e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9617714979381e-10</v>
+        <v>4.44886144610728e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.323075897920957e-10</v>
+        <v>6.328201328034477e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.30897848882364e-10</v>
+        <v>4.935030324055037e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.956196316950514e-10</v>
+        <v>4.447438184603756e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.946356195757136e-10</v>
+        <v>4.433478045429574e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.944575057191495e-10</v>
+        <v>4.441644713297196e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.827608572919956e-10</v>
+        <v>8.322570529434547e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.811702258441497e-10</v>
+        <v>8.441205234601276e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.157862565132433e-10</v>
+        <v>4.515339297240079e-10</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.252029257873916e-10</v>
+        <v>4.252029257873929e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.309355339678307e-10</v>
+        <v>4.309355339678325e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.332886366098647e-10</v>
+        <v>4.332886366098655e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.318124985401497e-10</v>
+        <v>4.318124985401524e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.318124985401517e-10</v>
+        <v>4.318124985401511e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.329577941776593e-10</v>
+        <v>4.329577941776617e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.328839630230569e-10</v>
+        <v>4.32883963023059e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.322469382619546e-10</v>
+        <v>4.322469382619562e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.042985232147126e-10</v>
+        <v>5.042985232147136e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.294955626012759e-10</v>
+        <v>4.294955626012763e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.434581944011897e-10</v>
+        <v>4.434581944011913e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.351612071045329e-09</v>
+        <v>1.35161207104533e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.41042257296662e-09</v>
+        <v>1.410422572966626e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.481575913477449e-09</v>
+        <v>1.48157591347745e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.410422606180481e-09</v>
+        <v>1.410422606180489e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.410422606180481e-09</v>
+        <v>1.410422606180489e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.497028924581889e-09</v>
+        <v>1.497028924581886e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.597730958084374e-09</v>
+        <v>1.597730958084376e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.410420958339424e-09</v>
+        <v>1.410420958339444e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.802126694995776e-09</v>
+        <v>2.802126694995782e-09</v>
       </c>
       <c r="K5" t="n">
         <v>1.400453608743029e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.844888546091611e-09</v>
+        <v>1.844888546091614e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1071,34 +1071,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.349746539597908e-10</v>
+        <v>5.192313377582666e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.257898850654919e-10</v>
+        <v>5.257898850654905e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.431330430785954e-10</v>
+        <v>8.431330430785955e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.223466210435261e-10</v>
+        <v>5.223466210435263e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.263931409590932e-10</v>
+        <v>5.263931409590943e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.269862061485351e-10</v>
+        <v>8.427295223500594e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.40828928137823e-10</v>
+        <v>8.408289281378227e-10</v>
       </c>
       <c r="I6" t="n">
         <v>5.26275350232831e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.129798673389989e-10</v>
+        <v>6.079665369064059e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.234141160714944e-10</v>
+        <v>5.234141160714967e-10</v>
       </c>
       <c r="L6" t="n">
         <v>5.376141243288915e-10</v>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.172776581833368e-09</v>
+        <v>1.172776581833373e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.179822208935117e-09</v>
+        <v>1.17982220893512e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.180832575544877e-09</v>
+        <v>1.18083257554488e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.179888636114031e-09</v>
+        <v>1.179888636114034e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.179888636114031e-09</v>
+        <v>1.179888636114034e-09</v>
       </c>
       <c r="G7" t="n">
         <v>1.180531450223643e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.180457619069037e-09</v>
+        <v>1.18045761906904e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.179820594307935e-09</v>
+        <v>1.17982059430794e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.251872179260691e-09</v>
+        <v>1.251872179260696e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.177069218647257e-09</v>
+        <v>1.17706921864726e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.191031850447171e-09</v>
+        <v>1.191031850447172e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1151,34 +1151,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.111844610621282e-09</v>
+        <v>1.111844610621289e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.61429246451219e-09</v>
+        <v>1.614292464512998e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.717818256982112e-09</v>
+        <v>1.717818256982115e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.478829800778161e-09</v>
+        <v>1.478829800778165e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.134644812182752e-09</v>
+        <v>1.134644812182756e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.614803611681492e-09</v>
+        <v>1.614803611681496e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.614729780526866e-09</v>
+        <v>1.614729780526871e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.614092755765789e-09</v>
+        <v>1.614092755765792e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.686241662581377e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.106938576427894e-09</v>
+        <v>1.106938576427895e-09</v>
       </c>
       <c r="L8" t="n">
         <v>2.142586136831176e-09</v>
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.960557357168953e-10</v>
+        <v>8.96055735716897e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.058963005625052e-09</v>
+        <v>1.058963005625054e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.060003298012354e-09</v>
+        <v>1.060003298012356e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.238824121713691e-09</v>
+        <v>1.238824121713699e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.058962929436191e-09</v>
+        <v>1.058962929436195e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.059672246913576e-09</v>
+        <v>1.059672246913577e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.059598415758969e-09</v>
+        <v>1.059598415758973e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.058961390997867e-09</v>
+        <v>1.058961390997873e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.131012975950628e-09</v>
+        <v>1.131012975950629e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.659032551436137e-10</v>
+        <v>9.659032551436214e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.070172647137103e-09</v>
+        <v>1.070172647137106e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.389720014398946e-10</v>
+        <v>6.204180772961409e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.847853717982487e-10</v>
+        <v>5.498592208993744e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>6.099653077409803e-10</v>
+        <v>6.241543140027056e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.072998656582287e-10</v>
+        <v>5.814061388188546e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.072998656582287e-10</v>
+        <v>5.814236389791244e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.705577624802077e-10</v>
+        <v>6.220803731653219e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.560051192752225e-10</v>
+        <v>6.250677100601028e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.538804734189542e-10</v>
+        <v>6.212054422520144e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.330358028097919e-10</v>
+        <v>6.62178897889242e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.480313367858875e-10</v>
+        <v>7.788455878773268e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.858783951742054e-10</v>
+        <v>6.227613786588885e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.190931558517398e-10</v>
+        <v>6.129096948274196e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.700895820338258e-10</v>
+        <v>5.072504567782309e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>7.007501643170863e-10</v>
+        <v>6.401594484293977e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.896682613568047e-10</v>
+        <v>5.541206513651835e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.896682613568047e-10</v>
+        <v>5.541381515254593e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.554233240187899e-10</v>
+        <v>6.25441889867409e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>7.531265859306751e-10</v>
+        <v>6.564103249802173e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.361989209030844e-10</v>
+        <v>6.191768395431703e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>7.201949575266693e-10</v>
+        <v>6.961070277048404e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.311551448833006e-10</v>
+        <v>8.80827873746869e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.730526774404072e-10</v>
+        <v>6.314189889666906e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.535477419274288e-10</v>
+        <v>4.535477419274294e-10</v>
       </c>
       <c r="C4" t="n">
         <v>4.661771984239933e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.957502542818563e-10</v>
+        <v>4.95750254281857e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.612784783360238e-10</v>
+        <v>4.612784783360241e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.612784783360236e-10</v>
+        <v>4.612784783360242e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.722817010914561e-10</v>
+        <v>4.722817010914572e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.23120580955105e-10</v>
+        <v>5.23120580955106e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.62382930113282e-10</v>
+        <v>4.623829301132816e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.814012294168926e-10</v>
+        <v>4.814012294168938e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.654310004158358e-10</v>
+        <v>4.654310004158356e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.814723868425648e-10</v>
+        <v>4.814723868425653e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.105810409225161e-09</v>
+        <v>1.105810409225165e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.729076810238209e-09</v>
+        <v>1.729076810238208e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.211051722894207e-09</v>
+        <v>2.211051722894197e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.625694348294713e-09</v>
+        <v>1.625694348294698e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.625694348294713e-09</v>
+        <v>1.625694348294698e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.820980526876716e-09</v>
+        <v>1.820980526876724e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.975919059273844e-09</v>
+        <v>2.975919059273831e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.625690572782488e-09</v>
+        <v>1.62569057278246e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.026292696290823e-09</v>
+        <v>2.026292696290814e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.67321067388748e-09</v>
+        <v>1.673210673887477e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.169518909931743e-09</v>
+        <v>2.169518909931739e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.440892584241356e-10</v>
+        <v>8.840413007591853e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.60502815755355e-10</v>
+        <v>5.605028157553546e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.873178983146246e-10</v>
+        <v>5.873177474085708e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.485839777808321e-10</v>
+        <v>5.485839777808308e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.530028487174208e-10</v>
+        <v>5.530028487174204e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.027752599232143e-10</v>
+        <v>5.62823217588163e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.619019681697701e-10</v>
+        <v>9.619019681697711e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.928764889450397e-10</v>
+        <v>5.52924446609987e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.171380345648484e-10</v>
+        <v>9.171380345648493e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.560469706525133e-10</v>
+        <v>5.560469706525135e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.72213204692575e-10</v>
+        <v>5.722132046925754e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.291362316828938e-09</v>
+        <v>1.291362316828939e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.308347633846975e-09</v>
+        <v>1.308347633846976e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.333533630215636e-09</v>
+        <v>1.333533630215638e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.30019532009839e-09</v>
+        <v>1.300195320098389e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.30019532009839e-09</v>
+        <v>1.300195320098389e-09</v>
       </c>
       <c r="G7" t="n">
         <v>1.310096275992966e-09</v>
@@ -1528,10 +1528,10 @@
         <v>1.360935155856616e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.300197505014791e-09</v>
+        <v>1.300197505014793e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.319215804318403e-09</v>
+        <v>1.319215804318402e-09</v>
       </c>
       <c r="K7" t="n">
         <v>1.303245575317344e-09</v>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.270576458720251e-09</v>
+        <v>1.270576458720255e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.878607032147319e-09</v>
+        <v>1.878607032147321e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>2.026200744328733e-09</v>
+        <v>2.026200744328735e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.708831991623039e-09</v>
@@ -1562,7 +1562,7 @@
         <v>1.298160959682151e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.88020611831881e-09</v>
+        <v>1.880206118318814e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.931044998182725e-09</v>
@@ -1571,13 +1571,13 @@
         <v>1.870307347340637e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.889441774664161e-09</v>
+        <v>1.88944177466416e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.271483526199601e-09</v>
+        <v>1.271483526199605e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.506636773147629e-09</v>
+        <v>2.506636773147634e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1587,34 +1587,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.036055373240628e-09</v>
+        <v>1.036055373240627e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.245371924891821e-09</v>
+        <v>1.245371924891822e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.270589344408558e-09</v>
+        <v>1.270589344408561e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.459171756807758e-09</v>
+        <v>1.459171756807761e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.237225424288482e-09</v>
+        <v>1.237225424288481e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.247120567037813e-09</v>
+        <v>1.247120567037812e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.297959446901462e-09</v>
+        <v>1.297959446901461e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.23722179605964e-09</v>
+        <v>1.237221796059641e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.25624009536325e-09</v>
+        <v>1.256240095363251e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.128832487962099e-09</v>
+        <v>1.128832487962097e-09</v>
       </c>
       <c r="L9" t="n">
         <v>1.256311252788922e-09</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.149780496693276e-10</v>
+        <v>6.115668995172483e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.709510100817741e-10</v>
+        <v>5.491601878476645e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.781979249684824e-10</v>
+        <v>6.148940359894594e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.03854921875075e-10</v>
+        <v>5.816687158526213e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.03854921875075e-10</v>
+        <v>5.816862165485119e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.435847998395189e-10</v>
+        <v>6.130724159611236e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.901065836191968e-10</v>
+        <v>6.139936150196035e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.401314435714195e-10</v>
+        <v>6.128935959580455e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.060949385964315e-10</v>
+        <v>6.614375733860238e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.277174827548928e-10</v>
+        <v>7.7769207118308e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.377140985452326e-10</v>
+        <v>6.126253129363988e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.934123119650292e-10</v>
+        <v>5.944375622187458e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.546313565101145e-10</v>
+        <v>5.023450056974386e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.661282645167725e-10</v>
+        <v>6.187824881721705e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.860757471800709e-10</v>
+        <v>5.536511394881681e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.860757471800708e-10</v>
+        <v>5.536686401840591e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.263160005311945e-10</v>
+        <v>6.058521007673716e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.792413510120681e-10</v>
+        <v>6.220884565241726e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.223016713682924e-10</v>
+        <v>6.045537844251605e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.895324189762059e-10</v>
+        <v>6.871020939395449e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.082616296923162e-10</v>
+        <v>8.733578986141928e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.195718812233602e-10</v>
+        <v>6.037735870548589e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.414013407440042e-10</v>
+        <v>4.414013407440048e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.543111378998156e-10</v>
+        <v>4.543111378998172e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.789828777559915e-10</v>
+        <v>4.789828777559953e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.556924029226429e-10</v>
+        <v>4.55692402922644e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.556924029226431e-10</v>
+        <v>4.556924029226442e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.583694872237288e-10</v>
+        <v>4.583694872237296e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.860727451892722e-10</v>
+        <v>4.860727451892687e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.563630113282891e-10</v>
+        <v>4.563630113282907e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.612020037550733e-10</v>
+        <v>4.612020037550788e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.497513894688357e-10</v>
+        <v>4.497513894688379e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.549620758246489e-10</v>
+        <v>4.549620758246483e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.119157682288361e-10</v>
+        <v>9.119157682288389e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.508108011365694e-09</v>
+        <v>1.508108011365713e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.887017154967034e-09</v>
+        <v>1.88701715496704e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.51250234591324e-09</v>
+        <v>1.512502345913245e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.51250234591324e-09</v>
+        <v>1.512502345913245e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.559648184930075e-09</v>
+        <v>1.559648184930269e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.196031681376191e-09</v>
+        <v>2.196031681376194e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.512500377301201e-09</v>
+        <v>1.512500377301206e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.638555838651009e-09</v>
+        <v>1.638555838651008e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.393642455337005e-09</v>
+        <v>1.393642455337007e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.623236524137241e-09</v>
+        <v>1.623236524137239e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.485136045094786e-10</v>
+        <v>8.48513604509483e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.420203089688721e-10</v>
+        <v>5.420203089688712e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.92483802805671e-10</v>
+        <v>8.924838028056787e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.364190729370633e-10</v>
+        <v>5.364190729370638e-10</v>
       </c>
       <c r="F6" t="n">
         <v>5.404574243706612e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.423190861132188e-10</v>
+        <v>8.654817509892058e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.023986922089395e-10</v>
+        <v>9.023986922089474e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.403126102177764e-10</v>
+        <v>5.403126102177782e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.54801459299415e-10</v>
+        <v>5.548014592994195e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.336725847688724e-10</v>
+        <v>5.336725847688678e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.390060303202956e-10</v>
+        <v>5.390060303203027e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1906,34 +1906,34 @@
         <v>1.238594283690473e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.255822791375642e-09</v>
+        <v>1.255822791375643e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.276146312813614e-09</v>
+        <v>1.276146312813617e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.253646719412885e-09</v>
+        <v>1.253646719412887e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.253646719412885e-09</v>
+        <v>1.253646719412887e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2555624301702e-09</v>
+        <v>1.255562430170202e-09</v>
       </c>
       <c r="H7" t="n">
         <v>1.283265688135738e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.253555954274756e-09</v>
+        <v>1.25355595427476e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.258394946701541e-09</v>
+        <v>1.258394946701546e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.246944332415303e-09</v>
+        <v>1.246944332415306e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.252155018771117e-09</v>
+        <v>1.252155018771115e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.219813974618956e-09</v>
+        <v>1.219813974618957e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.801135920815157e-09</v>
+        <v>1.801135920813847e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.938176452516083e-09</v>
+        <v>1.93817645251609e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.644627837254706e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.252721702980426e-09</v>
+        <v>1.252721702980429e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.800642863773204e-09</v>
+        <v>1.800642863773208e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.828346121739429e-09</v>
+        <v>1.82834612173944e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.798636387877765e-09</v>
+        <v>1.798636387877763e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.803586195171173e-09</v>
+        <v>1.803586195171176e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.217690020555515e-09</v>
+        <v>1.217690020555514e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.386235147437319e-09</v>
+        <v>2.386235147437322e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.68074567286712e-10</v>
+        <v>9.680745672867196e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.161105441533317e-09</v>
+        <v>1.161105441533319e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.181458687254591e-09</v>
+        <v>1.181458687254599e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.361712808797304e-09</v>
+        <v>1.361712808797311e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.158840442434191e-09</v>
+        <v>1.158840442434193e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.160845080327873e-09</v>
+        <v>1.160845080327877e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.188548338293409e-09</v>
+        <v>1.188548338293415e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.15883860443243e-09</v>
+        <v>1.158838604432436e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.163677596859214e-09</v>
+        <v>1.163677596859223e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.050366491972802e-09</v>
+        <v>1.050366491972805e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.157437668928786e-09</v>
+        <v>1.157437668928796e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.974366259749458e-10</v>
+        <v>6.008511086807007e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.565256858822791e-10</v>
+        <v>5.454427840045617e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.495405483278585e-10</v>
+        <v>6.035932346274077e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.985323463629766e-10</v>
+        <v>5.782194539715901e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.985323463629766e-10</v>
+        <v>5.782369767789485e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.216852280647206e-10</v>
+        <v>6.021272644470812e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.474766232174875e-10</v>
+        <v>6.019486773483912e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.263127499644259e-10</v>
+        <v>6.023738205095123e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.756647463532831e-10</v>
+        <v>6.560553154326765e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.154524199379255e-10</v>
+        <v>7.733009986060295e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.217841145179636e-10</v>
+        <v>6.020002990862704e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.744530268564075e-10</v>
+        <v>5.772807073075256e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.379622790930611e-10</v>
+        <v>4.951101157872614e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.343833308572575e-10</v>
+        <v>5.974629150700279e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.798947634901241e-10</v>
+        <v>5.495646049889905e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.798947634901243e-10</v>
+        <v>5.495821277963483e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.023439423424406e-10</v>
+        <v>5.870593663864304e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.314385676547804e-10</v>
+        <v>5.954474904613101e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.076249773090653e-10</v>
+        <v>5.88796147471276e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.545902759776635e-10</v>
+        <v>6.727949159506479e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.942063693952515e-10</v>
+        <v>8.659304201064997e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.024656645802919e-10</v>
+        <v>5.872149380788399e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.364471474550997e-10</v>
+        <v>4.364471474550996e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.456884567851688e-10</v>
+        <v>4.456884567851681e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.674207214634314e-10</v>
+        <v>4.674207214634309e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.531770160268974e-10</v>
+        <v>4.531770160268973e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.531770160268974e-10</v>
+        <v>4.531770160268976e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.50826562454879e-10</v>
+        <v>4.508265624548812e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.662092733502734e-10</v>
+        <v>4.662092733502733e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.536369671219549e-10</v>
+        <v>4.536369671219551e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.440026875590854e-10</v>
+        <v>4.44002687559085e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.433236443892259e-10</v>
+        <v>4.433236443892264e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.509640699401647e-10</v>
+        <v>4.50964069940165e-10</v>
       </c>
     </row>
     <row r="5">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.420208495764615e-10</v>
+        <v>8.420208495764624e-10</v>
       </c>
       <c r="C5" t="n">
         <v>1.380183923786099e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.706743428480341e-09</v>
+        <v>1.706743428480337e-09</v>
       </c>
       <c r="E5" t="n">
         <v>1.481907796626238e-09</v>
@@ -2234,22 +2234,22 @@
         <v>1.481907796626238e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.44449308331879e-09</v>
+        <v>1.444493083318833e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.834221945665701e-09</v>
+        <v>1.834221945665706e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.481906922981955e-09</v>
+        <v>1.481906922981956e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.348632339140751e-09</v>
+        <v>1.34863233914075e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.300274531487607e-09</v>
+        <v>1.300274531487604e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.563989661303458e-09</v>
+        <v>1.563989661303459e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.20784560409406e-10</v>
+        <v>5.207845604094052e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.339773297454535e-10</v>
+        <v>5.339773297454537e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.524304924903684e-10</v>
+        <v>5.524306213115155e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.341997555849353e-10</v>
+        <v>5.341997555849339e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.381537795060459e-10</v>
+        <v>5.381537795060464e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.57897329818538e-10</v>
+        <v>8.578973298185413e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.83606875105407e-10</v>
+        <v>8.836068751054072e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.607077344856127e-10</v>
+        <v>8.607077344856136e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.5649252324018e-10</v>
+        <v>8.564925232401787e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.276231721850386e-10</v>
+        <v>5.276231721850276e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.353868083682516e-10</v>
+        <v>5.353868083682506e-10</v>
       </c>
     </row>
     <row r="7">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.230914667984315e-09</v>
+        <v>1.230914667984316e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.244790937552114e-09</v>
+        <v>1.244790937552115e-09</v>
       </c>
       <c r="D7" t="n">
         <v>1.261858798140739e-09</v>
@@ -2314,10 +2314,10 @@
         <v>1.248252083666356e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.245294082984095e-09</v>
+        <v>1.245294082984096e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.26067679387949e-09</v>
+        <v>1.260676793879491e-09</v>
       </c>
       <c r="I7" t="n">
         <v>1.24810448765117e-09</v>
@@ -2326,10 +2326,10 @@
         <v>1.238470208088302e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.237791164918442e-09</v>
+        <v>1.237791164918441e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.245431590469383e-09</v>
+        <v>1.245431590469382e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2339,34 +2339,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.211135351417904e-09</v>
+        <v>1.211135351417905e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.786423672756598e-09</v>
+        <v>1.786423672758235e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.919586330593363e-09</v>
+        <v>1.919586330593364e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.636237391690956e-09</v>
+        <v>1.636237391690953e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.246217918830887e-09</v>
+        <v>1.246217918830888e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.786639336571634e-09</v>
+        <v>1.786639336571635e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.802022047468024e-09</v>
+        <v>1.802022047468025e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.789449741238709e-09</v>
+        <v>1.789449741238711e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.779925738798961e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.207588671373344e-09</v>
+        <v>1.207588671373343e-09</v>
       </c>
       <c r="L8" t="n">
         <v>2.372918378121905e-09</v>
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.41484521167484e-10</v>
+        <v>9.414845211674846e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.125018731431801e-09</v>
+        <v>1.125018731431803e-09</v>
       </c>
       <c r="D9" t="n">
         <v>1.142116254368992e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.324114862105438e-09</v>
+        <v>1.32411486210544e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.128333029718746e-09</v>
+        <v>1.128333029718745e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.125521876863779e-09</v>
+        <v>1.125521876863787e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.140904587759174e-09</v>
+        <v>1.14090458775918e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.128332281530857e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.118698001967986e-09</v>
+        <v>1.11869800196799e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.04389270996277e-10</v>
+        <v>1.015730393893479e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.125659384349066e-09</v>
+        <v>1.125659384349069e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.114473776027679e-10</v>
+        <v>6.121241173181565e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.276911279237052e-10</v>
+        <v>5.4251228107693e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.694162497974773e-10</v>
+        <v>6.151749039263102e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.921976778918172e-10</v>
+        <v>5.766434547522368e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.921976778918172e-10</v>
+        <v>5.766609540412469e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.471178677330659e-10</v>
+        <v>6.140013843664139e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.208225188524982e-10</v>
+        <v>6.163693589090681e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.350869077386785e-10</v>
+        <v>6.133710404659004e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.266694658238757e-10</v>
+        <v>6.565795573484937e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.309649093384334e-10</v>
+        <v>7.736272832835032e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.848538221649001e-10</v>
+        <v>6.158817825380599e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.88037183012233e-10</v>
+        <v>5.958655877561793e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.045539070853358e-10</v>
+        <v>4.823189426104911e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.547133942518483e-10</v>
+        <v>6.182452231625049e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.723463630280176e-10</v>
+        <v>5.454293723974516e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.723463630280176e-10</v>
+        <v>5.454468716864599e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.290656357818445e-10</v>
+        <v>6.099313621598316e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>7.132698818660242e-10</v>
+        <v>6.364383922109532e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.151815486377686e-10</v>
+        <v>6.054151772583746e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>7.131708187818122e-10</v>
+        <v>6.890297921886253e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.116418052389892e-10</v>
+        <v>8.709502085982458e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.72475897945769e-10</v>
+        <v>6.243529887866165e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.387973739987862e-10</v>
+        <v>4.387973739987873e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.317199373326574e-10</v>
+        <v>4.317199373326582e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.732574121690605e-10</v>
+        <v>4.732574121690608e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.522695896514784e-10</v>
+        <v>4.522695896514788e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.522695896514784e-10</v>
+        <v>4.522695896514789e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.599606262046529e-10</v>
+        <v>4.599606262046539e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.038204747096596e-10</v>
+        <v>5.038204747096628e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.528301573070315e-10</v>
+        <v>4.528301573070304e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.78023170201884e-10</v>
+        <v>4.780231702018844e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.54972383792476e-10</v>
+        <v>4.54972383792477e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.824692386873248e-10</v>
+        <v>4.824692386873249e-10</v>
       </c>
     </row>
     <row r="5">
@@ -2615,34 +2615,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.788173400095599e-10</v>
+        <v>8.78817340009562e-10</v>
       </c>
       <c r="C5" t="n">
         <v>1.144631880418601e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.85193723711605e-09</v>
+        <v>1.851937237116049e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.496745930144903e-09</v>
+        <v>1.496745930144886e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.496745930144903e-09</v>
+        <v>1.496745930144886e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.638822525966249e-09</v>
+        <v>1.638822525966251e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.636061539200618e-09</v>
+        <v>2.636061539200603e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.496742801432283e-09</v>
+        <v>1.496742801432271e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.008403076516699e-09</v>
+        <v>2.008403076516701e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.528823505807444e-09</v>
+        <v>1.528823505807448e-09</v>
       </c>
       <c r="L5" t="n">
         <v>2.240052480976573e-09</v>
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.278516662771611e-10</v>
+        <v>5.278516662771625e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.240584880545953e-10</v>
+        <v>5.24058488054595e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.629875557206104e-10</v>
+        <v>5.629877070142358e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.378065771212734e-10</v>
+        <v>5.378065771212722e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.420302175434187e-10</v>
+        <v>5.42030217543418e-10</v>
       </c>
       <c r="G6" t="n">
         <v>5.490149184830297e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.397419023565417e-10</v>
+        <v>9.397419023565454e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.418844495854059e-10</v>
+        <v>8.808034571461676e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.111637276651505e-10</v>
+        <v>5.772514177205461e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.441405860592973e-10</v>
+        <v>5.441405860592986e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.718127659795997e-10</v>
+        <v>5.718127659796006e-10</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.274720179068407e-09</v>
+        <v>1.27472017906841e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.272222318054821e-09</v>
+        <v>1.272222318054825e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.309149083227104e-09</v>
+        <v>1.309149083227107e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.288893026722473e-09</v>
+        <v>1.288893026722475e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.288893026722473e-09</v>
+        <v>1.288893026722475e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.295883431274276e-09</v>
+        <v>1.295883431274277e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.339743279779277e-09</v>
+        <v>1.339743279779285e-09</v>
       </c>
       <c r="I7" t="n">
         <v>1.288752962376652e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.313945975271501e-09</v>
+        <v>1.313945975271505e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.290895188862096e-09</v>
+        <v>1.290895188862098e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.318392043756944e-09</v>
+        <v>1.318392043756946e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.251611746277518e-09</v>
+        <v>1.251611746277521e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.83736081737613e-09</v>
+        <v>1.837360817377297e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.995950921815163e-09</v>
+        <v>1.995950921815169e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.693054070838274e-09</v>
+        <v>1.693054070838279e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.28438539136673e-09</v>
+        <v>1.284385391366732e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.86073649030226e-09</v>
+        <v>1.860736490302263e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.9045963388075e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.853606021404639e-09</v>
+        <v>1.853606021404638e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.878914585664329e-09</v>
+        <v>1.878914585664333e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.256865069493572e-09</v>
+        <v>1.256865069493575e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.497420045609871e-09</v>
+        <v>2.497420045609873e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.013159995377582e-09</v>
+        <v>1.013159995377581e-09</v>
       </c>
       <c r="C9" t="n">
         <v>1.200629197180691e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.237587322146785e-09</v>
+        <v>1.237587322146789e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.436380960544824e-09</v>
+        <v>1.436380960544829e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.217162829166464e-09</v>
+        <v>1.21716282916646e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.224290310400138e-09</v>
+        <v>1.224290310400139e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.268150158905147e-09</v>
+        <v>1.26815015890515e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.217159841502515e-09</v>
+        <v>1.217159841502517e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.242352854397369e-09</v>
+        <v>1.24235285439737e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.800995683830694e-10</v>
+        <v>1.109234500696902e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.24679892288281e-09</v>
+        <v>1.246798922882811e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.917936198404364e-10</v>
+        <v>5.92592856591115e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.286845360995054e-10</v>
+        <v>5.356282237133096e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.198207892578709e-10</v>
+        <v>5.940678708511184e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.910378096958311e-10</v>
+        <v>5.682701058251172e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.910378096958311e-10</v>
+        <v>5.682876479647396e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.073984909329215e-10</v>
+        <v>5.934141099629444e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.139510019800104e-10</v>
+        <v>5.922166660206138e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.208606748781955e-10</v>
+        <v>5.941256696800116e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.840392949943643e-10</v>
+        <v>6.416535895598576e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.034159807378303e-10</v>
+        <v>7.620185380870658e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.255306014834524e-10</v>
+        <v>5.942514380548576e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.665634866379923e-10</v>
+        <v>5.695439845830797e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.046173067320485e-10</v>
+        <v>4.7853834694052e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.988005372786945e-10</v>
+        <v>5.80699338477981e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.701825230401235e-10</v>
+        <v>5.390895510363167e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.701825230401235e-10</v>
+        <v>5.391070931759446e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.845123209336626e-10</v>
+        <v>5.760758215798537e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.91450024914172e-10</v>
+        <v>5.771860082648062e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.999250158767314e-10</v>
+        <v>5.811290506466914e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.641494000781055e-10</v>
+        <v>6.615150721504166e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.794808142381283e-10</v>
+        <v>8.52350626590549e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.053750635322505e-10</v>
+        <v>5.8303609387854e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.308243747884409e-10</v>
+        <v>4.308243747884418e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.27632412197304e-10</v>
+        <v>4.276324121973041e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.474853393951946e-10</v>
+        <v>4.47485339395194e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.479133533846301e-10</v>
+        <v>4.479133533846304e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.479133533846301e-10</v>
+        <v>4.479133533846305e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.400658535638998e-10</v>
+        <v>4.400658535638975e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.440156598898079e-10</v>
+        <v>4.440156598898086e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.481300373931399e-10</v>
+        <v>4.481300373931386e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.519588240422498e-10</v>
+        <v>4.519588240422493e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.35949316148317e-10</v>
+        <v>4.359493161483167e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.509180757792305e-10</v>
+        <v>4.5091807577923e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.438802989595744e-10</v>
+        <v>8.438802989595745e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.154913916994601e-09</v>
+        <v>1.1549139169946e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.46405573087911e-09</v>
+        <v>1.464055730879111e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.484507151260217e-09</v>
+        <v>1.484507151260235e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.484507151260217e-09</v>
+        <v>1.484507151260235e-09</v>
       </c>
       <c r="G5" t="n">
         <v>1.355389609634349e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.518263731883953e-09</v>
+        <v>1.518263731883947e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.484507520843323e-09</v>
+        <v>1.484507520843322e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.591867956727394e-09</v>
+        <v>1.59186795672739e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.270996514126382e-09</v>
+        <v>1.270996514126379e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6740769722987e-09</v>
+        <v>1.674076972298705e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.148288736737216e-10</v>
+        <v>5.148288736737212e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.149594214017299e-10</v>
+        <v>5.149594214017306e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.317706314005481e-10</v>
+        <v>8.57884207334959e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.286649213375669e-10</v>
+        <v>5.286649213375667e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.323352062218856e-10</v>
+        <v>5.32335206221887e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.442901616261279e-10</v>
+        <v>5.240703524491765e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.570373786767565e-10</v>
+        <v>8.570373786767591e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.523543454553671e-10</v>
+        <v>8.523543454553686e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.454317834840825e-10</v>
+        <v>8.612246936607287e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.199303881167426e-10</v>
+        <v>5.199303881167445e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.350570952672839e-10</v>
+        <v>5.350570952672851e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.217064466345027e-09</v>
+        <v>1.217064466345024e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.218052272794819e-09</v>
+        <v>1.21805227279482e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.233696109327224e-09</v>
+        <v>1.23369610932722e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.234557338455213e-09</v>
+        <v>1.234557338455217e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.234557338455213e-09</v>
+        <v>1.234557338455217e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.226305945120478e-09</v>
+        <v>1.226305945120481e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.230255751446395e-09</v>
+        <v>1.230255751446392e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.234370128949722e-09</v>
+        <v>1.234370128949724e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.238198915598836e-09</v>
+        <v>1.238198915598834e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.222189407704898e-09</v>
+        <v>1.2221894077049e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.237158167335816e-09</v>
+        <v>1.237158167335815e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3131,19 +3131,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.186979291216885e-09</v>
+        <v>1.186979291216886e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.735899196219051e-09</v>
+        <v>1.735899196217778e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.864798844508544e-09</v>
+        <v>1.864798844508541e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.60240876478513e-09</v>
+        <v>1.602408764785124e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.221772317228387e-09</v>
+        <v>1.221772317228385e-09</v>
       </c>
       <c r="G8" t="n">
         <v>1.743829186227937e-09</v>
@@ -3155,13 +3155,13 @@
         <v>1.75189337005718e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.755829777525368e-09</v>
+        <v>1.75582977752537e-09</v>
       </c>
       <c r="K8" t="n">
         <v>1.1819321250961e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.326704189543869e-09</v>
+        <v>2.32670418954387e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.399946877599734e-10</v>
+        <v>9.399946877599701e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.11102594012914e-09</v>
+        <v>1.111025940129141e-09</v>
       </c>
       <c r="D9" t="n">
         <v>1.126699317576564e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.323570006140021e-09</v>
+        <v>1.323570006140026e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.127343306794993e-09</v>
+        <v>1.127343306794997e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.119279612454805e-09</v>
+        <v>1.119279612454804e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.123229418780714e-09</v>
+        <v>1.123229418780712e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.127343796284044e-09</v>
+        <v>1.127343796284045e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.131172582933152e-09</v>
+        <v>1.131172582933154e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.010479671436139e-10</v>
+        <v>1.01663932689413e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.130131834670134e-09</v>
+        <v>1.130131834670137e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.775083224639015e-10</v>
+        <v>5.758877382513646e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.315783107193047e-10</v>
+        <v>5.32012162911531e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.028124536940863e-10</v>
+        <v>5.772194444199559e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.896135908995472e-10</v>
+        <v>5.634211593176833e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.896135908995471e-10</v>
+        <v>5.634387974966113e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.903614304928039e-10</v>
+        <v>5.765641717985971e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.92265614764184e-10</v>
+        <v>5.751192476840084e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.05097444742162e-10</v>
+        <v>5.773428791403854e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.787679023241743e-10</v>
+        <v>6.348341941391309e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>6.980673074767818e-10</v>
+        <v>7.562382805771897e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.060294016555712e-10</v>
+        <v>5.772679908591413e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.514234713445884e-10</v>
+        <v>5.460254764737385e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.069158060216575e-10</v>
+        <v>4.770716828881668e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.805284639942936e-10</v>
+        <v>5.561559158902036e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.676818998357251e-10</v>
+        <v>5.347129441508853e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.676818998357251e-10</v>
+        <v>5.347305823298162e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.662072080911332e-10</v>
+        <v>5.51522453685287e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.677592980188837e-10</v>
+        <v>5.508792065778004e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.832084138677035e-10</v>
+        <v>5.570535823507287e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.57564269172147e-10</v>
+        <v>6.534315609955366e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.726058346299159e-10</v>
+        <v>8.455738707647104e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.842358704666286e-10</v>
+        <v>5.575516244639475e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.331192243321224e-10</v>
+        <v>4.331192243321235e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.30624233365265e-10</v>
+        <v>4.306242333652663e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.481614581214725e-10</v>
+        <v>4.481614581214733e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.496524099720083e-10</v>
+        <v>4.49652409972009e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.496524099720085e-10</v>
+        <v>4.496524099720092e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.407226852666505e-10</v>
+        <v>4.407226852672505e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.419126687481894e-10</v>
+        <v>4.419126687481895e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.49533975372949e-10</v>
+        <v>4.495339753728099e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.524370614580942e-10</v>
+        <v>4.524370614580962e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.355862971028365e-10</v>
+        <v>4.355862971028377e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.501130435802384e-10</v>
+        <v>4.501130435802387e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.872033769824062e-10</v>
+        <v>8.872033769824318e-10</v>
       </c>
       <c r="C5" t="n">
         <v>1.214221058682809e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.477651549834414e-09</v>
+        <v>1.477651549834416e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.510946754086918e-09</v>
+        <v>1.510946754086924e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.510946754086918e-09</v>
+        <v>1.510946754086924e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.369118590924206e-09</v>
+        <v>1.369118590924191e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.480404922276825e-09</v>
+        <v>1.480404922276824e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.51094729263585e-09</v>
+        <v>1.510947292635856e-09</v>
       </c>
       <c r="J5" t="n">
         <v>1.602623889353522e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.266914009623183e-09</v>
+        <v>1.266914009623186e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.660809199359768e-09</v>
+        <v>1.660809199359771e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.402157913746895e-10</v>
+        <v>8.402157913746911e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.20641729732615e-10</v>
+        <v>5.206417297326184e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.348138929049354e-10</v>
+        <v>5.3481389290494e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.323784679312441e-10</v>
+        <v>5.323784679312463e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.362179359029161e-10</v>
+        <v>5.362179359029167e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.478192523091245e-10</v>
+        <v>8.478192523091252e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.59444088208274e-10</v>
+        <v>5.28451897708111e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.359974577095417e-10</v>
+        <v>8.566305424154744e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.649756434265892e-10</v>
+        <v>5.484752277603531e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.220128392121449e-10</v>
+        <v>5.22012839212143e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.366977555170805e-10</v>
+        <v>5.366977555170824e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.212549527202894e-09</v>
+        <v>1.212549527202896e-09</v>
       </c>
       <c r="C7" t="n">
         <v>1.214462154555274e-09</v>
@@ -3496,22 +3496,22 @@
         <v>1.227562576762338e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.22926216885779e-09</v>
+        <v>1.229262168857791e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.22926216885779e-09</v>
+        <v>1.229262168857791e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.22015298813733e-09</v>
+        <v>1.220152988137331e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.221342971618962e-09</v>
+        <v>1.221342971618963e-09</v>
       </c>
       <c r="I7" t="n">
         <v>1.22896427824368e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.231867364328868e-09</v>
+        <v>1.231867364328869e-09</v>
       </c>
       <c r="K7" t="n">
         <v>1.215016599973608e-09</v>
@@ -3530,10 +3530,10 @@
         <v>1.177067162478251e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.718735987398563e-09</v>
+        <v>1.718735987400312e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.843270917526296e-09</v>
+        <v>1.843270917526293e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.585683145223976e-09</v>
@@ -3542,19 +3542,19 @@
         <v>1.210772686164589e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.723998910867059e-09</v>
+        <v>1.723998910867061e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.725188894349699e-09</v>
+        <v>1.725188894349702e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.732810200973409e-09</v>
+        <v>1.73281020097341e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.735819280570418e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.169515935413392e-09</v>
+        <v>1.169515935413394e-09</v>
       </c>
       <c r="L8" t="n">
         <v>2.296762763374446e-09</v>
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.187483861247383e-10</v>
+        <v>9.187483861247399e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.083965979394488e-09</v>
+        <v>1.083965979394492e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.097095806559892e-09</v>
+        <v>1.09709580655989e-09</v>
       </c>
       <c r="E9" t="n">
         <v>1.286918084460988e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.09846744641322e-09</v>
+        <v>1.098467446413214e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.089656812976542e-09</v>
+        <v>1.089656812976547e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.090846796458172e-09</v>
+        <v>1.090846796458188e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.098468103082896e-09</v>
+        <v>1.098468103082901e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.101371189168085e-09</v>
+        <v>1.101371189168087e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.860621396576521e-10</v>
+        <v>9.899009790497518e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.099047171290224e-09</v>
+        <v>1.099047171290232e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.04734657126671e-10</v>
+        <v>6.05176724929552e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.283444257460832e-10</v>
+        <v>5.401705054693862e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.325576742357334e-10</v>
+        <v>6.066409950590459e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.91151013915438e-10</v>
+        <v>5.729245642087692e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.911510139154382e-10</v>
+        <v>5.72942072001859e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.246078694676628e-10</v>
+        <v>6.062226126236869e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.97690051780537e-10</v>
+        <v>6.085642740429437e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.30279159432503e-10</v>
+        <v>6.065240594122157e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.730309649756375e-10</v>
+        <v>6.47857976488624e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.139454964219084e-10</v>
+        <v>7.682830254804751e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.695608097312596e-10</v>
+        <v>6.084906104510672e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.804766314620377e-10</v>
+        <v>5.869940804875834e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.046546366973011e-10</v>
+        <v>4.8160413728853e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.124788646580888e-10</v>
+        <v>5.980732068201123e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.707384548973585e-10</v>
+        <v>5.424355443219524e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.707384548973534e-10</v>
+        <v>5.424530521150409e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.033349423777099e-10</v>
+        <v>5.951286130357716e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.86799650885373e-10</v>
+        <v>6.213767277083906e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.098017729187411e-10</v>
+        <v>5.972578324847204e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.515019350373972e-10</v>
+        <v>6.634124319092625e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.918131087549332e-10</v>
+        <v>8.609625583987753e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.550456404392994e-10</v>
+        <v>6.122452630765688e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.37643741634083e-10</v>
+        <v>4.376437416340864e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.318685569679565e-10</v>
+        <v>4.318685569679575e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.54183346344175e-10</v>
+        <v>4.541833463441785e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.524907294847926e-10</v>
+        <v>4.524907294847937e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.524907294847925e-10</v>
+        <v>4.524907294847938e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.494212982861852e-10</v>
+        <v>4.494212982861879e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.929060490256867e-10</v>
+        <v>4.929060490256899e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.528452234258481e-10</v>
+        <v>4.528452234258503e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.484439753694317e-10</v>
+        <v>4.484439753694345e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.460561356109005e-10</v>
+        <v>4.460561356109034e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.76212609622025e-10</v>
+        <v>4.762126096220271e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.757982152481036e-10</v>
+        <v>8.757982152481055e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.163354838318224e-09</v>
+        <v>1.163354838318225e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.527620085082178e-09</v>
+        <v>1.527620085082181e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.513518548272854e-09</v>
+        <v>1.51351854827285e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.513518548272854e-09</v>
+        <v>1.51351854827285e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.462265361917842e-09</v>
+        <v>1.462265361917797e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.435330741130778e-09</v>
+        <v>2.435330741130788e-09</v>
       </c>
       <c r="I5" t="n">
         <v>1.513517833327636e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.470418438389461e-09</v>
+        <v>1.470418438389464e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.385664829958924e-09</v>
+        <v>1.385664829958927e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.131153631918268e-09</v>
+        <v>2.131153631918276e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.259330246840166e-10</v>
+        <v>5.259330246840219e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.236002788959306e-10</v>
+        <v>5.236002788959302e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.427552442297814e-10</v>
+        <v>5.427552442297837e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.373707592970663e-10</v>
+        <v>5.373707592970671e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.413168567420191e-10</v>
+        <v>5.413168567420194e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.7614457690374e-10</v>
+        <v>5.377105813361237e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.274503288034791e-10</v>
+        <v>9.274503288034809e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.795685020434023e-10</v>
+        <v>5.411345064757864e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.802792447615792e-10</v>
+        <v>5.466881472363147e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.344116821097362e-10</v>
+        <v>5.344116821097382e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.647596956451531e-10</v>
+        <v>5.647596956451558e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.271021963903829e-09</v>
+        <v>1.271021963903833e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.269709949480357e-09</v>
+        <v>1.269709949480358e-09</v>
       </c>
       <c r="D7" t="n">
         <v>1.287530509610893e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.286389382145018e-09</v>
+        <v>1.28638938214502e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.286389382145018e-09</v>
+        <v>1.28638938214502e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.282799520555931e-09</v>
+        <v>1.282799520555937e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.326284271295433e-09</v>
+        <v>1.326284271295438e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.286223445695596e-09</v>
+        <v>1.286223445695597e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.281822197639181e-09</v>
+        <v>1.281822197639186e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.27943435788065e-09</v>
+        <v>1.279434357880652e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.309590831891774e-09</v>
+        <v>1.309590831891778e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.243123978654407e-09</v>
+        <v>1.243123978654408e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.825236681698947e-09</v>
+        <v>1.825236681697798e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.963689220806108e-09</v>
+        <v>1.963689220806112e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.682233591607036e-09</v>
+        <v>1.682233591607037e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.276927057310951e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.838014832034795e-09</v>
+        <v>1.838014832034797e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.881499582774516e-09</v>
+        <v>1.881499582774519e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.841438757174456e-09</v>
+        <v>1.841438757174459e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.837152107672495e-09</v>
+        <v>1.837152107672504e-09</v>
       </c>
       <c r="K8" t="n">
         <v>1.240704743766581e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.473916741022878e-09</v>
+        <v>2.473916741022877e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3966,34 +3966,34 @@
         <v>1.004171596674707e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1905780028769e-09</v>
+        <v>1.190578002876896e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.208429843757395e-09</v>
+        <v>1.2084298437574e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.423715319447194e-09</v>
+        <v>1.423715319447189e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.207092076298684e-09</v>
+        <v>1.207092076298683e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.203667573952474e-09</v>
+        <v>1.203667573952478e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.24715232469198e-09</v>
+        <v>1.247152324691977e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.207091499092138e-09</v>
+        <v>1.207091499092137e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.20269025103572e-09</v>
+        <v>1.202690251035722e-09</v>
       </c>
       <c r="K9" t="n">
         <v>1.091537714405476e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.230458885288318e-09</v>
+        <v>1.230458885288313e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.677817347136489e-10</v>
+        <v>5.700973275176136e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.257708463414894e-10</v>
+        <v>5.31351187917215e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.947158255779217e-10</v>
+        <v>5.715148152243854e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.851615522498565e-10</v>
+        <v>5.616580794717284e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.851615522498566e-10</v>
+        <v>5.616756751948269e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.817549774714055e-10</v>
+        <v>5.708327115308592e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.855552918537951e-10</v>
+        <v>5.694990569589051e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.958380660681824e-10</v>
+        <v>5.715769497536102e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.709443733060268e-10</v>
+        <v>6.297831895569423e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>6.995852098232185e-10</v>
+        <v>7.550795821451286e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.962457405706072e-10</v>
+        <v>5.71472743314272e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.407262312754614e-10</v>
+        <v>5.356622162797858e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.997717214664924e-10</v>
+        <v>4.744755464307515e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7170601514949e-10</v>
+        <v>5.464052410125924e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.62329081793644e-10</v>
+        <v>5.31132848321737e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.623290817936445e-10</v>
+        <v>5.311504440448332e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.567983549953989e-10</v>
+        <v>5.415796780440198e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.605261336957696e-10</v>
+        <v>5.416592097711648e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.729304062980168e-10</v>
+        <v>5.468658391517001e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.489327972073157e-10</v>
+        <v>6.446004695550579e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.740638456065263e-10</v>
+        <v>8.446039037861615e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.734728966212987e-10</v>
+        <v>5.471578491530515e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.280897144433458e-10</v>
+        <v>4.280897144433446e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.243331323392012e-10</v>
+        <v>4.243331323391997e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.441008901679125e-10</v>
+        <v>4.441008901679113e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4473363437775e-10</v>
+        <v>4.447336343777474e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.447336343777499e-10</v>
+        <v>4.447336343777469e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.363571727503271e-10</v>
+        <v>4.363571727503111e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.386755508340828e-10</v>
+        <v>4.386755508340822e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.447672732459751e-10</v>
+        <v>4.44767273245973e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.480514878106109e-10</v>
+        <v>4.480514878106097e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.341612014795619e-10</v>
+        <v>4.341612014795593e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.450495713526098e-10</v>
+        <v>4.450495713526087e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.532669532995992e-10</v>
+        <v>8.532669532995963e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.157200002742956e-09</v>
+        <v>1.157200002742952e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.461038092253877e-09</v>
+        <v>1.46103809225387e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.482298239119888e-09</v>
+        <v>1.482298239119886e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.482298239119888e-09</v>
+        <v>1.482298239119886e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.346828900034188e-09</v>
+        <v>1.346828900033887e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.477755789660366e-09</v>
+        <v>1.477755789660359e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.482298645756054e-09</v>
+        <v>1.48229864575605e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.579493267445463e-09</v>
+        <v>1.579493267445456e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.295218777759979e-09</v>
+        <v>1.295218777759975e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.622527463051992e-09</v>
+        <v>1.622527463051989e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.130399146328557e-10</v>
+        <v>8.323128726994246e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.126860786197146e-10</v>
+        <v>5.12686078619712e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.293496326842396e-10</v>
+        <v>5.293494936525665e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.262573853452036e-10</v>
+        <v>5.262573853452013e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.299269114869204e-10</v>
+        <v>5.299269114869133e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.213073729398367e-10</v>
+        <v>5.213073729398247e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.514519996967351e-10</v>
+        <v>8.514519996967287e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.489904315020601e-10</v>
+        <v>8.489904315020527e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.572485302882018e-10</v>
+        <v>5.424186691794235e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.192141608053807e-10</v>
+        <v>5.192141608053772e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.301136389093072e-10</v>
+        <v>5.301136389093051e-10</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.205323304644908e-09</v>
+        <v>1.205323304644904e-09</v>
       </c>
       <c r="C7" t="n">
         <v>1.205845784216158e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.221305372785449e-09</v>
+        <v>1.221305372785444e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.222241282711269e-09</v>
+        <v>1.222241282711262e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.222241282711269e-09</v>
+        <v>1.222241282711262e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.21359076295189e-09</v>
+        <v>1.213590762951872e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.215909141035647e-09</v>
+        <v>1.215909141035642e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.222000863447538e-09</v>
+        <v>1.222000863447534e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.225285078012171e-09</v>
+        <v>1.225285078012168e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.211394791681125e-09</v>
+        <v>1.211394791681118e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.222283161554172e-09</v>
+        <v>1.222283161554167e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.164114831425364e-09</v>
+        <v>1.164114831425359e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.698627082014802e-09</v>
+        <v>1.698627082014793e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.824393459094121e-09</v>
+        <v>1.824393459094111e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.568795041304132e-09</v>
+        <v>1.568795041304122e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.19786788605622e-09</v>
+        <v>1.197867886056215e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.706000524493773e-09</v>
+        <v>1.706000524493757e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.708318902578203e-09</v>
+        <v>1.708318902578198e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.714410624989422e-09</v>
+        <v>1.714410624989412e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.717799710896546e-09</v>
+        <v>1.717799710896538e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.160274085784859e-09</v>
+        <v>1.160274085784856e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.272101789802165e-09</v>
+        <v>2.272101789802159e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.269165762993719e-10</v>
+        <v>9.269165762993595e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.094099691862175e-09</v>
+        <v>1.094099691862164e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.109588605293188e-09</v>
+        <v>1.109588605293177e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.302577258839477e-09</v>
+        <v>1.302577258839459e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.110254250705086e-09</v>
+        <v>1.110254250705068e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1018446705979e-09</v>
+        <v>1.101844670597871e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.104163048681663e-09</v>
+        <v>1.104163048681647e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.110254771093557e-09</v>
+        <v>1.110254771093536e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.113538985658188e-09</v>
+        <v>1.11353898565817e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.003084963692981e-09</v>
+        <v>8.897931534817559e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.110537069200191e-09</v>
+        <v>1.110537069200179e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.663525240755982e-10</v>
+        <v>5.685893268658384e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>4.270766998941485e-10</v>
+        <v>5.312246052878528e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.895183909702799e-10</v>
+        <v>5.698085004293883e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.822952138174029e-10</v>
+        <v>5.591827276620217e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.822952138174029e-10</v>
+        <v>5.592004173474733e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.789241576027746e-10</v>
+        <v>5.692509469691e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.816373112727661e-10</v>
+        <v>5.678625763740493e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9411389868379e-10</v>
+        <v>5.700535108980325e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.71457081366189e-10</v>
+        <v>6.258340903685579e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>6.927000112738341e-10</v>
+        <v>7.515421612037657e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.939387572221567e-10</v>
+        <v>5.699163662268523e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.388328143818683e-10</v>
+        <v>5.313087060124138e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.008174858267189e-10</v>
+        <v>4.727280510380655e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.65478360105623e-10</v>
+        <v>5.406366060018703e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.589544744778694e-10</v>
+        <v>5.250956871503618e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.589544744778692e-10</v>
+        <v>5.251133768358131e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.532927971441619e-10</v>
+        <v>5.366987677063066e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.557389993526242e-10</v>
+        <v>5.36372956360257e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.708087656496478e-10</v>
+        <v>5.424000732714876e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.497629226607086e-10</v>
+        <v>6.377206839432961e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.66230540691118e-10</v>
+        <v>8.359700507481315e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.705699539138641e-10</v>
+        <v>5.424751151551988e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.291576763177681e-10</v>
+        <v>4.291576763177672e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.257133719738417e-10</v>
+        <v>4.25713371973842e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.429288025656078e-10</v>
+        <v>4.429288025656073e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.458645469994861e-10</v>
+        <v>4.458645469994851e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.458645469994862e-10</v>
+        <v>4.458645469994851e-10</v>
       </c>
       <c r="G4" t="n">
         <v>4.365849966969355e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.382644864898645e-10</v>
+        <v>4.382644864898638e-10</v>
       </c>
       <c r="I4" t="n">
         <v>4.456156862397848e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.522127920520504e-10</v>
+        <v>4.522127920520498e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.333140873253921e-10</v>
+        <v>4.333140873253917e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.455956866166312e-10</v>
+        <v>4.455956866166311e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4595,34 +4595,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.79673589086529e-10</v>
+        <v>8.796735890865277e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.195690727435751e-09</v>
+        <v>1.19569072743575e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.447956962445814e-09</v>
+        <v>1.447956962445811e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.504501387536189e-09</v>
+        <v>1.504501387536191e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.504501387536189e-09</v>
+        <v>1.504501387536191e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.358003249795926e-09</v>
+        <v>1.358003249795925e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.477651729459535e-09</v>
+        <v>1.477651729459532e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.504501927866862e-09</v>
+        <v>1.504501927866839e-09</v>
       </c>
       <c r="J5" t="n">
         <v>1.660985947087887e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.287633289497122e-09</v>
+        <v>1.287633289497123e-09</v>
       </c>
       <c r="L5" t="n">
         <v>1.641094481425986e-09</v>
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.162898819139159e-10</v>
+        <v>8.358993584511621e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.165872872312004e-10</v>
+        <v>5.165872872312033e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.302813426460382e-10</v>
+        <v>5.302814702074409e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.291639326365982e-10</v>
+        <v>5.291639326365966e-10</v>
       </c>
       <c r="F6" t="n">
         <v>5.329776410892511e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.433266788303277e-10</v>
+        <v>5.237172022930861e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.549451519530505e-10</v>
+        <v>8.549451519530515e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.523573683731764e-10</v>
+        <v>5.32747891835935e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.488350600023175e-10</v>
+        <v>8.643158269391799e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.205139091925195e-10</v>
+        <v>5.205139091925184e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.328742165442364e-10</v>
+        <v>5.328742165442367e-10</v>
       </c>
     </row>
     <row r="7">
@@ -4675,31 +4675,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.198976725466366e-09</v>
+        <v>1.198976725466367e-09</v>
       </c>
       <c r="C7" t="n">
         <v>1.20019491777885e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.212718909434057e-09</v>
+        <v>1.212718909434058e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.215771235081481e-09</v>
+        <v>1.215771235081482e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.215771235081481e-09</v>
+        <v>1.215771235081482e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.206404045845532e-09</v>
+        <v>1.206404045845535e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.208083535638462e-09</v>
+        <v>1.208083535638463e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.215434735388383e-09</v>
+        <v>1.215434735388384e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.222031841200648e-09</v>
+        <v>1.222031841200649e-09</v>
       </c>
       <c r="K7" t="n">
         <v>1.203133136473991e-09</v>
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.151095127660149e-09</v>
+        <v>1.151095127660148e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.676869138248125e-09</v>
+        <v>1.676869138246446e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.79763496024023e-09</v>
+        <v>1.797634960240226e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.548716878829887e-09</v>
+        <v>1.548716878829883e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.18438390451203e-09</v>
+        <v>1.184383904512031e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.682616780396709e-09</v>
+        <v>1.682616780396707e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.684296270190588e-09</v>
+        <v>1.684296270190589e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.691647469939558e-09</v>
+        <v>1.691647469939557e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.698347575351658e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.145516217369621e-09</v>
+        <v>1.145516217369623e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.239087824565507e-09</v>
+        <v>2.239087824565506e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.039188178332934e-10</v>
+        <v>9.039188178332928e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.064892851742615e-09</v>
+        <v>1.064892851742613e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.077446003264373e-09</v>
+        <v>1.077446003264367e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.264487041557816e-09</v>
+        <v>1.264487041557818e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.080132018630306e-09</v>
+        <v>1.080132018630302e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.071101979809301e-09</v>
+        <v>1.071101979809298e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.072781469602227e-09</v>
+        <v>1.072781469602225e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.08013266935215e-09</v>
+        <v>1.080132669352147e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.086729775164415e-09</v>
+        <v>1.086729775164411e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.715125903997415e-10</v>
+        <v>9.715125903997442e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.080112669728993e-09</v>
+        <v>1.080112669728991e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.031890439112046e-10</v>
+        <v>5.368602500669173e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.586176531734821e-10</v>
+        <v>6.339574237700792e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.491215099508771e-10</v>
+        <v>5.392775845253584e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.979510701044299e-10</v>
+        <v>6.683187425837735e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.77600732104664e-10</v>
+        <v>5.681603682019286e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.01308348514437e-10</v>
+        <v>5.367612728035463e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.561194242981243e-10</v>
+        <v>5.434318019416059e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.344513152083405e-10</v>
+        <v>5.332449067515801e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>8.2402401296094e-10</v>
+        <v>7.838256045071777e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.749649674986683e-10</v>
+        <v>7.927994694425463e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>7.275894007165386e-10</v>
+        <v>5.486916288115728e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.948796102683812e-10</v>
+        <v>4.877868080474107e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.38769202025452e-10</v>
+        <v>6.300432671062898e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.477114610956794e-10</v>
+        <v>5.050457040690139e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.793229796515203e-10</v>
+        <v>6.855865365669831e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.589726416517537e-10</v>
+        <v>5.202453692413647e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.927164209772217e-10</v>
+        <v>4.872040485184051e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>7.701673319667929e-10</v>
+        <v>5.443952320524168e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.15681570506761e-10</v>
+        <v>4.619823123395672e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.195842505678853e-10</v>
+        <v>9.031259786836968e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.609301202807312e-10</v>
+        <v>8.993572354536205e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.529832637280575e-10</v>
+        <v>5.731571259902514e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.966894305854873e-10</v>
+        <v>4.966894305854878e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.533152641711422e-10</v>
+        <v>4.533152641711411e-10</v>
       </c>
       <c r="D4" t="n">
         <v>5.239943353223848e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.543684588508022e-10</v>
+        <v>4.543684588508003e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.543684588508021e-10</v>
+        <v>4.543684588508006e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.955142758510297e-10</v>
+        <v>4.955142758510398e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.875852927176676e-10</v>
+        <v>5.875852927176682e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.556904513248323e-10</v>
+        <v>4.556904513248317e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.120039851567183e-10</v>
+        <v>5.120039851567194e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.740306172187925e-10</v>
+        <v>4.740306172187933e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>6.300792982967693e-10</v>
+        <v>6.300792982967694e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.260500207805924e-09</v>
+        <v>2.260500207805934e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.487311844996569e-09</v>
+        <v>1.487311844996565e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.780259964620139e-09</v>
+        <v>2.78025996462013e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.487311895881658e-09</v>
+        <v>1.487311895881651e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.487311895881658e-09</v>
+        <v>1.487311895881651e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.308070204049993e-09</v>
+        <v>2.308070204049917e-09</v>
       </c>
       <c r="H5" t="n">
         <v>4.341388130399167e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.487301210831004e-09</v>
+        <v>1.487301210830998e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.683066033484554e-09</v>
+        <v>2.683066033484562e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.888575350508746e-09</v>
+        <v>1.888575350508767e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.097308185399344e-09</v>
+        <v>2.097308185399329e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.441411897334472e-10</v>
+        <v>5.932772241087865e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.505488042306985e-10</v>
+        <v>5.50548804230697e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>6.219323377906988e-10</v>
+        <v>6.219320970655138e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.468140515009005e-10</v>
+        <v>5.468140515008995e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.522152958699128e-10</v>
+        <v>5.522152958699119e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.429660349989883e-10</v>
+        <v>5.921020693743212e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>1.032368044570475e-09</v>
+        <v>1.032368044570474e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>9.031422104727934e-10</v>
+        <v>9.031422104727939e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.570729122901728e-10</v>
+        <v>6.190740329627383e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.70178245349718e-10</v>
+        <v>5.701782453497168e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>7.277195333746235e-10</v>
+        <v>7.277195333746242e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5074,31 +5074,31 @@
         <v>1.335190792617673e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.294202447522585e-09</v>
+        <v>1.294202447522586e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.362463374565287e-09</v>
+        <v>1.362463374565286e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.294137987260426e-09</v>
+        <v>1.294137987260424e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.294137987260426e-09</v>
+        <v>1.294137987260424e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.334015637883217e-09</v>
+        <v>1.33401563788322e-09</v>
       </c>
       <c r="H7" t="n">
         <v>1.426086654749854e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.294191813357019e-09</v>
+        <v>1.29419181335702e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.350505347188905e-09</v>
+        <v>1.350505347188906e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.31253197925098e-09</v>
+        <v>1.312531979250979e-09</v>
       </c>
       <c r="L7" t="n">
         <v>1.468580660328956e-09</v>
@@ -5114,10 +5114,10 @@
         <v>1.304692344684998e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.846761680602509e-09</v>
+        <v>1.846761680603383e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>2.035842960128341e-09</v>
+        <v>2.035842960128345e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.68730788268031e-09</v>
@@ -5126,22 +5126,22 @@
         <v>1.282163915755573e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.886481461322958e-09</v>
+        <v>1.886481461322962e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.978552478189572e-09</v>
+        <v>1.978552478189567e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.846657636796762e-09</v>
+        <v>1.846657636796757e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.903085739892893e-09</v>
+        <v>1.903085739892891e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.271204670676776e-09</v>
+        <v>1.271204670676775e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.630001411971366e-09</v>
+        <v>2.630001411971368e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5151,34 +5151,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.08686223163772e-09</v>
+        <v>1.086862231637718e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.239368916085024e-09</v>
+        <v>1.239368916085018e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.307662385635563e-09</v>
+        <v>1.307662385635568e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.462658116456471e-09</v>
+        <v>1.462658116456473e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.23936879859474e-09</v>
+        <v>1.239368798594737e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.279182106445657e-09</v>
+        <v>1.279182106445654e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.371253123312296e-09</v>
+        <v>1.3712531233123e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.239358281919461e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.295671815751346e-09</v>
+        <v>1.295671815751347e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.145586760195725e-09</v>
+        <v>1.14558676019573e-09</v>
       </c>
       <c r="L9" t="n">
         <v>1.413747128891397e-09</v>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.817456643711823e-10</v>
+        <v>5.316503021309407e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.615723267403332e-10</v>
+        <v>6.262850892765988e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.364480935190332e-10</v>
+        <v>5.345291823292169e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.992950209260673e-10</v>
+        <v>6.592640884358433e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.838572869610053e-10</v>
+        <v>5.631948523653333e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.952419643662165e-10</v>
+        <v>5.32360585593869e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.252973524002592e-10</v>
+        <v>5.377237605571305e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.422610762411091e-10</v>
+        <v>5.295746439140456e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.970458700048995e-10</v>
+        <v>7.689849023052544e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.700745882446932e-10</v>
+        <v>7.85316014349375e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>7.024585160804868e-10</v>
+        <v>5.432715110392439e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.68144199707747e-10</v>
+        <v>4.774405406748509e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.408191031714307e-10</v>
+        <v>6.239632093139509e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.310633248018349e-10</v>
+        <v>4.979080351332088e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.797693596021588e-10</v>
+        <v>6.772559813320655e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.64331625637095e-10</v>
+        <v>5.186646615183651e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.836677404521644e-10</v>
+        <v>4.825550265078428e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>7.325865523077078e-10</v>
+        <v>5.304395222637292e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.227574670046441e-10</v>
+        <v>4.625396355547144e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.882818442922502e-10</v>
+        <v>8.786853390860749e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.538398669872398e-10</v>
+        <v>8.910600215879389e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.220073017494182e-10</v>
+        <v>5.613330451549082e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.756996620618107e-10</v>
+        <v>4.75699662061811e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.502368401800058e-10</v>
+        <v>4.502368401800062e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.082179382516599e-10</v>
+        <v>5.082179382516606e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.511944475739686e-10</v>
+        <v>4.511944475739682e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.511944475739686e-10</v>
+        <v>4.511944475739678e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.836681394231812e-10</v>
+        <v>4.836681394231851e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.610259259491993e-10</v>
+        <v>5.610259259491972e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.521101542436259e-10</v>
+        <v>4.521101542436253e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.948442399897816e-10</v>
+        <v>4.948442399897812e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.652783241221673e-10</v>
+        <v>4.652783241221668e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>6.069016135524663e-10</v>
+        <v>6.069016135524659e-10</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.960728583041016e-09</v>
+        <v>1.960728583041018e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.500923814788661e-09</v>
+        <v>1.500923814788659e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.494815734646686e-09</v>
+        <v>2.4948157346467e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.500923857778591e-09</v>
+        <v>1.500923857778586e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.500923857778591e-09</v>
+        <v>1.500923857778586e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.125975347643491e-09</v>
+        <v>2.125975347643531e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>3.763207302169692e-09</v>
+        <v>3.763207302169691e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.500915077160088e-09</v>
+        <v>1.500915077160091e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.393543291357194e-09</v>
+        <v>2.39354329135719e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7554620742992e-09</v>
+        <v>1.755462074299201e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.185591835159489e-09</v>
+        <v>2.185591835159488e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.923274007539733e-10</v>
+        <v>5.667124025452323e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.417680913361204e-10</v>
+        <v>5.417680913361208e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>6.002879836840252e-10</v>
+        <v>6.002879836840468e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.382709607273361e-10</v>
+        <v>5.38270960727336e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.431077310641497e-10</v>
+        <v>5.4310773106415e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.002958781153444e-10</v>
+        <v>5.746808799066073e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.751336710126361e-10</v>
+        <v>9.751336710126338e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.687378929357893e-10</v>
+        <v>8.687378929357878e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.093829058487707e-10</v>
+        <v>5.955168041999536e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.558940214370589e-10</v>
+        <v>5.558940214370588e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.987890531412296e-10</v>
+        <v>6.987890531412299e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5467,16 +5467,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.249384926138193e-09</v>
+        <v>1.249384926138192e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.22580415594858e-09</v>
+        <v>1.225804155948581e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.281873141358913e-09</v>
+        <v>1.281873141358916e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.22581016815031e-09</v>
+        <v>1.225810168150309e-09</v>
       </c>
       <c r="F7" t="n">
         <v>1.22581016815031e-09</v>
@@ -5494,10 +5494,10 @@
         <v>1.268529504066165e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.238963588198549e-09</v>
+        <v>1.23896358819855e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.380586877628847e-09</v>
+        <v>1.380586877628848e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.211606335672019e-09</v>
+        <v>1.211606335672021e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.719514914208147e-09</v>
+        <v>1.71951491420815e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.885643258893364e-09</v>
+        <v>1.885643258893368e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.574174278038266e-09</v>
+        <v>1.574174278038269e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.20488980796071e-09</v>
+        <v>1.204889807960711e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.750916334264477e-09</v>
+        <v>1.750916334264481e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82827412079046e-09</v>
+        <v>1.828274120790458e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.719358349084921e-09</v>
+        <v>1.71935834908492e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.762196858734412e-09</v>
+        <v>1.762196858734414e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.191315056178874e-09</v>
+        <v>1.191315056178876e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.429180457439045e-09</v>
+        <v>2.429180457439046e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5547,22 +5547,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.955627902229021e-10</v>
+        <v>9.955627902229047e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.143502163137033e-09</v>
+        <v>1.143502163137035e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.199601414376398e-09</v>
+        <v>1.199601414376396e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.341432815437262e-09</v>
+        <v>1.341432815437263e-09</v>
       </c>
       <c r="F9" t="n">
         <v>1.14350205876215e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.175051410688021e-09</v>
+        <v>1.17505141068802e-09</v>
       </c>
       <c r="H9" t="n">
         <v>1.252409197214034e-09</v>
@@ -5574,10 +5574,10 @@
         <v>1.186227511254618e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.406870658868547e-10</v>
+        <v>1.057282237024412e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.298284884817302e-09</v>
+        <v>1.298284884817301e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.679869852871992e-10</v>
+        <v>5.283969284192615e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.835222769645452e-10</v>
+        <v>6.230355130531127e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.196459079935584e-10</v>
+        <v>5.311156349184125e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.201891770237749e-10</v>
+        <v>6.551094617364607e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.07962376920775e-10</v>
+        <v>5.617129239757721e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.872732074681643e-10</v>
+        <v>5.294119239871224e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.922620390175598e-10</v>
+        <v>5.334486134419e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.666435833676671e-10</v>
+        <v>5.283288977398088e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.847230307688896e-10</v>
+        <v>7.601545646341936e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.649701676970351e-10</v>
+        <v>7.807175908612269e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>6.80045488449277e-10</v>
+        <v>5.395515870837789e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.509841308297152e-10</v>
+        <v>4.7082597778889e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.651143072935207e-10</v>
+        <v>6.283005894656468e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.104025930556292e-10</v>
+        <v>4.901283041409728e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>7.029921542197194e-10</v>
+        <v>6.801260049472666e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.907653541167223e-10</v>
+        <v>5.259464532338456e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.731672814667366e-10</v>
+        <v>4.781078909811562e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.932416972757751e-10</v>
+        <v>5.163919718688148e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.495882280038258e-10</v>
+        <v>4.702112845520169e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.738621756526676e-10</v>
+        <v>8.654043753540551e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.469808324830747e-10</v>
+        <v>8.853516013547942e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>7.948935271203985e-10</v>
+        <v>5.513434872296221e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.67699211615628e-10</v>
+        <v>4.676992116156262e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.655387841652202e-10</v>
+        <v>4.655387841652226e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.984082521903177e-10</v>
+        <v>4.98408252190317e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.664591296382819e-10</v>
+        <v>4.66459129638285e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.664591296382815e-10</v>
+        <v>4.664591296382849e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.791199170636601e-10</v>
+        <v>4.791199170636509e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.415720599306408e-10</v>
+        <v>5.415720599306404e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.668569670033937e-10</v>
+        <v>4.668569670033923e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.920066987423095e-10</v>
+        <v>4.920066987423079e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.637951297431827e-10</v>
+        <v>4.637951297431812e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.937595403314275e-10</v>
+        <v>5.937595403314298e-10</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.815528573891112e-09</v>
+        <v>1.815528573891113e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.734936752250425e-09</v>
+        <v>1.734936752250428e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.306215242082475e-09</v>
+        <v>2.306215242082485e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.734936783492013e-09</v>
+        <v>1.734936783492054e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.734936783492013e-09</v>
+        <v>1.734936783492054e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.037868304410119e-09</v>
+        <v>2.037868304409947e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>3.317830314701786e-09</v>
+        <v>3.317830314701814e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.734932429834609e-09</v>
+        <v>1.734932429834657e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.35608566037116e-09</v>
+        <v>2.356085660371159e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.705251787033316e-09</v>
+        <v>1.705251787033315e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.496874446130652e-09</v>
+        <v>1.982110814457966e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.59705829302317e-10</v>
+        <v>5.597058293023211e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.581477865165738e-10</v>
+        <v>5.581477865165744e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>9.141755396449865e-10</v>
+        <v>5.912189080776065e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.546127758927038e-10</v>
+        <v>5.546127758927025e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.590295592101558e-10</v>
+        <v>5.59029559210149e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.711265347503494e-10</v>
+        <v>8.957175408414876e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.55671284877493e-10</v>
+        <v>9.556712848774885e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.834545907812575e-10</v>
+        <v>5.588635846900884e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.936841558617628e-10</v>
+        <v>9.06537382466447e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.554190172841195e-10</v>
+        <v>5.5541901728412e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.866017600841458e-10</v>
+        <v>6.866017600841479e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5866,34 +5866,34 @@
         <v>1.236620752088378e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.235782829891916e-09</v>
+        <v>1.235782829891912e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.267299753392806e-09</v>
+        <v>1.267299753392805e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.235885390673013e-09</v>
+        <v>1.235885390673016e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.235885390673013e-09</v>
+        <v>1.235885390673015e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.248041457536386e-09</v>
+        <v>1.248041457536376e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.310493600403391e-09</v>
+        <v>1.310493600403392e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.235778507476146e-09</v>
+        <v>1.235778507476144e-09</v>
       </c>
       <c r="J7" t="n">
         <v>1.260928239215059e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.232716670215933e-09</v>
+        <v>1.232716670215931e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.362681080804183e-09</v>
+        <v>1.362681080804181e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5903,28 +5903,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.192838240521835e-09</v>
+        <v>1.192838240521833e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.715998047719295e-09</v>
+        <v>1.715998047719292e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.855911209230793e-09</v>
+        <v>1.855911209230794e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.572721486781405e-09</v>
+        <v>1.572721486781403e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.208681787118136e-09</v>
+        <v>1.20868178711813e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.728018018447987e-09</v>
+        <v>1.728018018447997e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.790470161314963e-09</v>
+        <v>1.790470161314962e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.715755068387738e-09</v>
+        <v>1.715755068387735e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.741007733857926e-09</v>
@@ -5933,7 +5933,7 @@
         <v>1.179205064974663e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.389767789001098e-09</v>
+        <v>2.389767789001102e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.654372359040866e-10</v>
+        <v>9.654372359040771e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.129678206650681e-09</v>
+        <v>1.129678206650676e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.161225373657723e-09</v>
+        <v>1.161225373657717e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.320175791525118e-09</v>
+        <v>1.320175791525109e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.129678099323872e-09</v>
+        <v>1.12967809932387e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.141936834295158e-09</v>
+        <v>1.14193683429515e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.204388977162158e-09</v>
+        <v>1.204388977162151e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.129673884234911e-09</v>
+        <v>1.129673884234907e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.154823615973828e-09</v>
+        <v>1.154823615973821e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.030964773989495e-09</v>
+        <v>1.030964773989486e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.256576457562947e-09</v>
+        <v>1.256576457562942e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.072801639675406e-10</v>
+        <v>5.079202332321704e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.042462261176091e-10</v>
+        <v>5.918225059484401e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.267208780642102e-10</v>
+        <v>5.089433594027099e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.372912378161296e-10</v>
+        <v>6.208084809695896e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.360282480049937e-10</v>
+        <v>5.365379234034821e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.204635140895649e-10</v>
+        <v>5.086140467648503e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.798294937453539e-10</v>
+        <v>5.10248163586466e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>3.999783541971259e-10</v>
+        <v>5.075385400365319e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.146588325288369e-10</v>
+        <v>7.17605035690605e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.096103517948999e-10</v>
+        <v>7.517185135349234e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.752821129012557e-10</v>
+        <v>5.114005533291938e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.795009534432801e-10</v>
+        <v>4.38065283054869e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.741950785947334e-10</v>
+        <v>5.760890527014793e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.018618017862441e-10</v>
+        <v>4.453160875128955e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.084226256088165e-10</v>
+        <v>6.228647748939107e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.071596357976805e-10</v>
+        <v>4.837492986725748e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.946645370063591e-10</v>
+        <v>4.430253055497128e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.622694291462297e-10</v>
+        <v>4.639595569673039e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.711002760747897e-10</v>
+        <v>4.352515971964956e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>7.957732574643447e-10</v>
+        <v>8.01395861245561e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.833437546358514e-10</v>
+        <v>8.433726159290205e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.577215220124367e-10</v>
+        <v>4.638753133984822e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.275338103591454e-10</v>
+        <v>4.275338103591452e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.214740837733477e-10</v>
+        <v>4.214740837733472e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.390904911166807e-10</v>
+        <v>4.390904911166795e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.224153513886398e-10</v>
+        <v>4.224153513886389e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.224153513886401e-10</v>
+        <v>4.224153513886387e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.353206351815984e-10</v>
+        <v>4.353206351815975e-10</v>
       </c>
       <c r="H4" t="n">
         <v>4.706678573775008e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.231082488173238e-10</v>
+        <v>4.231082488173222e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.627311325072254e-10</v>
+        <v>4.627311325072251e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.335201069801023e-10</v>
+        <v>4.335201069801021e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.679876126447165e-10</v>
+        <v>4.679876126447164e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6179,34 +6179,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.423647043981981e-09</v>
+        <v>1.423647043981997e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.292229446265529e-09</v>
+        <v>1.292229446265528e-09</v>
       </c>
       <c r="D5" t="n">
         <v>1.613630147513432e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.292229483234796e-09</v>
+        <v>1.292229483234795e-09</v>
       </c>
       <c r="F5" t="n">
         <v>1.292229483234796e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.576360193350951e-09</v>
+        <v>1.576360193350949e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.311939046613711e-09</v>
+        <v>2.31193904661371e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.292225205835511e-09</v>
+        <v>1.292225205835508e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.151210694673264e-09</v>
+        <v>2.151210694673271e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.51793121806919e-09</v>
+        <v>1.517931218069198e-09</v>
       </c>
       <c r="L5" t="n">
         <v>2.383390811555883e-09</v>
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.291187562752979e-10</v>
+        <v>8.67100217406579e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.237528890939246e-10</v>
+        <v>5.237528890939233e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.78252715023732e-10</v>
+        <v>8.782527150237286e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.201745490153733e-10</v>
+        <v>5.201745490153726e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.247072123489765e-10</v>
+        <v>5.247072123489764e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.369055810977522e-10</v>
+        <v>8.748870422290308e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.078808861488226e-10</v>
+        <v>5.725459638063395e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.246931947334779e-10</v>
+        <v>8.626746558647552e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.006182482042496e-10</v>
+        <v>9.006182482042471e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.350458284959157e-10</v>
+        <v>5.350458284959155e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.698388979047723e-10</v>
+        <v>5.698388979047721e-10</v>
       </c>
     </row>
     <row r="7">
@@ -6259,34 +6259,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.227368914906126e-09</v>
+        <v>1.227368914906125e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.222947593794323e-09</v>
+        <v>1.222947593794321e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.238893689670076e-09</v>
+        <v>1.238893689670074e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2229893664037e-09</v>
+        <v>1.222989366403696e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2229893664037e-09</v>
+        <v>1.222989366403698e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.235155739728579e-09</v>
+        <v>1.235155739728576e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.270502961924482e-09</v>
+        <v>1.270502961924479e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.222943353364304e-09</v>
+        <v>1.222943353364302e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.262566237054207e-09</v>
+        <v>1.262566237054204e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.233355211527083e-09</v>
+        <v>1.23335521152708e-09</v>
       </c>
       <c r="L7" t="n">
         <v>1.267822717191697e-09</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.166774738593046e-09</v>
+        <v>1.166774738593047e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.694179999603223e-09</v>
+        <v>1.69417999960322e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.820213039588764e-09</v>
+        <v>1.820213039588762e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.548752740024759e-09</v>
+        <v>1.548752740024757e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.179249620649988e-09</v>
+        <v>1.179249620649985e-09</v>
       </c>
       <c r="G8" t="n">
         <v>1.70620371929948e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.74155094149535e-09</v>
+        <v>1.741550941495348e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.693991332935204e-09</v>
+        <v>1.693991332935203e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.733718699612408e-09</v>
+        <v>1.733718699612404e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.162885509217452e-09</v>
+        <v>1.162885509217453e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.294215383842027e-09</v>
+        <v>2.294215383842026e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6342,31 +6342,31 @@
         <v>9.715830291059461e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.14457937107285e-09</v>
+        <v>1.144579371072847e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.16055759122354e-09</v>
+        <v>1.160557591223541e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.349315663091984e-09</v>
+        <v>1.349315663091982e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.144579277160003e-09</v>
+        <v>1.144579277160002e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.156787517007106e-09</v>
+        <v>1.156787517007105e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.192134739203008e-09</v>
+        <v>1.192134739203009e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.144575130642832e-09</v>
+        <v>1.14457513064283e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.184198014332732e-09</v>
+        <v>1.184198014332733e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.052190589853189e-09</v>
+        <v>1.052190589853188e-09</v>
       </c>
       <c r="L9" t="n">
         <v>1.189454494470224e-09</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.268103441221272e-10</v>
+        <v>5.030407382897802e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.046361644717949e-10</v>
+        <v>5.79970908927844e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.014816940029808e-10</v>
+        <v>5.017077417407604e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.352034340197469e-10</v>
+        <v>6.068380239290654e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.415093101454405e-10</v>
+        <v>5.288676176476454e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.136121627065401e-10</v>
+        <v>5.023461442155777e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.13644633103183e-10</v>
+        <v>5.008363530172576e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.080869641925882e-10</v>
+        <v>5.020581179895758e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.046951121277286e-10</v>
+        <v>6.967562081900002e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.057404131809448e-10</v>
+        <v>7.404962812888385e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.171235278696786e-10</v>
+        <v>5.023914619307609e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.997837245606299e-10</v>
+        <v>4.41999234203335e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.73627723516503e-10</v>
+        <v>5.65170172365816e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.706505301095448e-10</v>
+        <v>4.325180610348685e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.053722891979762e-10</v>
+        <v>6.084892679542644e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.116781653236668e-10</v>
+        <v>4.797733068364407e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.846030819376639e-10</v>
+        <v>4.370667157270878e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.839159480782689e-10</v>
+        <v>4.357279872592179e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.782999985817424e-10</v>
+        <v>4.348903151589152e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>7.849092071617877e-10</v>
+        <v>7.757129724151602e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.776961555446031e-10</v>
+        <v>8.31974290903169e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.886486807601876e-10</v>
+        <v>4.385079873158463e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.313430800215613e-10</v>
+        <v>4.313430800215617e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.187686620515196e-10</v>
+        <v>4.187686620515186e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.162862707916762e-10</v>
+        <v>4.162862707916759e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.196224465977831e-10</v>
+        <v>4.196224465977827e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.196224465977832e-10</v>
+        <v>4.196224465977829e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.23448375771986e-10</v>
+        <v>4.234483757719891e-10</v>
       </c>
       <c r="H4" t="n">
         <v>4.235367392853954e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.201382296140032e-10</v>
+        <v>4.201382296140023e-10</v>
       </c>
       <c r="J4" t="n">
         <v>4.599988266344139e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.273156903997937e-10</v>
+        <v>4.273156903997933e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.256257728048422e-10</v>
+        <v>4.256257728048418e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6581,28 +6581,28 @@
         <v>1.32699314626664e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.323638219934589e-09</v>
+        <v>1.32363821993459e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.326993180780897e-09</v>
+        <v>1.326993180780898e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.326993180780897e-09</v>
+        <v>1.326993180780898e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.447161268354518e-09</v>
+        <v>1.447161268354551e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.525457481350748e-09</v>
+        <v>1.525457481350749e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.326990945530431e-09</v>
+        <v>1.32699094553043e-09</v>
       </c>
       <c r="J5" t="n">
         <v>2.096712625601213e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.484966564499678e-09</v>
+        <v>1.484966564499677e-09</v>
       </c>
       <c r="L5" t="n">
         <v>1.687671223747659e-09</v>
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.405735298999203e-10</v>
+        <v>8.405735298999204e-10</v>
       </c>
       <c r="C6" t="n">
         <v>5.154095364753491e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.119255964195136e-10</v>
+        <v>5.119253810231156e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.120411226849392e-10</v>
+        <v>5.120411226849388e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.16101762552681e-10</v>
+        <v>5.161017625526806e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.193790652517787e-10</v>
+        <v>8.326788256503415e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.194998618665696e-10</v>
+        <v>8.305015455429496e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.160689190937952e-10</v>
+        <v>8.293686794923589e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.676799747536748e-10</v>
+        <v>5.652090599531066e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.233088488416443e-10</v>
+        <v>5.233088488416436e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.215764142094144e-10</v>
+        <v>5.215764142094146e-10</v>
       </c>
     </row>
     <row r="7">
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.166555248977801e-09</v>
+        <v>1.166555248977799e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.15535259930645e-09</v>
+        <v>1.155352599306449e-09</v>
       </c>
       <c r="D7" t="n">
         <v>1.15146889126669e-09</v>
@@ -6670,22 +6670,22 @@
         <v>1.155402295133794e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.158660544728226e-09</v>
+        <v>1.158660544728228e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.158748908241635e-09</v>
+        <v>1.158748908241633e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.155350398570241e-09</v>
+        <v>1.155350398570239e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.195210995590651e-09</v>
+        <v>1.19521099559065e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.162527859356032e-09</v>
+        <v>1.16252785935603e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.160837941761081e-09</v>
+        <v>1.16083794176108e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6698,34 +6698,34 @@
         <v>1.097158678241402e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.565567774962157e-09</v>
+        <v>1.565567774962154e-09</v>
       </c>
       <c r="D8" t="n">
         <v>1.660948376653174e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.434420472848039e-09</v>
+        <v>1.43442047284804e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.101200600079933e-09</v>
+        <v>1.101200600079932e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.568696934129465e-09</v>
+        <v>1.568696934129466e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.568785297642864e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.565386787971479e-09</v>
+        <v>1.565386787971477e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.60534160736462e-09</v>
+        <v>1.605341607364621e-09</v>
       </c>
       <c r="K8" t="n">
         <v>1.084225575239298e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.071682147611906e-09</v>
+        <v>2.071682147611908e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.066034689152452e-10</v>
+        <v>9.066034689152456e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.051376502844673e-09</v>
+        <v>1.051376502844674e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.047522550530944e-09</v>
+        <v>1.047522550530946e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.231369223791054e-09</v>
+        <v>1.231369223791055e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.051376431303369e-09</v>
+        <v>1.05137643130337e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.054684448266447e-09</v>
+        <v>1.05468444826645e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.054772811779858e-09</v>
+        <v>1.05477281177986e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.051374302108464e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.091234899128875e-09</v>
+        <v>1.091234899128877e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.64512377876571e-10</v>
+        <v>9.681789264185646e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.056861845299303e-09</v>
+        <v>1.056861845299305e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.510603808697196e-10</v>
+        <v>5.04062320827111e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.116217618820855e-10</v>
+        <v>5.793489475842616e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.214657450403642e-10</v>
+        <v>5.025048139230937e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4195500405379e-10</v>
+        <v>6.059871184887026e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.491114623832958e-10</v>
+        <v>5.287247287214702e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.183523339988228e-10</v>
+        <v>5.023409612837098e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.058714160895533e-10</v>
+        <v>5.001721517728209e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.160574259833042e-10</v>
+        <v>5.022230130347252e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>8.118149176503326e-10</v>
+        <v>7.008030097630796e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.068103953389684e-10</v>
+        <v>7.393645093560258e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>4.304532178606853e-10</v>
+        <v>5.028411880717033e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.270570062814747e-10</v>
+        <v>4.5090432811913e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.81195865160888e-10</v>
+        <v>5.666822422201461e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.930170445673729e-10</v>
+        <v>4.398289257262774e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.127020074456233e-10</v>
+        <v>6.096463158089306e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.198584657751292e-10</v>
+        <v>4.820990539469816e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.894359769284452e-10</v>
+        <v>4.387022103541361e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.743574449884758e-10</v>
+        <v>4.327096918138337e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.869043593594481e-10</v>
+        <v>4.377240895600064e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.077572626633004e-10</v>
+        <v>8.140337890467112e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.784873868371961e-10</v>
+        <v>8.310035744878615e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.033609141577932e-10</v>
+        <v>4.434257783014305e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.46331967305679e-10</v>
+        <v>4.463319673056769e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.240831144037748e-10</v>
+        <v>4.240831144037729e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.287392103362232e-10</v>
+        <v>4.287392103362218e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.249455963140226e-10</v>
+        <v>4.249455963140215e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.249455963140229e-10</v>
+        <v>4.249455963140216e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.268397993092369e-10</v>
+        <v>4.268397993092345e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.19492080582095e-10</v>
+        <v>4.194920805820936e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.254529367543115e-10</v>
+        <v>4.254529367543095e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.252688566638101e-10</v>
+        <v>5.252688566638078e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.292366470506528e-10</v>
+        <v>4.292366470506514e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.341212402597232e-10</v>
+        <v>4.341212402597212e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.799993222714913e-09</v>
+        <v>1.799993222714909e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.404967381216826e-09</v>
+        <v>1.404967381216884e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.509877257152018e-09</v>
+        <v>1.509877257152013e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.404967416010067e-09</v>
+        <v>1.404967416010109e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.404967416010067e-09</v>
+        <v>1.404967416010109e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.499227246330688e-09</v>
+        <v>1.49922724633066e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.469445910456525e-09</v>
+        <v>1.46944591045652e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.404965613884268e-09</v>
+        <v>1.404965613884287e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>3.212787590466567e-09</v>
+        <v>3.212787590466559e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.494187784545349e-09</v>
+        <v>1.494187784545343e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.779353388153896e-09</v>
+        <v>1.77857699850358e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.430102334831531e-10</v>
+        <v>5.430102334831506e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.214229418125878e-10</v>
+        <v>5.214229418125835e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.252921549697313e-10</v>
+        <v>5.252921549697299e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.179819838619111e-10</v>
+        <v>5.179819838619107e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.221242533061909e-10</v>
+        <v>5.221242533061891e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.379643514070911e-10</v>
+        <v>5.23518065486709e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.272794291465998e-10</v>
+        <v>8.272794291465982e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.221312029317863e-10</v>
+        <v>5.221312029317837e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.337002375485961e-10</v>
+        <v>6.315466804749153e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.25818473443774e-10</v>
+        <v>5.25818473443772e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.307915506118056e-10</v>
+        <v>5.307915506118048e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.179723634850729e-09</v>
+        <v>1.179723634850723e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.158846371631958e-09</v>
+        <v>1.158846371631953e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.162101388749746e-09</v>
+        <v>1.162101388749741e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.158894327361773e-09</v>
+        <v>1.158894327361769e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.158894327361773e-09</v>
+        <v>1.158894327361769e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.160231466854287e-09</v>
+        <v>1.160231466854283e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.152883748127146e-09</v>
+        <v>1.152883748127141e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.158844604299363e-09</v>
+        <v>1.158844604299359e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.25866052420886e-09</v>
+        <v>1.258660524208855e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.162628314595703e-09</v>
+        <v>1.162628314595697e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.167512907804774e-09</v>
+        <v>1.167512907804769e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.106575840276249e-09</v>
+        <v>1.106575840276246e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.561821295207199e-09</v>
+        <v>1.561821295207196e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.66362001631889e-09</v>
+        <v>1.663620016318889e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.431627820349043e-09</v>
+        <v>1.431627820349041e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.100831555245667e-09</v>
+        <v>1.100831555245666e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.563030027939691e-09</v>
+        <v>1.563030027939687e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.555682309212562e-09</v>
+        <v>1.55568230921256e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.561643165384767e-09</v>
+        <v>1.561643165384762e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.661552622446544e-09</v>
+        <v>1.661552622446539e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.080639572109342e-09</v>
+        <v>1.08063957210934e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.067477235415012e-09</v>
+        <v>2.067477235415007e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.048444171640152e-10</v>
+        <v>9.048444171640092e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.035334441656477e-09</v>
+        <v>1.035334441656469e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.038619155377048e-09</v>
+        <v>1.03861915537704e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.210009179509138e-09</v>
+        <v>1.21000917950913e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.035334376446434e-09</v>
+        <v>1.035334376446427e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.036719536878807e-09</v>
+        <v>1.036719536878801e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.029371818151664e-09</v>
+        <v>1.029371818151659e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.035332674323883e-09</v>
+        <v>1.035332674323877e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.135148594233381e-09</v>
+        <v>1.135148594233375e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.478554526193033e-10</v>
+        <v>9.478554526192966e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.044000977829294e-09</v>
+        <v>1.044000977829285e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.509519447523739e-10</v>
+        <v>5.205573819045657e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.269630094841247e-10</v>
+        <v>6.083612573827135e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.308921991043552e-10</v>
+        <v>5.247644787169756e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.621779775387284e-10</v>
+        <v>6.392157631032299e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.543094267438893e-10</v>
+        <v>5.494469214583003e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.765414478326569e-10</v>
+        <v>5.219041066268333e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.419205643360481e-10</v>
+        <v>5.291573728649325e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.162047699725546e-10</v>
+        <v>5.18730901688959e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.397854020885398e-10</v>
+        <v>7.415123172914378e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.441711802176062e-10</v>
+        <v>7.685916791508547e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>6.714670997875892e-10</v>
+        <v>5.321601469688772e-10</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.313351177538503e-10</v>
+        <v>4.603450786434501e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.009295347934853e-10</v>
+        <v>5.969794905172364e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2328296983243e-10</v>
+        <v>4.902179839280732e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.373481400813322e-10</v>
+        <v>6.467874091052137e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.294795892864925e-10</v>
+        <v>4.985960193522903e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.607683471457692e-10</v>
+        <v>4.699836437864266e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>7.503314121483779e-10</v>
+        <v>5.307754651824941e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.913421901671222e-10</v>
+        <v>4.47264770057319e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.239175279068606e-10</v>
+        <v>8.324505758375366e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.237900544663304e-10</v>
+        <v>8.683241643824767e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>7.849711577721075e-10</v>
+        <v>5.440484650202901e-10</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.577637651878236e-10</v>
+        <v>4.577637651878232e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.347856337620459e-10</v>
+        <v>4.347856337620447e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.052848590441588e-10</v>
+        <v>5.052848590441573e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.357848514527102e-10</v>
+        <v>4.357848514527088e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.357848514527099e-10</v>
+        <v>4.357848514527089e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.729138214004868e-10</v>
+        <v>4.729138214004832e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.712689120016522e-10</v>
+        <v>5.712689120016473e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.369397139491413e-10</v>
+        <v>4.369397139491392e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.726005662473381e-10</v>
+        <v>4.72600566247337e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.547389875769523e-10</v>
+        <v>4.547389875769508e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.888502164854713e-10</v>
+        <v>5.88850216485471e-10</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.805446129608731e-09</v>
+        <v>1.805446129608729e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.39035489979257e-09</v>
+        <v>1.390354899792565e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.618682040774357e-09</v>
+        <v>2.618682040774353e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.390354945510541e-09</v>
+        <v>1.39035494551054e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.390354945510541e-09</v>
+        <v>1.39035494551054e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.107982651343984e-09</v>
+        <v>2.107982651343971e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.041005463608673e-09</v>
+        <v>4.04100546360863e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.390345188275991e-09</v>
+        <v>1.390345188275987e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.181903670447525e-09</v>
+        <v>2.181903670447524e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.760627376496713e-09</v>
+        <v>1.760627376496709e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.772720923941607e-09</v>
+        <v>1.994829972709163e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.58198195070077e-10</v>
+        <v>5.581981950700767e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.358069630427928e-10</v>
+        <v>5.358069630427927e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>6.07187242723028e-10</v>
+        <v>6.071872427230285e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.321788256134609e-10</v>
+        <v>5.321788256134595e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.373276243913533e-10</v>
+        <v>5.373276243913525e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.170685699440167e-10</v>
+        <v>9.170685699440138e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01353503316435e-09</v>
+        <v>1.013535033164346e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.810944624926707e-10</v>
+        <v>8.810944624926675e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.15146007635253e-10</v>
+        <v>9.151460076352505e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.548337837566883e-10</v>
+        <v>5.54833783756687e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.902000285948351e-10</v>
+        <v>6.902000285948343e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.271404615894384e-09</v>
+        <v>1.271404615894382e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.250590276172281e-09</v>
+        <v>1.25059027617228e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.318893680077388e-09</v>
+        <v>1.318893680077386e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.250565633700203e-09</v>
+        <v>1.2505656337002e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.250565633700203e-09</v>
+        <v>1.2505656337002e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.286554672107048e-09</v>
+        <v>1.286554672107045e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.384909762708212e-09</v>
+        <v>1.38490976270821e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.250580564655702e-09</v>
+        <v>1.2505805646557e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.286241416953898e-09</v>
+        <v>1.286241416953896e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.268379838283513e-09</v>
+        <v>1.268379838283511e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.402491067192032e-09</v>
+        <v>1.402491067192031e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.222075540524941e-09</v>
+        <v>1.222075540524938e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.75162567179541e-09</v>
+        <v>1.751625671794546e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.933932202035211e-09</v>
+        <v>1.933932202035208e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.601118464240683e-09</v>
+        <v>1.60111846424068e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.218707377028254e-09</v>
+        <v>1.218707377028252e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.787465364137078e-09</v>
+        <v>1.787465364137075e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.885820454738223e-09</v>
+        <v>1.885820454738218e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.751491256685732e-09</v>
+        <v>1.75149125668573e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.787260246939103e-09</v>
+        <v>1.787260246939098e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.208829776735181e-09</v>
+        <v>1.208829776735177e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.478173206640514e-09</v>
+        <v>2.478173206640511e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7527,22 +7527,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.024325934349066e-09</v>
+        <v>1.024325934349065e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.18831654158465e-09</v>
+        <v>1.188316541584647e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25665218681984e-09</v>
+        <v>1.256652186819839e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.401577569899605e-09</v>
+        <v>1.401577569899599e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.188316428080499e-09</v>
+        <v>1.188316428080498e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.224280937519417e-09</v>
+        <v>1.224280937519414e-09</v>
       </c>
       <c r="H9" t="n">
         <v>1.32263602812058e-09</v>
@@ -7551,13 +7551,13 @@
         <v>1.18830683006807e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.223967682366267e-09</v>
+        <v>1.223967682366261e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.099029480665595e-09</v>
+        <v>1.099029480665594e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3402173326044e-09</v>
+        <v>1.340217332604397e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.12581240283544e-10</v>
+        <v>5.129913486377052e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.171280525111502e-10</v>
+        <v>5.990313963087131e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.973948945895414e-10</v>
+        <v>5.174549228103437e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.509358257162292e-10</v>
+        <v>6.286575113397267e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>4.473891241766595e-10</v>
+        <v>5.424860670502525e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>4.478826354581442e-10</v>
+        <v>5.148491909515258e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>4.482556035498235e-10</v>
+        <v>5.13339067990868e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.106262029769939e-10</v>
+        <v>5.128909035444515e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.278526458622082e-10</v>
+        <v>7.272837986538202e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.075736361755958e-10</v>
+        <v>7.575674043764682e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.77793028874742e-10</v>
+        <v>5.216376104977894e-10</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.852925319112176e-10</v>
+        <v>4.429199190858063e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.883466827597728e-10</v>
+        <v>5.860042911111655e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.828458034586744e-10</v>
+        <v>4.745401425899426e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.233604340734245e-10</v>
+        <v>6.338284616167097e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.198137325338558e-10</v>
+        <v>4.91575220477797e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.258964490239887e-10</v>
+        <v>4.561387426949276e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.25614820469588e-10</v>
+        <v>4.549573624995391e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.831765918913982e-10</v>
+        <v>4.420940965449146e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.098355319480014e-10</v>
+        <v>8.145793299395391e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.804711326038433e-10</v>
+        <v>8.469675431137283e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.753211759385699e-10</v>
+        <v>5.054569925450648e-10</v>
       </c>
     </row>
     <row r="4">
@@ -7723,28 +7723,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.271487386801892e-10</v>
+        <v>4.271487386801881e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.241670281305923e-10</v>
+        <v>4.241670281305918e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.775668623057117e-10</v>
+        <v>4.775668623057121e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.250710399260322e-10</v>
+        <v>4.25071039926033e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.250710399260323e-10</v>
+        <v>4.250710399260326e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.480790975693557e-10</v>
+        <v>4.48079097569355e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.483760303838724e-10</v>
+        <v>4.483760303838718e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.258682871569491e-10</v>
+        <v>4.25868287156949e-10</v>
       </c>
       <c r="J4" t="n">
         <v>4.638418658546784e-10</v>
@@ -7753,7 +7753,7 @@
         <v>4.278856600866221e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.253735275135057e-10</v>
+        <v>5.253735275135043e-10</v>
       </c>
     </row>
     <row r="5">
@@ -7766,34 +7766,34 @@
         <v>1.369831786069333e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.293169775769833e-09</v>
+        <v>1.293169775769829e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.138984912427588e-09</v>
+        <v>2.138984912427566e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.293169815333557e-09</v>
+        <v>1.293169815333556e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.293169815333557e-09</v>
+        <v>1.293169815333556e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.719848205624215e-09</v>
+        <v>1.719848205624224e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.826379314238954e-09</v>
+        <v>1.826379314238955e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.293163241471174e-09</v>
+        <v>1.293163241471173e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.074837605069708e-09</v>
+        <v>2.074837605069707e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.368425750581005e-09</v>
+        <v>1.368425750581006e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.737968435087287e-09</v>
+        <v>3.378293942536025e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.390256423356989e-10</v>
+        <v>8.390256423356986e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.183941427065008e-10</v>
+        <v>5.183941427065024e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.723122471924039e-10</v>
+        <v>5.72312036234103e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.150051638760872e-10</v>
+        <v>5.15005163876086e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.194776228474632e-10</v>
+        <v>5.19477622847461e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.416896364925654e-10</v>
+        <v>8.599560012248671e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.579436537656807e-10</v>
+        <v>8.579436537656796e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.377451908124574e-10</v>
+        <v>8.377451908124564e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.668615907476419e-10</v>
+        <v>5.668615907476386e-10</v>
       </c>
       <c r="K6" t="n">
         <v>5.209964626121306e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.1954041923731e-10</v>
+        <v>6.195404192373086e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.178360724202157e-09</v>
+        <v>1.178360724202156e-09</v>
       </c>
       <c r="C7" t="n">
         <v>1.177086806977574e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.228749081579107e-09</v>
+        <v>1.228749081579104e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.177106098928703e-09</v>
+        <v>1.177106098928702e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.177106098928703e-09</v>
+        <v>1.177106098928702e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.199291083091324e-09</v>
+        <v>1.199291083091322e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.199588015905841e-09</v>
+        <v>1.19958801590584e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.177080272678917e-09</v>
+        <v>1.177080272678916e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.215053851376646e-09</v>
+        <v>1.215053851376645e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.179097645608591e-09</v>
+        <v>1.179097645608589e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.276585513035473e-09</v>
+        <v>1.276585513035471e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.122959578408213e-09</v>
+        <v>1.122959578408212e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.623341831332293e-09</v>
+        <v>1.623341831332291e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.778869242654425e-09</v>
+        <v>1.778869242654424e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.486161442414931e-09</v>
+        <v>1.486161442414928e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.13761177737524e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.645391799752557e-09</v>
+        <v>1.645391799752556e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.645688732567047e-09</v>
+        <v>1.645688732567042e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.623180989340152e-09</v>
+        <v>1.62318098934015e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.661253127587616e-09</v>
+        <v>1.661253127587614e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.114380845243099e-09</v>
+        <v>1.114380845243098e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2465468599936e-09</v>
+        <v>2.246546859993595e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7923,34 +7923,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.217689736338696e-10</v>
+        <v>9.217689736338658e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.083135029269777e-09</v>
+        <v>1.08313502926978e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.134827283740239e-09</v>
+        <v>1.134827283740238e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.27081819596648e-09</v>
+        <v>1.270818195966479e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.083134951927974e-09</v>
+        <v>1.083134951927973e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.105339305383526e-09</v>
+        <v>1.105339305383524e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.105636238198044e-09</v>
+        <v>1.105636238198042e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.08312849497112e-09</v>
+        <v>1.083128494971118e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.121102073668851e-09</v>
+        <v>1.121102073668848e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>8.803530555711634e-10</v>
+        <v>9.909117187368764e-10</v>
       </c>
       <c r="L9" t="n">
         <v>1.182633735327676e-09</v>

--- a/Results/Ammonia/ammonia human toxicity carcinogenic results.xlsx
+++ b/Results/Ammonia/ammonia human toxicity carcinogenic results.xlsx
@@ -515,34 +515,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.458331570201232e-10</v>
+        <v>5.458331570201235e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>6.500517131178855e-10</v>
+        <v>6.500517131178856e-10</v>
       </c>
       <c r="D2" t="n">
         <v>5.474202923602853e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.864379671662867e-10</v>
+        <v>6.86437967166286e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.801619304409469e-10</v>
+        <v>5.801619304409471e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.449763756304533e-10</v>
+        <v>5.449763756304534e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.526548885404812e-10</v>
+        <v>5.526548885404817e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.422266824126871e-10</v>
+        <v>5.422266824126868e-10</v>
       </c>
       <c r="J2" t="n">
         <v>8.068605038159237e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>8.078412891299867e-10</v>
+        <v>8.078412891299865e-10</v>
       </c>
       <c r="L2" t="n">
         <v>5.571483221741775e-10</v>
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.015801141282879e-10</v>
+        <v>5.015801141282883e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.556599065993364e-10</v>
+        <v>6.556599065993367e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.129518675344799e-10</v>
+        <v>5.129518675344796e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>7.145321654875356e-10</v>
+        <v>7.145321654875358e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.390927137599746e-10</v>
+        <v>5.390927137599749e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.956196857060929e-10</v>
+        <v>4.956196857060933e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.600262093597187e-10</v>
+        <v>5.600262093597198e-10</v>
       </c>
       <c r="I3" t="n">
         <v>4.758449901555856e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.318932021821864e-10</v>
+        <v>9.318932021821866e-10</v>
       </c>
       <c r="K3" t="n">
         <v>9.215521948879172e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.832757602236174e-10</v>
+        <v>5.832757602236179e-10</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.238148682585903e-10</v>
+        <v>5.238148682585899e-10</v>
       </c>
       <c r="C4" t="n">
         <v>4.805965590888617e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.417422920440489e-10</v>
+        <v>5.417422920440482e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.81728065289641e-10</v>
+        <v>4.817280652896409e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.81728065289641e-10</v>
+        <v>4.817280652896408e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.140897547850402e-10</v>
+        <v>5.140897547850398e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>6.174840269164069e-10</v>
+        <v>6.174840269164086e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.829819866862337e-10</v>
+        <v>4.829819866862336e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.22136804229265e-10</v>
+        <v>5.221368042292651e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.978009448117728e-10</v>
+        <v>4.978009448117732e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>6.513328288842879e-10</v>
+        <v>6.513328288842878e-10</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.623241424266033e-09</v>
+        <v>2.623241424266035e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.805456489068291e-09</v>
+        <v>1.805456489068293e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>3.010584547568585e-09</v>
+        <v>3.010584547568581e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.805456537895784e-09</v>
+        <v>1.805456537895793e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.805456537895784e-09</v>
+        <v>1.805456537895793e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.520110264442807e-09</v>
+        <v>2.52011026444279e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.944619915619117e-09</v>
+        <v>4.944619915619145e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.805447838187818e-09</v>
+        <v>1.805447838187824e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.740844929726696e-09</v>
+        <v>2.740844929726699e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.167743964283841e-09</v>
+        <v>2.167743964283845e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.843428216767569e-09</v>
+        <v>5.843428216767586e-09</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.250762265323212e-10</v>
+        <v>6.250762265323216e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.82685760008254e-10</v>
+        <v>5.82685760008255e-10</v>
       </c>
       <c r="D6" t="n">
         <v>6.442574047926907e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.786392654081811e-10</v>
+        <v>5.786392654081805e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.842620336795677e-10</v>
+        <v>5.842620336795696e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.933266319395284e-10</v>
+        <v>9.933266319395293e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>1.093923665115467e-09</v>
+        <v>1.093923665115469e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>9.622188638407242e-10</v>
+        <v>9.622188638407234e-10</v>
       </c>
       <c r="J6" t="n">
         <v>9.987606572510656e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.987414339717548e-10</v>
+        <v>5.987414339717562e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>7.537489603004618e-10</v>
+        <v>7.537489603004619e-10</v>
       </c>
     </row>
     <row r="7">
@@ -715,34 +715,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.433317373804776e-09</v>
+        <v>1.433317373804778e-09</v>
       </c>
       <c r="C7" t="n">
         <v>1.392493143112889e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.451210076829724e-09</v>
+        <v>1.451210076829723e-09</v>
       </c>
       <c r="E7" t="n">
         <v>1.392443537495807e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.392443537495808e-09</v>
+        <v>1.392443537495807e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.423592260331227e-09</v>
+        <v>1.423592260331226e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.526986532462593e-09</v>
+        <v>1.526986532462595e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.392484492232421e-09</v>
+        <v>1.392484492232419e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.431639309775451e-09</v>
+        <v>1.431639309775453e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.40730345035796e-09</v>
+        <v>1.407303450357958e-09</v>
       </c>
       <c r="L7" t="n">
         <v>1.560835334430475e-09</v>
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.41170935224068e-09</v>
+        <v>1.411709352240681e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>2.012174057114199e-09</v>
+        <v>2.012174057114203e-09</v>
       </c>
       <c r="D8" t="n">
         <v>2.203753788877377e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.836798711641032e-09</v>
+        <v>1.836798711641034e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.391200261814392e-09</v>
+        <v>1.391200261814394e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>2.043151121635336e-09</v>
+        <v>2.04315112163534e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>2.146545393766702e-09</v>
+        <v>2.146545393766706e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>2.012043353536532e-09</v>
+        <v>2.012043353536534e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>2.05132417883583e-09</v>
+        <v>2.051324178835831e-09</v>
       </c>
       <c r="K8" t="n">
         <v>1.373785424761607e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.850146618478154e-09</v>
+        <v>2.850146618478157e-09</v>
       </c>
     </row>
     <row r="9">
@@ -801,31 +801,31 @@
         <v>1.38518864225655e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.443940529218488e-09</v>
+        <v>1.443940529218486e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.641037867398149e-09</v>
+        <v>1.64103786739815e-09</v>
       </c>
       <c r="F9" t="n">
         <v>1.38518850494342e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.416287759474886e-09</v>
+        <v>1.416287759474885e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.519682031606253e-09</v>
+        <v>1.519682031606254e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.385179991376079e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.42433480891911e-09</v>
+        <v>1.424334808919111e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.120825813275108e-09</v>
+        <v>1.120825813275107e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.553530833574134e-09</v>
+        <v>1.553530833574133e-09</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.09547564390489e-10</v>
+        <v>5.095475643904888e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.950518875789506e-10</v>
+        <v>5.950518875789512e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.102634016212172e-10</v>
+        <v>5.10263401621217e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.240783036714361e-10</v>
+        <v>6.240783036714356e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.396856036039103e-10</v>
+        <v>5.396856036039102e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.102378922421174e-10</v>
+        <v>5.10237892242118e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.087069772761523e-10</v>
+        <v>5.087069772761525e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.101768301253612e-10</v>
+        <v>5.10176830125361e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.239662578104578e-10</v>
+        <v>7.239662578104584e-10</v>
       </c>
       <c r="K2" t="n">
         <v>7.532560271631229e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.110318704585669e-10</v>
+        <v>5.110318704585636e-10</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.398023516595449e-10</v>
+        <v>4.398023516595447e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.859538487426847e-10</v>
+        <v>5.859538487426849e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.44886144610728e-10</v>
+        <v>4.448861446107273e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.328201328034477e-10</v>
+        <v>6.328201328034476e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.935030324055037e-10</v>
+        <v>4.935030324055034e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.447438184603756e-10</v>
+        <v>4.447438184603755e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.433478045429574e-10</v>
+        <v>4.433478045429576e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.441644713297196e-10</v>
+        <v>4.441644713297197e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.322570529434547e-10</v>
+        <v>8.322570529434553e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.441205234601276e-10</v>
+        <v>8.441205234601294e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.515339297240079e-10</v>
+        <v>4.515339297240068e-10</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.252029257873929e-10</v>
+        <v>4.252029257873921e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.309355339678325e-10</v>
+        <v>4.309355339678322e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.332886366098655e-10</v>
+        <v>4.332886366098652e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.318124985401524e-10</v>
+        <v>4.318124985401516e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.318124985401511e-10</v>
+        <v>4.318124985401516e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.329577941776617e-10</v>
+        <v>4.329577941776609e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.32883963023059e-10</v>
+        <v>4.328839630230586e-10</v>
       </c>
       <c r="I4" t="n">
         <v>4.322469382619562e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.042985232147136e-10</v>
+        <v>5.042985232147128e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.294955626012763e-10</v>
+        <v>4.294955626012757e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.434581944011913e-10</v>
+        <v>4.434581944011909e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1034,34 +1034,34 @@
         <v>1.35161207104533e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.410422572966626e-09</v>
+        <v>1.410422572966629e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.48157591347745e-09</v>
+        <v>1.481575913477452e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.410422606180489e-09</v>
+        <v>1.410422606180487e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.410422606180489e-09</v>
+        <v>1.410422606180487e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.497028924581886e-09</v>
+        <v>1.497028924581895e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.597730958084376e-09</v>
+        <v>1.597730958084377e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.410420958339444e-09</v>
+        <v>1.410420958339448e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.802126694995782e-09</v>
+        <v>2.802126694995772e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.400453608743029e-09</v>
+        <v>1.400453608743028e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.844888546091614e-09</v>
+        <v>1.844888546091611e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.192313377582666e-10</v>
+        <v>5.192313377582664e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.257898850654905e-10</v>
+        <v>5.257898850654903e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.431330430785955e-10</v>
+        <v>8.431330430785957e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.223466210435263e-10</v>
+        <v>5.223466210435279e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.263931409590943e-10</v>
+        <v>5.263931409590951e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.427295223500594e-10</v>
+        <v>8.427295223500584e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.408289281378227e-10</v>
+        <v>8.408289281378233e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.26275350232831e-10</v>
+        <v>5.262753502328311e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>6.079665369064059e-10</v>
+        <v>6.079665369064049e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.234141160714967e-10</v>
+        <v>5.234141160714965e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.376141243288915e-10</v>
+        <v>5.376141243288907e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.172776581833373e-09</v>
+        <v>1.172776581833372e-09</v>
       </c>
       <c r="C7" t="n">
         <v>1.17982220893512e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.18083257554488e-09</v>
+        <v>1.180832575544879e-09</v>
       </c>
       <c r="E7" t="n">
         <v>1.179888636114034e-09</v>
@@ -1126,22 +1126,22 @@
         <v>1.179888636114034e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.180531450223643e-09</v>
+        <v>1.180531450223644e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.18045761906904e-09</v>
+        <v>1.180457619069039e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.17982059430794e-09</v>
+        <v>1.179820594307937e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.251872179260696e-09</v>
+        <v>1.251872179260694e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.17706921864726e-09</v>
+        <v>1.177069218647259e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.191031850447172e-09</v>
+        <v>1.191031850447171e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.111844610621289e-09</v>
+        <v>1.11184461062129e-09</v>
       </c>
       <c r="C8" t="n">
         <v>1.614292464512998e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.717818256982115e-09</v>
+        <v>1.717818256982117e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.478829800778165e-09</v>
+        <v>1.478829800778166e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.134644812182756e-09</v>
+        <v>1.134644812182755e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.614803611681496e-09</v>
+        <v>1.614803611681498e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.614729780526871e-09</v>
+        <v>1.614729780526872e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.614092755765792e-09</v>
+        <v>1.614092755765793e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.686241662581377e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.106938576427895e-09</v>
+        <v>1.106938576427897e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.142586136831176e-09</v>
+        <v>2.142586136831179e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.96055735716897e-10</v>
+        <v>8.96055735716896e-10</v>
       </c>
       <c r="C9" t="n">
         <v>1.058963005625054e-09</v>
@@ -1203,13 +1203,13 @@
         <v>1.238824121713699e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.058962929436195e-09</v>
+        <v>1.058962929436196e-09</v>
       </c>
       <c r="G9" t="n">
         <v>1.059672246913577e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.059598415758973e-09</v>
+        <v>1.059598415758974e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.058961390997873e-09</v>
@@ -1218,10 +1218,10 @@
         <v>1.131012975950629e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.659032551436214e-10</v>
+        <v>9.659032551436203e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.070172647137106e-09</v>
+        <v>1.070172647137105e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.204180772961409e-10</v>
+        <v>6.204180772961434e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.498592208993744e-10</v>
+        <v>5.498592208993746e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>6.241543140027056e-10</v>
+        <v>6.241543140027067e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.814061388188546e-10</v>
+        <v>5.814061388188548e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.814236389791244e-10</v>
+        <v>5.814236389791269e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>6.220803731653219e-10</v>
+        <v>6.220803731653208e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.250677100601028e-10</v>
+        <v>6.250677100601029e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>6.212054422520144e-10</v>
+        <v>6.212054422520146e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.62178897889242e-10</v>
+        <v>6.621788978892459e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.788455878773268e-10</v>
+        <v>7.788455878773262e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>6.227613786588885e-10</v>
+        <v>6.227613786588893e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.129096948274196e-10</v>
+        <v>6.129096948274221e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.072504567782309e-10</v>
+        <v>5.072504567782308e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.401594484293977e-10</v>
+        <v>6.401594484294001e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.541206513651835e-10</v>
+        <v>5.541206513651844e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.541381515254593e-10</v>
+        <v>5.541381515254561e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.25441889867409e-10</v>
+        <v>6.254418898674099e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.564103249802173e-10</v>
+        <v>6.564103249802191e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.191768395431703e-10</v>
+        <v>6.191768395431726e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.961070277048404e-10</v>
+        <v>6.96107027704839e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.80827873746869e-10</v>
+        <v>8.808278737468682e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.314189889666906e-10</v>
+        <v>6.314189889666902e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.535477419274294e-10</v>
+        <v>4.53547741927429e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.661771984239933e-10</v>
+        <v>4.661771984239943e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.95750254281857e-10</v>
+        <v>4.957502542818565e-10</v>
       </c>
       <c r="E4" t="n">
+        <v>4.612784783360244e-10</v>
+      </c>
+      <c r="F4" t="n">
         <v>4.612784783360241e-10</v>
       </c>
-      <c r="F4" t="n">
-        <v>4.612784783360242e-10</v>
-      </c>
       <c r="G4" t="n">
-        <v>4.722817010914572e-10</v>
+        <v>4.722817010914571e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.23120580955106e-10</v>
+        <v>5.231205809551077e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.623829301132816e-10</v>
+        <v>4.623829301132822e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.814012294168938e-10</v>
+        <v>4.814012294168933e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.654310004158356e-10</v>
+        <v>4.654310004158357e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.814723868425653e-10</v>
+        <v>4.814723868425649e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.105810409225165e-09</v>
+        <v>1.105810409225167e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.729076810238208e-09</v>
+        <v>1.729076810238211e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.211051722894197e-09</v>
+        <v>2.211051722894184e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.625694348294698e-09</v>
+        <v>1.625694348294716e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.625694348294698e-09</v>
+        <v>1.625694348294718e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.820980526876724e-09</v>
+        <v>1.82098052687672e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.975919059273831e-09</v>
+        <v>2.975919059273865e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.62569057278246e-09</v>
+        <v>1.625690572782496e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.026292696290814e-09</v>
+        <v>2.026292696290816e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.673210673887477e-09</v>
+        <v>1.673210673887481e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.169518909931739e-09</v>
+        <v>2.169518909931742e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.840413007591853e-10</v>
+        <v>8.840413007591874e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.605028157553546e-10</v>
+        <v>5.60502815755355e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.873177474085708e-10</v>
+        <v>5.873177474085714e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.485839777808308e-10</v>
+        <v>5.485839777808326e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.530028487174204e-10</v>
+        <v>5.530028487174209e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.62823217588163e-10</v>
+        <v>5.628232175881627e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.619019681697711e-10</v>
+        <v>9.619019681697717e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.52924446609987e-10</v>
+        <v>5.529244466099885e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.171380345648493e-10</v>
+        <v>9.171380345648486e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.560469706525135e-10</v>
+        <v>5.560469706525134e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.722132046925754e-10</v>
+        <v>5.72213204692575e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1513,25 +1513,25 @@
         <v>1.308347633846976e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.333533630215638e-09</v>
+        <v>1.333533630215637e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.300195320098389e-09</v>
+        <v>1.30019532009839e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.300195320098389e-09</v>
+        <v>1.300195320098391e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.310096275992966e-09</v>
+        <v>1.310096275992968e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.360935155856616e-09</v>
+        <v>1.360935155856619e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.300197505014793e-09</v>
+        <v>1.300197505014792e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.319215804318402e-09</v>
+        <v>1.319215804318405e-09</v>
       </c>
       <c r="K7" t="n">
         <v>1.303245575317344e-09</v>
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.270576458720255e-09</v>
+        <v>1.270576458720253e-09</v>
       </c>
       <c r="C8" t="n">
         <v>1.878607032147321e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>2.026200744328735e-09</v>
+        <v>2.026200744328738e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.708831991623039e-09</v>
+        <v>1.708831991623038e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.298160959682151e-09</v>
+        <v>1.298160959682154e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.880206118318814e-09</v>
+        <v>1.880206118318812e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.931044998182725e-09</v>
+        <v>1.931044998182728e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.870307347340637e-09</v>
+        <v>1.870307347340636e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.88944177466416e-09</v>
+        <v>1.889441774664163e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.271483526199605e-09</v>
+        <v>1.271483526199602e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.506636773147634e-09</v>
+        <v>2.50663677314763e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1587,25 +1587,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.036055373240627e-09</v>
+        <v>1.036055373240628e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.245371924891822e-09</v>
+        <v>1.245371924891823e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.270589344408561e-09</v>
+        <v>1.270589344408562e-09</v>
       </c>
       <c r="E9" t="n">
         <v>1.459171756807761e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.237225424288481e-09</v>
+        <v>1.237225424288485e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.247120567037812e-09</v>
+        <v>1.247120567037816e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.297959446901461e-09</v>
+        <v>1.297959446901464e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.237221796059641e-09</v>
@@ -1614,10 +1614,10 @@
         <v>1.256240095363251e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.128832487962097e-09</v>
+        <v>1.1288324879621e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.256311252788922e-09</v>
+        <v>1.256311252788923e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.115668995172483e-10</v>
+        <v>6.115668995172495e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.491601878476645e-10</v>
+        <v>5.491601878476623e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>6.148940359894594e-10</v>
+        <v>6.148940359894596e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.816687158526213e-10</v>
+        <v>5.816687158526235e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.816862165485119e-10</v>
+        <v>5.816862165485122e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>6.130724159611236e-10</v>
+        <v>6.130724159611257e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.139936150196035e-10</v>
+        <v>6.139936150196018e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>6.128935959580455e-10</v>
+        <v>6.128935959580449e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.614375733860238e-10</v>
+        <v>6.614375733860204e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7769207118308e-10</v>
+        <v>7.77692071183069e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>6.126253129363988e-10</v>
+        <v>6.126253129363957e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.944375622187458e-10</v>
+        <v>5.944375622187448e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.023450056974386e-10</v>
+        <v>5.023450056974379e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.187824881721705e-10</v>
+        <v>6.187824881721707e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.536511394881681e-10</v>
+        <v>5.536511394881703e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.536686401840591e-10</v>
+        <v>5.536686401840622e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.058521007673716e-10</v>
+        <v>6.058521007673613e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.220884565241726e-10</v>
+        <v>6.22088456524169e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.045537844251605e-10</v>
+        <v>6.045537844251576e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.871020939395449e-10</v>
+        <v>6.871020939395447e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.733578986141928e-10</v>
+        <v>8.733578986141796e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.037735870548589e-10</v>
+        <v>6.037735870548553e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.414013407440048e-10</v>
+        <v>4.414013407440037e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.543111378998172e-10</v>
+        <v>4.543111378998158e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.789828777559953e-10</v>
+        <v>4.789828777559944e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.55692402922644e-10</v>
+        <v>4.556924029226431e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.556924029226442e-10</v>
+        <v>4.556924029226431e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.583694872237296e-10</v>
+        <v>4.583694872237304e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.860727451892687e-10</v>
+        <v>4.860727451892671e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.563630113282907e-10</v>
+        <v>4.563630113282895e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.612020037550788e-10</v>
+        <v>4.612020037550773e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.497513894688379e-10</v>
+        <v>4.497513894688375e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.549620758246483e-10</v>
+        <v>4.549620758246466e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.119157682288389e-10</v>
+        <v>9.119157682288372e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.508108011365713e-09</v>
+        <v>1.508108011365703e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.88701715496704e-09</v>
+        <v>1.887017154967042e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.512502345913245e-09</v>
+        <v>1.512502345913242e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.512502345913245e-09</v>
+        <v>1.512502345913242e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.559648184930269e-09</v>
+        <v>1.559648184930127e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.196031681376194e-09</v>
+        <v>2.196031681376174e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.512500377301206e-09</v>
+        <v>1.512500377301199e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.638555838651008e-09</v>
+        <v>1.638555838651004e-09</v>
       </c>
       <c r="K5" t="n">
         <v>1.393642455337007e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.623236524137239e-09</v>
+        <v>1.623236524137238e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.48513604509483e-10</v>
+        <v>8.4851360450948e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.420203089688712e-10</v>
+        <v>5.420203089688713e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.924838028056787e-10</v>
+        <v>8.924838028056734e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.364190729370638e-10</v>
+        <v>5.364190729370647e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.404574243706612e-10</v>
+        <v>5.404574243706568e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.654817509892058e-10</v>
+        <v>8.654817509892065e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.023986922089474e-10</v>
+        <v>9.023986922089406e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.403126102177782e-10</v>
+        <v>5.403126102177752e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.548014592994195e-10</v>
+        <v>5.548014592994194e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.336725847688678e-10</v>
+        <v>5.336725847688666e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.390060303203027e-10</v>
+        <v>5.390060303203043e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.238594283690473e-09</v>
+        <v>1.238594283690469e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.255822791375643e-09</v>
+        <v>1.255822791375641e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.276146312813617e-09</v>
+        <v>1.276146312813615e-09</v>
       </c>
       <c r="E7" t="n">
         <v>1.253646719412887e-09</v>
@@ -1918,22 +1918,22 @@
         <v>1.253646719412887e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.255562430170202e-09</v>
+        <v>1.255562430170198e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.283265688135738e-09</v>
+        <v>1.283265688135732e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.25355595427476e-09</v>
+        <v>1.253555954274757e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.258394946701546e-09</v>
+        <v>1.258394946701544e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.246944332415306e-09</v>
+        <v>1.246944332415304e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.252155018771115e-09</v>
+        <v>1.252155018771112e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1946,34 +1946,34 @@
         <v>1.219813974618957e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.801135920813847e-09</v>
+        <v>1.801135920813844e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.93817645251609e-09</v>
+        <v>1.938176452516084e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.644627837254706e-09</v>
+        <v>1.644627837254704e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.252721702980429e-09</v>
+        <v>1.252721702980425e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.800642863773208e-09</v>
+        <v>1.800642863773205e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82834612173944e-09</v>
+        <v>1.828346121739435e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.798636387877763e-09</v>
+        <v>1.798636387877762e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.803586195171176e-09</v>
+        <v>1.80358619517117e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.217690020555514e-09</v>
+        <v>1.21769002055551e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.386235147437322e-09</v>
+        <v>2.386235147437314e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.680745672867196e-10</v>
+        <v>9.680745672867122e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.161105441533319e-09</v>
+        <v>1.161105441533321e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.181458687254599e-09</v>
+        <v>1.181458687254593e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.361712808797311e-09</v>
+        <v>1.361712808797301e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.158840442434193e-09</v>
+        <v>1.158840442434185e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.160845080327877e-09</v>
+        <v>1.160845080327867e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.188548338293415e-09</v>
+        <v>1.188548338293407e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.158838604432436e-09</v>
+        <v>1.158838604432431e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.163677596859223e-09</v>
+        <v>1.16367759685922e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.050366491972805e-09</v>
+        <v>1.050366491972799e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.157437668928796e-09</v>
+        <v>1.15743766892879e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.008511086807007e-10</v>
+        <v>6.008511086807e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.454427840045617e-10</v>
+        <v>5.454427840045614e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>6.035932346274077e-10</v>
+        <v>6.035932346274079e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.782194539715901e-10</v>
+        <v>5.782194539715915e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.782369767789485e-10</v>
+        <v>5.782369767789482e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>6.021272644470812e-10</v>
+        <v>6.021272644470815e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.019486773483912e-10</v>
+        <v>6.019486773483918e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>6.023738205095123e-10</v>
+        <v>6.023738205095101e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.560553154326765e-10</v>
+        <v>6.56055315432674e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.733009986060295e-10</v>
+        <v>7.733009986060282e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>6.020002990862704e-10</v>
+        <v>6.020002990862714e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.772807073075256e-10</v>
+        <v>5.772807073075262e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.951101157872614e-10</v>
+        <v>4.951101157872616e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.974629150700279e-10</v>
+        <v>5.974629150700281e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.495646049889905e-10</v>
+        <v>5.495646049889868e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.495821277963483e-10</v>
+        <v>5.495821277963444e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.870593663864304e-10</v>
+        <v>5.870593663864272e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.954474904613101e-10</v>
+        <v>5.954474904613099e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.88796147471276e-10</v>
+        <v>5.887961474712755e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.727949159506479e-10</v>
+        <v>6.727949159506497e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.659304201064997e-10</v>
+        <v>8.659304201064901e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.872149380788399e-10</v>
+        <v>5.8721493807884e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2179,34 +2179,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.364471474550996e-10</v>
+        <v>4.364471474551003e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.456884567851681e-10</v>
+        <v>4.45688456785169e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.674207214634309e-10</v>
+        <v>4.674207214634312e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.531770160268973e-10</v>
+        <v>4.531770160268978e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.531770160268976e-10</v>
+        <v>4.531770160268979e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.508265624548812e-10</v>
+        <v>4.508265624548804e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.662092733502733e-10</v>
+        <v>4.662092733502743e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.536369671219551e-10</v>
+        <v>4.536369671219556e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.44002687559085e-10</v>
+        <v>4.440026875590854e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.433236443892264e-10</v>
+        <v>4.433236443892259e-10</v>
       </c>
       <c r="L4" t="n">
         <v>4.50964069940165e-10</v>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.420208495764624e-10</v>
+        <v>8.420208495764633e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.380183923786099e-09</v>
+        <v>1.380183923786098e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.706743428480337e-09</v>
+        <v>1.706743428480334e-09</v>
       </c>
       <c r="E5" t="n">
         <v>1.481907796626238e-09</v>
@@ -2234,13 +2234,13 @@
         <v>1.481907796626238e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.444493083318833e-09</v>
+        <v>1.444493083318832e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.834221945665706e-09</v>
+        <v>1.83422194566571e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.481906922981956e-09</v>
+        <v>1.481906922981955e-09</v>
       </c>
       <c r="J5" t="n">
         <v>1.34863233914075e-09</v>
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.207845604094052e-10</v>
+        <v>5.207845604094062e-10</v>
       </c>
       <c r="C6" t="n">
         <v>5.339773297454537e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.524306213115155e-10</v>
+        <v>5.524306213115136e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.341997555849339e-10</v>
+        <v>5.341997555849358e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.381537795060464e-10</v>
+        <v>5.381537795060472e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.578973298185413e-10</v>
+        <v>8.578973298185399e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.836068751054072e-10</v>
+        <v>8.836068751054095e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.607077344856136e-10</v>
+        <v>8.607077344856142e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.564925232401787e-10</v>
+        <v>8.564925232401807e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.276231721850276e-10</v>
+        <v>5.276231721850093e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.353868083682506e-10</v>
+        <v>5.353868083682525e-10</v>
       </c>
     </row>
     <row r="7">
@@ -2305,7 +2305,7 @@
         <v>1.244790937552115e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.261858798140739e-09</v>
+        <v>1.26185879814074e-09</v>
       </c>
       <c r="E7" t="n">
         <v>1.248252083666356e-09</v>
@@ -2314,7 +2314,7 @@
         <v>1.248252083666356e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.245294082984096e-09</v>
+        <v>1.245294082984097e-09</v>
       </c>
       <c r="H7" t="n">
         <v>1.260676793879491e-09</v>
@@ -2323,13 +2323,13 @@
         <v>1.24810448765117e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.238470208088302e-09</v>
+        <v>1.238470208088303e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.237791164918441e-09</v>
+        <v>1.237791164918443e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.245431590469382e-09</v>
+        <v>1.245431590469384e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2342,13 +2342,13 @@
         <v>1.211135351417905e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.786423672758235e-09</v>
+        <v>1.786423672758236e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.919586330593364e-09</v>
+        <v>1.919586330593363e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.636237391690953e-09</v>
+        <v>1.636237391690956e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.246217918830888e-09</v>
@@ -2360,7 +2360,7 @@
         <v>1.802022047468025e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.789449741238711e-09</v>
+        <v>1.78944974123871e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.779925738798961e-09</v>
@@ -2369,7 +2369,7 @@
         <v>1.207588671373343e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.372918378121905e-09</v>
+        <v>2.372918378121906e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.414845211674846e-10</v>
+        <v>9.41484521167485e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.125018731431803e-09</v>
+        <v>1.125018731431802e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.142116254368992e-09</v>
+        <v>1.142116254368994e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.32411486210544e-09</v>
+        <v>1.324114862105438e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.128333029718745e-09</v>
+        <v>1.128333029718746e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.125521876863787e-09</v>
+        <v>1.125521876863783e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.14090458775918e-09</v>
+        <v>1.140904587759176e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.128332281530857e-09</v>
+        <v>1.128332281530858e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.11869800196799e-09</v>
+        <v>1.118698001967988e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.015730393893479e-09</v>
+        <v>1.015730393893475e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.125659384349069e-09</v>
+        <v>1.125659384349068e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.121241173181565e-10</v>
+        <v>6.12124117318179e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.4251228107693e-10</v>
+        <v>5.425122810769256e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>6.151749039263102e-10</v>
+        <v>6.151749039263114e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.766434547522368e-10</v>
+        <v>5.766434547522204e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.766609540412469e-10</v>
+        <v>5.766609540412394e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>6.140013843664139e-10</v>
+        <v>6.140013843664097e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.163693589090681e-10</v>
+        <v>6.163693589090527e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>6.133710404659004e-10</v>
+        <v>6.133710404659035e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.565795573484937e-10</v>
+        <v>6.565795573485033e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.736272832835032e-10</v>
+        <v>7.736272832835325e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>6.158817825380599e-10</v>
+        <v>6.158817825380681e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.958655877561793e-10</v>
+        <v>5.958655877561782e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.823189426104911e-10</v>
+        <v>4.823189426104822e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.182452231625049e-10</v>
+        <v>6.182452231624992e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.454293723974516e-10</v>
+        <v>5.454293723974509e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.454468716864599e-10</v>
+        <v>5.454468716864761e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.099313621598316e-10</v>
+        <v>6.099313621598462e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.364383922109532e-10</v>
+        <v>6.364383922109644e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.054151772583746e-10</v>
+        <v>6.05415177258382e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.890297921886253e-10</v>
+        <v>6.890297921886181e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.709502085982458e-10</v>
+        <v>8.709502085982487e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.243529887866165e-10</v>
+        <v>6.243529887866219e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.387973739987873e-10</v>
+        <v>4.387973739988093e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.317199373326582e-10</v>
+        <v>4.317199373326865e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.732574121690608e-10</v>
+        <v>4.732574121690732e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.522695896514788e-10</v>
+        <v>4.522695896514919e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.522695896514789e-10</v>
+        <v>4.522695896514867e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.599606262046539e-10</v>
+        <v>4.59960626204683e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.038204747096628e-10</v>
+        <v>5.038204747096698e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.528301573070304e-10</v>
+        <v>4.528301573070315e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.780231702018844e-10</v>
+        <v>4.780231702019016e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.54972383792477e-10</v>
+        <v>4.549723837924928e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.824692386873249e-10</v>
+        <v>4.824692386873356e-10</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.78817340009562e-10</v>
+        <v>8.788173400095316e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.144631880418601e-09</v>
+        <v>1.144631880418572e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.851937237116049e-09</v>
+        <v>1.851937237116068e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.496745930144886e-09</v>
+        <v>1.496745930144933e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.496745930144886e-09</v>
+        <v>1.496745930144933e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.638822525966251e-09</v>
+        <v>1.638822525966271e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.636061539200603e-09</v>
+        <v>2.636061539200628e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.496742801432271e-09</v>
+        <v>1.496742801432311e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.008403076516701e-09</v>
+        <v>2.00840307651674e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.528823505807448e-09</v>
+        <v>1.528823505807431e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.240052480976573e-09</v>
+        <v>2.240052480976586e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.278516662771625e-10</v>
+        <v>5.278516662771608e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.24058488054595e-10</v>
+        <v>5.240584880545271e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.629877070142358e-10</v>
+        <v>5.629877070142667e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.378065771212722e-10</v>
+        <v>5.378065771212737e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.42030217543418e-10</v>
+        <v>5.420302175433837e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.490149184830297e-10</v>
+        <v>5.490149184830287e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.397419023565454e-10</v>
+        <v>9.397419023565729e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.808034571461676e-10</v>
+        <v>8.808034571461683e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.772514177205461e-10</v>
+        <v>5.772514177205415e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.441405860592986e-10</v>
+        <v>5.441405860592996e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.718127659796006e-10</v>
+        <v>5.718127659796355e-10</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.27472017906841e-09</v>
+        <v>1.274720179068398e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.272222318054825e-09</v>
+        <v>1.272222318054889e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.309149083227107e-09</v>
+        <v>1.309149083227124e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.288893026722475e-09</v>
+        <v>1.288893026722556e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.288893026722475e-09</v>
+        <v>1.288893026722556e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.295883431274277e-09</v>
+        <v>1.295883431274286e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.339743279779285e-09</v>
+        <v>1.339743279779244e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.288752962376652e-09</v>
+        <v>1.288752962376732e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.313945975271505e-09</v>
+        <v>1.313945975271524e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.290895188862098e-09</v>
+        <v>1.29089518886206e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.318392043756946e-09</v>
+        <v>1.31839204375697e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.251611746277521e-09</v>
+        <v>1.251611746277536e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.837360817377297e-09</v>
+        <v>1.837360817377303e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.995950921815169e-09</v>
+        <v>1.995950921815209e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.693054070838279e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.284385391366732e-09</v>
+        <v>1.284385391366758e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.860736490302263e-09</v>
+        <v>1.860736490302296e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9045963388075e-09</v>
+        <v>1.90459633880747e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.853606021404638e-09</v>
+        <v>1.853606021404695e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.878914585664333e-09</v>
+        <v>1.878914585664343e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.256865069493575e-09</v>
+        <v>1.2568650694936e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.497420045609873e-09</v>
+        <v>2.497420045609944e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.013159995377581e-09</v>
+        <v>1.013159995377622e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.200629197180691e-09</v>
+        <v>1.200629197180705e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.237587322146789e-09</v>
+        <v>1.237587322146806e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.436380960544829e-09</v>
+        <v>1.436380960544874e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.21716282916646e-09</v>
+        <v>1.217162829166473e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.224290310400139e-09</v>
+        <v>1.224290310400165e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.26815015890515e-09</v>
+        <v>1.268150158905188e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.217159841502517e-09</v>
+        <v>1.217159841502547e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.24235285439737e-09</v>
+        <v>1.242352854397361e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.109234500696902e-09</v>
+        <v>1.109234500696894e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.246798922882811e-09</v>
+        <v>1.246798922882813e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.92592856591115e-10</v>
+        <v>5.925928565911148e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.356282237133096e-10</v>
+        <v>5.356282237133097e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.940678708511184e-10</v>
+        <v>5.940678708511113e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.682701058251172e-10</v>
+        <v>5.682701058251122e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.682876479647396e-10</v>
+        <v>5.682876479647388e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.934141099629444e-10</v>
+        <v>5.934141099629414e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.922166660206138e-10</v>
+        <v>5.922166660206148e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.941256696800116e-10</v>
+        <v>5.941256696800118e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.416535895598576e-10</v>
+        <v>6.416535895598564e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.620185380870658e-10</v>
+        <v>7.620185380870682e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.942514380548576e-10</v>
+        <v>5.94251438054859e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.695439845830797e-10</v>
+        <v>5.695439845830726e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.7853834694052e-10</v>
+        <v>4.785383469405203e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.80699338477981e-10</v>
+        <v>5.806993384779785e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.390895510363167e-10</v>
+        <v>5.390895510363105e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.391070931759446e-10</v>
+        <v>5.391070931759357e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.760758215798537e-10</v>
+        <v>5.760758215798519e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.771860082648062e-10</v>
+        <v>5.771860082648079e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.811290506466914e-10</v>
+        <v>5.811290506466841e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.615150721504166e-10</v>
+        <v>6.615150721504086e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.52350626590549e-10</v>
+        <v>8.523506265905505e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8303609387854e-10</v>
+        <v>5.830360938785398e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.308243747884418e-10</v>
+        <v>4.308243747884416e-10</v>
       </c>
       <c r="C4" t="n">
         <v>4.276324121973041e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.47485339395194e-10</v>
+        <v>4.474853393951937e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.479133533846304e-10</v>
+        <v>4.479133533846306e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.479133533846305e-10</v>
+        <v>4.479133533846306e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.400658535638975e-10</v>
+        <v>4.400658535638977e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.440156598898086e-10</v>
+        <v>4.440156598898087e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.481300373931386e-10</v>
+        <v>4.481300373931397e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.519588240422493e-10</v>
+        <v>4.519588240422499e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.359493161483167e-10</v>
+        <v>4.359493161483165e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.5091807577923e-10</v>
+        <v>4.509180757792301e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.438802989595745e-10</v>
+        <v>8.438802989595744e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1549139169946e-09</v>
+        <v>1.154913916994601e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.464055730879111e-09</v>
+        <v>1.464055730879112e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.484507151260235e-09</v>
+        <v>1.484507151260236e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.484507151260235e-09</v>
+        <v>1.484507151260236e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.355389609634349e-09</v>
+        <v>1.355389609634352e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.518263731883947e-09</v>
+        <v>1.518263731883952e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.484507520843322e-09</v>
+        <v>1.484507520843323e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.59186795672739e-09</v>
+        <v>1.591867956727393e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.270996514126379e-09</v>
+        <v>1.27099651412638e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.674076972298705e-09</v>
+        <v>1.674076972298707e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.148288736737212e-10</v>
+        <v>5.148288736737205e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.149594214017306e-10</v>
+        <v>5.149594214017303e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.57884207334959e-10</v>
+        <v>8.5788420733496e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.286649213375667e-10</v>
+        <v>5.286649213375673e-10</v>
       </c>
       <c r="F6" t="n">
         <v>5.32335206221887e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.240703524491765e-10</v>
+        <v>5.240703524491774e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.570373786767591e-10</v>
+        <v>8.570373786767588e-10</v>
       </c>
       <c r="I6" t="n">
         <v>8.523543454553686e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.612246936607287e-10</v>
+        <v>8.612246936607278e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.199303881167445e-10</v>
+        <v>5.199303881167417e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.350570952672851e-10</v>
+        <v>5.350570952672857e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3094,16 +3094,16 @@
         <v>1.217064466345024e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.21805227279482e-09</v>
+        <v>1.218052272794819e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.23369610932722e-09</v>
+        <v>1.233696109327221e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.234557338455217e-09</v>
+        <v>1.234557338455218e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.234557338455217e-09</v>
+        <v>1.234557338455218e-09</v>
       </c>
       <c r="G7" t="n">
         <v>1.226305945120481e-09</v>
@@ -3112,10 +3112,10 @@
         <v>1.230255751446392e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.234370128949724e-09</v>
+        <v>1.234370128949726e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.238198915598834e-09</v>
+        <v>1.238198915598833e-09</v>
       </c>
       <c r="K7" t="n">
         <v>1.2221894077049e-09</v>
@@ -3134,34 +3134,34 @@
         <v>1.186979291216886e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.735899196217778e-09</v>
+        <v>1.735899196217777e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.864798844508541e-09</v>
+        <v>1.864798844508543e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.602408764785124e-09</v>
+        <v>1.60240876478513e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.221772317228385e-09</v>
+        <v>1.221772317228389e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.743829186227937e-09</v>
+        <v>1.743829186227938e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.747778992554549e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.75189337005718e-09</v>
+        <v>1.751893370057181e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.75582977752537e-09</v>
+        <v>1.755829777525369e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1819321250961e-09</v>
+        <v>1.181932125096098e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.32670418954387e-09</v>
+        <v>2.326704189543868e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.399946877599701e-10</v>
+        <v>9.399946877599726e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.111025940129141e-09</v>
+        <v>1.111025940129142e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.126699317576564e-09</v>
+        <v>1.126699317576566e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.323570006140026e-09</v>
+        <v>1.323570006140027e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.127343306794997e-09</v>
+        <v>1.127343306794996e-09</v>
       </c>
       <c r="G9" t="n">
         <v>1.119279612454804e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.123229418780712e-09</v>
+        <v>1.123229418780715e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.127343796284045e-09</v>
+        <v>1.127343796284047e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.131172582933154e-09</v>
+        <v>1.131172582933155e-09</v>
       </c>
       <c r="K9" t="n">
         <v>1.01663932689413e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.130131834670137e-09</v>
+        <v>1.130131834670136e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.758877382513646e-10</v>
+        <v>5.758877382513633e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.32012162911531e-10</v>
+        <v>5.320121629115304e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.772194444199559e-10</v>
+        <v>5.772194444199545e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.634211593176833e-10</v>
+        <v>5.634211593176827e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.634387974966113e-10</v>
+        <v>5.634387974966104e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.765641717985971e-10</v>
+        <v>5.76564171798598e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.751192476840084e-10</v>
+        <v>5.751192476840063e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.773428791403854e-10</v>
+        <v>5.773428791403835e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.348341941391309e-10</v>
+        <v>6.348341941391294e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.562382805771897e-10</v>
+        <v>7.562382805771901e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.772679908591413e-10</v>
+        <v>5.772679908591412e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.460254764737385e-10</v>
+        <v>5.460254764737371e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.770716828881668e-10</v>
+        <v>4.770716828881651e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.561559158902036e-10</v>
+        <v>5.56155915890203e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.347129441508853e-10</v>
+        <v>5.347129441508792e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.347305823298162e-10</v>
+        <v>5.347305823298156e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.51522453685287e-10</v>
+        <v>5.515224536852897e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.508792065778004e-10</v>
+        <v>5.508792065777995e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.570535823507287e-10</v>
+        <v>5.570535823507258e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.534315609955366e-10</v>
+        <v>6.534315609955338e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.455738707647104e-10</v>
+        <v>8.455738707647123e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.575516244639475e-10</v>
+        <v>5.57551624463947e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.331192243321235e-10</v>
+        <v>4.331192243321234e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.306242333652663e-10</v>
+        <v>4.306242333652635e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.481614581214733e-10</v>
+        <v>4.481614581214724e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.49652409972009e-10</v>
+        <v>4.496524099720081e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.496524099720092e-10</v>
+        <v>4.496524099720083e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.407226852672505e-10</v>
+        <v>4.407226852665654e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.419126687481895e-10</v>
+        <v>4.419126687481863e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.495339753728099e-10</v>
+        <v>4.495339753729062e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.524370614580962e-10</v>
+        <v>4.524370614580923e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.355862971028377e-10</v>
+        <v>4.355862971028348e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.501130435802387e-10</v>
+        <v>4.501130435802363e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.872033769824318e-10</v>
+        <v>8.872033769824054e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.214221058682809e-09</v>
+        <v>1.214221058682811e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.477651549834416e-09</v>
+        <v>1.477651549834412e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.510946754086924e-09</v>
+        <v>1.510946754086917e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.510946754086924e-09</v>
+        <v>1.510946754086916e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.369118590924191e-09</v>
+        <v>1.369118590924115e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.480404922276824e-09</v>
+        <v>1.480404922276822e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.510947292635856e-09</v>
+        <v>1.510947292635849e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.602623889353522e-09</v>
+        <v>1.602623889353521e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.266914009623186e-09</v>
+        <v>1.266914009623184e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.660809199359771e-09</v>
+        <v>1.660809199359764e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.402157913746911e-10</v>
+        <v>8.402157913746903e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.206417297326184e-10</v>
+        <v>5.206417297326112e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.3481389290494e-10</v>
+        <v>5.348138929049335e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.323784679312463e-10</v>
+        <v>5.323784679312454e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.362179359029167e-10</v>
+        <v>5.362179359029162e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.478192523091252e-10</v>
+        <v>8.478192523091306e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.28451897708111e-10</v>
+        <v>5.284518977081078e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.566305424154744e-10</v>
+        <v>8.566305424154734e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.484752277603531e-10</v>
+        <v>5.484752277603539e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.22012839212143e-10</v>
+        <v>5.220128392121401e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.366977555170824e-10</v>
+        <v>5.366977555170786e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.212549527202896e-09</v>
+        <v>1.212549527202895e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.214462154555274e-09</v>
+        <v>1.214462154555271e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.227562576762338e-09</v>
+        <v>1.227562576762336e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.229262168857791e-09</v>
+        <v>1.229262168857789e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.229262168857791e-09</v>
+        <v>1.229262168857789e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.220152988137331e-09</v>
+        <v>1.220152988137322e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.221342971618963e-09</v>
+        <v>1.221342971618959e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.22896427824368e-09</v>
+        <v>1.228964278243679e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.231867364328869e-09</v>
+        <v>1.231867364328868e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.215016599973608e-09</v>
+        <v>1.215016599973604e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.22954334645101e-09</v>
+        <v>1.229543346451009e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3527,34 +3527,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.177067162478251e-09</v>
+        <v>1.177067162478252e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.718735987400312e-09</v>
+        <v>1.71873598740031e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.843270917526293e-09</v>
+        <v>1.843270917526296e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.585683145223976e-09</v>
+        <v>1.585683145223979e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.210772686164589e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.723998910867061e-09</v>
+        <v>1.723998910867073e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.725188894349702e-09</v>
+        <v>1.725188894349699e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.73281020097341e-09</v>
+        <v>1.732810200973408e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.735819280570418e-09</v>
+        <v>1.735819280570416e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.169515935413394e-09</v>
+        <v>1.169515935413393e-09</v>
       </c>
       <c r="L8" t="n">
         <v>2.296762763374446e-09</v>
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.187483861247399e-10</v>
+        <v>9.187483861247419e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.083965979394492e-09</v>
+        <v>1.083965979394485e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.09709580655989e-09</v>
+        <v>1.097095806559887e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.286918084460988e-09</v>
+        <v>1.286918084460994e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.098467446413214e-09</v>
+        <v>1.098467446413221e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.089656812976547e-09</v>
+        <v>1.08965681297655e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.090846796458188e-09</v>
+        <v>1.090846796458181e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.098468103082901e-09</v>
+        <v>1.098468103082895e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.101371189168087e-09</v>
+        <v>1.101371189168089e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.899009790497518e-10</v>
+        <v>9.899009790497455e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.099047171290232e-09</v>
+        <v>1.099047171290228e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.05176724929552e-10</v>
+        <v>6.051767249295556e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.401705054693862e-10</v>
+        <v>5.401705054693894e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>6.066409950590459e-10</v>
+        <v>6.066409950590423e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.729245642087692e-10</v>
+        <v>5.729245642087755e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.72942072001859e-10</v>
+        <v>5.729420720018621e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>6.062226126236869e-10</v>
+        <v>6.062226126236842e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>6.085642740429437e-10</v>
+        <v>6.085642740429471e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>6.065240594122157e-10</v>
+        <v>6.065240594122116e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.47857976488624e-10</v>
+        <v>6.478579764886251e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.682830254804751e-10</v>
+        <v>7.682830254804777e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>6.084906104510672e-10</v>
+        <v>6.084906104510648e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3726,34 +3726,34 @@
         <v>5.869940804875834e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.8160413728853e-10</v>
+        <v>4.816041372885292e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.980732068201123e-10</v>
+        <v>5.980732068201076e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.424355443219524e-10</v>
+        <v>5.424355443219466e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.424530521150409e-10</v>
+        <v>5.424530521150375e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.951286130357716e-10</v>
+        <v>5.951286130357698e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.213767277083906e-10</v>
+        <v>6.213767277083899e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.972578324847204e-10</v>
+        <v>5.972578324847213e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.634124319092625e-10</v>
+        <v>6.634124319092596e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.609625583987753e-10</v>
+        <v>8.609625583987751e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.122452630765688e-10</v>
+        <v>6.122452630765672e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.376437416340864e-10</v>
+        <v>4.376437416340844e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.318685569679575e-10</v>
+        <v>4.318685569679543e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.541833463441785e-10</v>
+        <v>4.541833463441768e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.524907294847937e-10</v>
+        <v>4.524907294847933e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.524907294847938e-10</v>
+        <v>4.524907294847927e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.494212982861879e-10</v>
+        <v>4.494212982861863e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.929060490256899e-10</v>
+        <v>4.929060490256874e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.528452234258503e-10</v>
+        <v>4.528452234258482e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.484439753694345e-10</v>
+        <v>4.484439753694342e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.460561356109034e-10</v>
+        <v>4.460561356109031e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.762126096220271e-10</v>
+        <v>4.762126096220275e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.757982152481055e-10</v>
+        <v>8.757982152481044e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.163354838318225e-09</v>
+        <v>1.163354838318228e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.527620085082181e-09</v>
+        <v>1.527620085082176e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.51351854827285e-09</v>
+        <v>1.513518548272846e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.51351854827285e-09</v>
+        <v>1.513518548272846e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.462265361917797e-09</v>
+        <v>1.462265361917864e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.435330741130788e-09</v>
+        <v>2.435330741130782e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.513517833327636e-09</v>
+        <v>1.513517833327631e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.470418438389464e-09</v>
+        <v>1.470418438389465e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.385664829958927e-09</v>
+        <v>1.385664829958925e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.131153631918276e-09</v>
+        <v>2.131153631918271e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.259330246840219e-10</v>
+        <v>5.259330246840197e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.236002788959302e-10</v>
+        <v>5.236002788959254e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.427552442297837e-10</v>
+        <v>5.427552442297805e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.373707592970671e-10</v>
+        <v>5.373707592970638e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.413168567420194e-10</v>
+        <v>5.413168567420191e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.377105813361237e-10</v>
+        <v>5.377105813361232e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.274503288034809e-10</v>
+        <v>9.27450328803477e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.411345064757864e-10</v>
+        <v>5.411345064757857e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.466881472363147e-10</v>
+        <v>5.466881472363096e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.344116821097382e-10</v>
+        <v>5.344116821097381e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.647596956451558e-10</v>
+        <v>5.647596956451545e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.271021963903833e-09</v>
+        <v>1.271021963903831e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.269709949480358e-09</v>
+        <v>1.269709949480362e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.287530509610893e-09</v>
+        <v>1.287530509610889e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.28638938214502e-09</v>
+        <v>1.286389382145018e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.28638938214502e-09</v>
+        <v>1.286389382145018e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.282799520555937e-09</v>
+        <v>1.282799520555932e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.326284271295438e-09</v>
+        <v>1.326284271295433e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.286223445695597e-09</v>
+        <v>1.286223445695596e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.281822197639186e-09</v>
+        <v>1.281822197639183e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.279434357880652e-09</v>
+        <v>1.27943435788065e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.309590831891778e-09</v>
+        <v>1.309590831891776e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.243123978654408e-09</v>
+        <v>1.243123978654407e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.825236681697798e-09</v>
+        <v>1.825236681697797e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.963689220806112e-09</v>
+        <v>1.963689220806111e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.682233591607037e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.276927057310951e-09</v>
+        <v>1.276927057310953e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.838014832034797e-09</v>
+        <v>1.838014832034795e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.881499582774519e-09</v>
+        <v>1.881499582774515e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.841438757174459e-09</v>
+        <v>1.841438757174457e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.837152107672504e-09</v>
+        <v>1.837152107672497e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.240704743766581e-09</v>
+        <v>1.240704743766579e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.473916741022877e-09</v>
+        <v>2.47391674102288e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.004171596674707e-09</v>
+        <v>1.004171596674705e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.190578002876896e-09</v>
+        <v>1.190578002876893e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2084298437574e-09</v>
+        <v>1.208429843757395e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.423715319447189e-09</v>
+        <v>1.423715319447191e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.207092076298683e-09</v>
+        <v>1.207092076298682e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.203667573952478e-09</v>
+        <v>1.203667573952474e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.247152324691977e-09</v>
+        <v>1.247152324691973e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.207091499092137e-09</v>
+        <v>1.207091499092135e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.202690251035722e-09</v>
+        <v>1.202690251035721e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.091537714405476e-09</v>
+        <v>1.091537714405473e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.230458885288313e-09</v>
+        <v>1.230458885288314e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.700973275176136e-10</v>
+        <v>5.700973275176056e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.31351187917215e-10</v>
+        <v>5.313511879172147e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.715148152243854e-10</v>
+        <v>5.715148152243774e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.616580794717284e-10</v>
+        <v>5.616580794717265e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.616756751948269e-10</v>
+        <v>5.616756751948254e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.708327115308592e-10</v>
+        <v>5.708327115308506e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.694990569589051e-10</v>
+        <v>5.694990569589068e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.715769497536102e-10</v>
+        <v>5.71576949753602e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.297831895569423e-10</v>
+        <v>6.297831895569415e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.550795821451286e-10</v>
+        <v>7.550795821451281e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.71472743314272e-10</v>
+        <v>5.714727433142741e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.356622162797858e-10</v>
+        <v>5.356622162797822e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.744755464307515e-10</v>
+        <v>4.744755464307522e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.464052410125924e-10</v>
+        <v>5.464052410125891e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.31132848321737e-10</v>
+        <v>5.311328483217417e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.311504440448332e-10</v>
+        <v>5.311504440448384e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.415796780440198e-10</v>
+        <v>5.415796780440223e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.416592097711648e-10</v>
+        <v>5.416592097711663e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.468658391517001e-10</v>
+        <v>5.468658391516982e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.446004695550579e-10</v>
+        <v>6.446004695550595e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.446039037861615e-10</v>
+        <v>8.446039037861558e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.471578491530515e-10</v>
+        <v>5.471578491530522e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.280897144433446e-10</v>
+        <v>4.280897144433422e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.243331323391997e-10</v>
+        <v>4.243331323392012e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.441008901679113e-10</v>
+        <v>4.441008901679124e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.447336343777474e-10</v>
+        <v>4.447336343777491e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.447336343777469e-10</v>
+        <v>4.44733634377749e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.363571727503111e-10</v>
+        <v>4.363571727503252e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.386755508340822e-10</v>
+        <v>4.386755508340815e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.44767273245973e-10</v>
+        <v>4.447672732459751e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.480514878106097e-10</v>
+        <v>4.4805148781061e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.341612014795593e-10</v>
+        <v>4.341612014795555e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.450495713526087e-10</v>
+        <v>4.450495713526075e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4199,34 +4199,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.532669532995963e-10</v>
+        <v>8.532669532995988e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.157200002742952e-09</v>
+        <v>1.157200002742953e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.46103809225387e-09</v>
+        <v>1.461038092253873e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.482298239119886e-09</v>
+        <v>1.482298239119885e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.482298239119886e-09</v>
+        <v>1.482298239119885e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.346828900033887e-09</v>
+        <v>1.346828900034136e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.477755789660359e-09</v>
+        <v>1.47775578966036e-09</v>
       </c>
       <c r="I5" t="n">
         <v>1.48229864575605e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.579493267445456e-09</v>
+        <v>1.579493267445458e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.295218777759975e-09</v>
+        <v>1.295218777759981e-09</v>
       </c>
       <c r="L5" t="n">
         <v>1.622527463051989e-09</v>
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.323128726994246e-10</v>
+        <v>8.323128726994265e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.12686078619712e-10</v>
+        <v>5.126860786197102e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.293494936525665e-10</v>
+        <v>5.293494936525693e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.262573853452013e-10</v>
+        <v>5.26257385345203e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.299269114869133e-10</v>
+        <v>5.299269114869193e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.213073729398247e-10</v>
+        <v>5.213073729398322e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.514519996967287e-10</v>
+        <v>8.514519996967335e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.489904315020527e-10</v>
+        <v>8.489904315020566e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.424186691794235e-10</v>
+        <v>5.424186691794268e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.192141608053772e-10</v>
+        <v>5.192141608053764e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.301136389093051e-10</v>
+        <v>5.301136389093053e-10</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.205323304644904e-09</v>
+        <v>1.205323304644901e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.205845784216158e-09</v>
+        <v>1.205845784216156e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.221305372785444e-09</v>
+        <v>1.221305372785442e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.222241282711262e-09</v>
+        <v>1.222241282711265e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.222241282711262e-09</v>
+        <v>1.222241282711265e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.213590762951872e-09</v>
+        <v>1.213590762951881e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.215909141035642e-09</v>
+        <v>1.215909141035638e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.222000863447534e-09</v>
+        <v>1.222000863447535e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.225285078012168e-09</v>
+        <v>1.225285078012171e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.211394791681118e-09</v>
+        <v>1.211394791681121e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.222283161554167e-09</v>
+        <v>1.222283161554171e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.164114831425359e-09</v>
+        <v>1.164114831425367e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.698627082014793e-09</v>
+        <v>1.698627082014794e-09</v>
       </c>
       <c r="D8" t="n">
         <v>1.824393459094111e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.568795041304122e-09</v>
+        <v>1.568795041304128e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.197867886056215e-09</v>
+        <v>1.197867886056218e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.706000524493757e-09</v>
+        <v>1.706000524493766e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.708318902578198e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.714410624989412e-09</v>
+        <v>1.714410624989418e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.717799710896538e-09</v>
+        <v>1.717799710896539e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.160274085784856e-09</v>
+        <v>1.160274085784859e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.272101789802159e-09</v>
+        <v>2.272101789802165e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.269165762993595e-10</v>
+        <v>9.26916576299363e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.094099691862164e-09</v>
+        <v>1.094099691862167e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.109588605293177e-09</v>
+        <v>1.109588605293187e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.302577258839459e-09</v>
+        <v>1.302577258839471e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.110254250705068e-09</v>
+        <v>1.110254250705078e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.101844670597871e-09</v>
+        <v>1.101844670597891e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.104163048681647e-09</v>
+        <v>1.104163048681652e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.110254771093536e-09</v>
+        <v>1.110254771093544e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.11353898565817e-09</v>
+        <v>1.113538985658184e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>8.897931534817559e-10</v>
+        <v>8.897931534817584e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.110537069200179e-09</v>
+        <v>1.110537069200181e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.685893268658384e-10</v>
+        <v>5.685893268658374e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.312246052878528e-10</v>
+        <v>5.312246052878533e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.698085004293883e-10</v>
+        <v>5.698085004293864e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.591827276620217e-10</v>
+        <v>5.591827276620213e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.592004173474733e-10</v>
+        <v>5.592004173474732e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.692509469691e-10</v>
+        <v>5.692509469690993e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.678625763740493e-10</v>
+        <v>5.6786257637405e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.700535108980325e-10</v>
+        <v>5.700535108980311e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.258340903685579e-10</v>
+        <v>6.258340903685575e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.515421612037657e-10</v>
+        <v>7.51542161203766e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.699163662268523e-10</v>
+        <v>5.699163662268522e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.313087060124138e-10</v>
+        <v>5.313087060124151e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.727280510380655e-10</v>
+        <v>4.727280510380654e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.406366060018703e-10</v>
+        <v>5.406366060018704e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.250956871503618e-10</v>
+        <v>5.250956871503612e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.251133768358131e-10</v>
+        <v>5.251133768358145e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.366987677063066e-10</v>
+        <v>5.36698767706304e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.36372956360257e-10</v>
+        <v>5.363729563602564e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.424000732714876e-10</v>
+        <v>5.424000732714871e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.377206839432961e-10</v>
+        <v>6.377206839432936e-10</v>
       </c>
       <c r="K3" t="n">
         <v>8.359700507481315e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.424751151551988e-10</v>
+        <v>5.42475115155199e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.291576763177672e-10</v>
+        <v>4.291576763177676e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.25713371973842e-10</v>
+        <v>4.257133719738417e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.429288025656073e-10</v>
+        <v>4.42928802565607e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.458645469994851e-10</v>
+        <v>4.458645469994864e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.458645469994851e-10</v>
+        <v>4.458645469994865e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.365849966969355e-10</v>
+        <v>4.365849966969356e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.382644864898638e-10</v>
+        <v>4.38264486489864e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.456156862397848e-10</v>
+        <v>4.456156862397856e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.522127920520498e-10</v>
+        <v>4.522127920520495e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.333140873253917e-10</v>
+        <v>4.333140873253916e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.455956866166311e-10</v>
+        <v>4.45595686616631e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.796735890865277e-10</v>
+        <v>8.796735890865295e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.19569072743575e-09</v>
+        <v>1.195690727435751e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.447956962445811e-09</v>
+        <v>1.447956962445815e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.504501387536191e-09</v>
+        <v>1.504501387536193e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.504501387536191e-09</v>
+        <v>1.504501387536193e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.358003249795925e-09</v>
+        <v>1.358003249795939e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.477651729459532e-09</v>
+        <v>1.477651729459533e-09</v>
       </c>
       <c r="I5" t="n">
         <v>1.504501927866839e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.660985947087887e-09</v>
+        <v>1.66098594708789e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.287633289497123e-09</v>
+        <v>1.287633289497125e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.641094481425986e-09</v>
+        <v>1.641094481425987e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.358993584511621e-10</v>
+        <v>8.358993584511638e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.165872872312033e-10</v>
+        <v>5.16587287231203e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.302814702074409e-10</v>
+        <v>5.30281470207441e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.291639326365966e-10</v>
+        <v>5.291639326365983e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.329776410892511e-10</v>
+        <v>5.329776410892526e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.237172022930861e-10</v>
+        <v>5.237172022930862e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.549451519530515e-10</v>
+        <v>8.549451519530524e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.32747891835935e-10</v>
+        <v>5.327478918359359e-10</v>
       </c>
       <c r="J6" t="n">
         <v>8.643158269391799e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.205139091925184e-10</v>
+        <v>5.205139091925181e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.328742165442367e-10</v>
+        <v>5.328742165442371e-10</v>
       </c>
     </row>
     <row r="7">
@@ -4678,25 +4678,25 @@
         <v>1.198976725466367e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.20019491777885e-09</v>
+        <v>1.200194917778851e-09</v>
       </c>
       <c r="D7" t="n">
         <v>1.212718909434058e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.215771235081482e-09</v>
+        <v>1.215771235081483e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.215771235081482e-09</v>
+        <v>1.215771235081483e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.206404045845535e-09</v>
+        <v>1.206404045845534e-09</v>
       </c>
       <c r="H7" t="n">
         <v>1.208083535638463e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.215434735388384e-09</v>
+        <v>1.215434735388385e-09</v>
       </c>
       <c r="J7" t="n">
         <v>1.222031841200649e-09</v>
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.151095127660148e-09</v>
+        <v>1.151095127660147e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.676869138246446e-09</v>
+        <v>1.676869138246445e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.797634960240226e-09</v>
+        <v>1.797634960240229e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.548716878829883e-09</v>
+        <v>1.548716878829885e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.184383904512031e-09</v>
+        <v>1.184383904512032e-09</v>
       </c>
       <c r="G8" t="n">
         <v>1.682616780396707e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.684296270190589e-09</v>
+        <v>1.684296270190588e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.691647469939557e-09</v>
+        <v>1.691647469939558e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.698347575351658e-09</v>
+        <v>1.698347575351657e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.145516217369623e-09</v>
+        <v>1.14551621736962e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.239087824565506e-09</v>
+        <v>2.239087824565507e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.039188178332928e-10</v>
+        <v>9.039188178332978e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.064892851742613e-09</v>
+        <v>1.064892851742621e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.077446003264367e-09</v>
+        <v>1.077446003264375e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.264487041557818e-09</v>
+        <v>1.264487041557826e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.080132018630302e-09</v>
+        <v>1.080132018630309e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.071101979809298e-09</v>
+        <v>1.071101979809304e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.072781469602225e-09</v>
+        <v>1.072781469602232e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.080132669352147e-09</v>
+        <v>1.080132669352154e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.086729775164411e-09</v>
+        <v>1.086729775164418e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.715125903997442e-10</v>
+        <v>9.715125903997502e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.080112669728991e-09</v>
+        <v>1.080112669728999e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.368602500669173e-10</v>
+        <v>5.36860250066916e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>6.339574237700792e-10</v>
+        <v>6.339574237700806e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.392775845253584e-10</v>
+        <v>5.392775845253586e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.683187425837735e-10</v>
+        <v>6.683187425837743e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.681603682019286e-10</v>
+        <v>5.681603682019298e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.367612728035463e-10</v>
+        <v>5.367612728035464e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.434318019416059e-10</v>
+        <v>5.434318019416052e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.332449067515801e-10</v>
+        <v>5.332449067515818e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.838256045071777e-10</v>
+        <v>7.838256045071782e-10</v>
       </c>
       <c r="K2" t="n">
         <v>7.927994694425463e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.486916288115728e-10</v>
+        <v>5.48691628811572e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.877868080474107e-10</v>
+        <v>4.877868080474084e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.300432671062898e-10</v>
+        <v>6.300432671062888e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.050457040690139e-10</v>
+        <v>5.050457040690134e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.855865365669831e-10</v>
+        <v>6.855865365669815e-10</v>
       </c>
       <c r="F3" t="n">
         <v>5.202453692413647e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.872040485184051e-10</v>
+        <v>4.872040485184064e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.443952320524168e-10</v>
+        <v>5.443952320524162e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.619823123395672e-10</v>
+        <v>4.619823123395674e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>9.031259786836968e-10</v>
+        <v>9.031259786836984e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.993572354536205e-10</v>
+        <v>8.993572354536192e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.731571259902514e-10</v>
+        <v>5.731571259902527e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.966894305854878e-10</v>
+        <v>4.966894305854872e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.533152641711411e-10</v>
+        <v>4.533152641711427e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.239943353223848e-10</v>
+        <v>5.239943353223854e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.543684588508003e-10</v>
+        <v>4.54368458850802e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.543684588508006e-10</v>
+        <v>4.54368458850802e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.955142758510398e-10</v>
+        <v>4.955142758510301e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.875852927176682e-10</v>
+        <v>5.875852927176687e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.556904513248317e-10</v>
+        <v>4.55690451324833e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.120039851567194e-10</v>
+        <v>5.120039851567196e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.740306172187933e-10</v>
+        <v>4.740306172187935e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>6.300792982967694e-10</v>
+        <v>6.300792982967705e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.260500207805934e-09</v>
+        <v>2.26050020780593e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.487311844996565e-09</v>
+        <v>1.487311844996568e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.78025996462013e-09</v>
+        <v>2.780259964620136e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.487311895881651e-09</v>
+        <v>1.487311895881654e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.487311895881651e-09</v>
+        <v>1.487311895881655e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.308070204049917e-09</v>
+        <v>2.308070204049991e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.341388130399167e-09</v>
+        <v>4.341388130399175e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.487301210830998e-09</v>
+        <v>1.487301210831001e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.683066033484562e-09</v>
+        <v>2.683066033484554e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.888575350508767e-09</v>
+        <v>1.888575350508769e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.097308185399329e-09</v>
+        <v>2.097308185399319e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.932772241087865e-10</v>
+        <v>5.932772241087841e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.50548804230697e-10</v>
+        <v>5.505488042306981e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>6.219320970655138e-10</v>
+        <v>6.21932097065514e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.468140515008995e-10</v>
+        <v>5.468140515008996e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.522152958699119e-10</v>
+        <v>5.52215295869913e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.921020693743212e-10</v>
+        <v>5.921020693743276e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>1.032368044570474e-09</v>
+        <v>1.032368044570476e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>9.031422104727939e-10</v>
+        <v>9.031422104727926e-10</v>
       </c>
       <c r="J6" t="n">
         <v>6.190740329627383e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.701782453497168e-10</v>
+        <v>5.701782453497167e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>7.277195333746242e-10</v>
+        <v>7.277195333746236e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5074,34 +5074,34 @@
         <v>1.335190792617673e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.294202447522586e-09</v>
+        <v>1.294202447522584e-09</v>
       </c>
       <c r="D7" t="n">
         <v>1.362463374565286e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.294137987260424e-09</v>
+        <v>1.294137987260426e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.294137987260424e-09</v>
+        <v>1.294137987260426e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.33401563788322e-09</v>
+        <v>1.334015637883217e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.426086654749854e-09</v>
+        <v>1.426086654749856e-09</v>
       </c>
       <c r="I7" t="n">
         <v>1.29419181335702e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.350505347188906e-09</v>
+        <v>1.350505347188905e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.312531979250979e-09</v>
+        <v>1.31253197925098e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.468580660328956e-09</v>
+        <v>1.468580660328957e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.304692344684998e-09</v>
+        <v>1.304692344684999e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.846761680603383e-09</v>
+        <v>1.846761680603388e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>2.035842960128345e-09</v>
+        <v>2.035842960128336e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.68730788268031e-09</v>
+        <v>1.687307882680307e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.282163915755573e-09</v>
+        <v>1.282163915755568e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.886481461322962e-09</v>
+        <v>1.886481461322954e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.978552478189567e-09</v>
+        <v>1.97855247818957e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.846657636796757e-09</v>
+        <v>1.846657636796761e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.903085739892891e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.271204670676775e-09</v>
+        <v>1.271204670676773e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.630001411971368e-09</v>
+        <v>2.630001411971369e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.086862231637718e-09</v>
+        <v>1.086862231637721e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.239368916085018e-09</v>
+        <v>1.239368916085028e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.307662385635568e-09</v>
+        <v>1.307662385635562e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.462658116456473e-09</v>
+        <v>1.462658116456472e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.239368798594737e-09</v>
+        <v>1.239368798594742e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.279182106445654e-09</v>
+        <v>1.279182106445656e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3712531233123e-09</v>
+        <v>1.371253123312295e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.239358281919461e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.295671815751347e-09</v>
+        <v>1.295671815751342e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.14558676019573e-09</v>
+        <v>1.145586760195725e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.413747128891397e-09</v>
+        <v>1.413747128891399e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.316503021309407e-10</v>
+        <v>5.316503021309412e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>6.262850892765988e-10</v>
+        <v>6.262850892765995e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.345291823292169e-10</v>
+        <v>5.345291823292174e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.592640884358433e-10</v>
+        <v>6.592640884358432e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.631948523653333e-10</v>
+        <v>5.631948523653338e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.32360585593869e-10</v>
+        <v>5.323605855938694e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.377237605571305e-10</v>
+        <v>5.377237605571306e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.295746439140456e-10</v>
+        <v>5.295746439140461e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.689849023052544e-10</v>
+        <v>7.689849023052553e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.85316014349375e-10</v>
+        <v>7.853160143493755e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.432715110392439e-10</v>
+        <v>5.432715110392449e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.774405406748509e-10</v>
+        <v>4.774405406748516e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.239632093139509e-10</v>
+        <v>6.239632093139517e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.979080351332088e-10</v>
+        <v>4.979080351332097e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.772559813320655e-10</v>
+        <v>6.772559813320651e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.186646615183651e-10</v>
+        <v>5.186646615183648e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.825550265078428e-10</v>
+        <v>4.825550265078429e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.304395222637292e-10</v>
+        <v>5.304395222637303e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.625396355547144e-10</v>
+        <v>4.625396355547157e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.786853390860749e-10</v>
+        <v>8.786853390860758e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.910600215879389e-10</v>
+        <v>8.910600215879397e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.613330451549082e-10</v>
+        <v>5.613330451549094e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.75699662061811e-10</v>
+        <v>4.756996620618106e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.502368401800062e-10</v>
+        <v>4.50236840180005e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.082179382516606e-10</v>
+        <v>5.082179382516614e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.511944475739682e-10</v>
+        <v>4.51194447573967e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.511944475739678e-10</v>
+        <v>4.511944475739669e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.836681394231851e-10</v>
+        <v>4.836681394231841e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.610259259491972e-10</v>
+        <v>5.610259259491964e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.521101542436253e-10</v>
+        <v>4.521101542436241e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.948442399897812e-10</v>
+        <v>4.948442399897818e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.652783241221668e-10</v>
+        <v>4.652783241221667e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>6.069016135524659e-10</v>
+        <v>6.06901613552464e-10</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.960728583041018e-09</v>
+        <v>1.960728583041022e-09</v>
       </c>
       <c r="C5" t="n">
         <v>1.500923814788659e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4948157346467e-09</v>
+        <v>2.494815734646711e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.500923857778586e-09</v>
+        <v>1.50092385777858e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.500923857778586e-09</v>
+        <v>1.50092385777858e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.125975347643531e-09</v>
+        <v>2.125975347643528e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>3.763207302169691e-09</v>
+        <v>3.76320730216965e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.500915077160091e-09</v>
+        <v>1.500915077160079e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.39354329135719e-09</v>
+        <v>2.393543291357193e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.755462074299201e-09</v>
+        <v>1.755462074299198e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.185591835159488e-09</v>
+        <v>2.185591835159436e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.667124025452323e-10</v>
+        <v>5.667124025452332e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.417680913361208e-10</v>
+        <v>5.417680913361199e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>6.002879836840468e-10</v>
+        <v>6.002879836840465e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.38270960727336e-10</v>
+        <v>5.38270960727335e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4310773106415e-10</v>
+        <v>5.431077310641479e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.746808799066073e-10</v>
+        <v>5.746808799066071e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.751336710126338e-10</v>
+        <v>9.751336710126346e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.687378929357878e-10</v>
+        <v>8.687378929357869e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.955168041999536e-10</v>
+        <v>5.955168041999545e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.558940214370588e-10</v>
+        <v>5.558940214370595e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.987890531412299e-10</v>
+        <v>6.98789053141228e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.249384926138192e-09</v>
+        <v>1.249384926138193e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.225804155948581e-09</v>
+        <v>1.225804155948579e-09</v>
       </c>
       <c r="D7" t="n">
         <v>1.281873141358916e-09</v>
@@ -5479,25 +5479,25 @@
         <v>1.225810168150309e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.22581016815031e-09</v>
+        <v>1.225810168150309e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.257353403499568e-09</v>
+        <v>1.257353403499569e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.334711190025581e-09</v>
+        <v>1.334711190025578e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.225795418320008e-09</v>
+        <v>1.225795418320009e-09</v>
       </c>
       <c r="J7" t="n">
         <v>1.268529504066165e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.23896358819855e-09</v>
+        <v>1.238963588198549e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.380586877628848e-09</v>
+        <v>1.380586877628846e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.211606335672021e-09</v>
+        <v>1.21160633567202e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.71951491420815e-09</v>
+        <v>1.719514914208146e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.885643258893368e-09</v>
+        <v>1.885643258893367e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.574174278038269e-09</v>
+        <v>1.574174278038267e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.204889807960711e-09</v>
+        <v>1.20488980796071e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.750916334264481e-09</v>
+        <v>1.750916334264478e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.828274120790458e-09</v>
+        <v>1.828274120790456e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.71935834908492e-09</v>
+        <v>1.719358349084918e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.762196858734414e-09</v>
+        <v>1.762196858734412e-09</v>
       </c>
       <c r="K8" t="n">
         <v>1.191315056178876e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.429180457439046e-09</v>
+        <v>2.429180457439045e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5547,22 +5547,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.955627902229047e-10</v>
+        <v>9.955627902229037e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.143502163137035e-09</v>
+        <v>1.143502163137033e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.199601414376396e-09</v>
+        <v>1.199601414376398e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.341432815437263e-09</v>
+        <v>1.341432815437262e-09</v>
       </c>
       <c r="F9" t="n">
         <v>1.14350205876215e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.17505141068802e-09</v>
+        <v>1.175051410688022e-09</v>
       </c>
       <c r="H9" t="n">
         <v>1.252409197214034e-09</v>
@@ -5571,13 +5571,13 @@
         <v>1.143493425508461e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.186227511254618e-09</v>
+        <v>1.18622751125462e-09</v>
       </c>
       <c r="K9" t="n">
         <v>1.057282237024412e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.298284884817301e-09</v>
+        <v>1.298284884817303e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.283969284192615e-10</v>
+        <v>5.283969284192624e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>6.230355130531127e-10</v>
+        <v>6.230355130531137e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.311156349184125e-10</v>
+        <v>5.311156349184161e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.551094617364607e-10</v>
+        <v>6.551094617364612e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.617129239757721e-10</v>
+        <v>5.617129239757736e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.294119239871224e-10</v>
+        <v>5.294119239871271e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.334486134419e-10</v>
+        <v>5.334486134419023e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.283288977398088e-10</v>
+        <v>5.283288977398119e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.601545646341936e-10</v>
+        <v>7.601545646341937e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.807175908612269e-10</v>
+        <v>7.80717590861227e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.395515870837789e-10</v>
+        <v>5.395515870837805e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7082597778889e-10</v>
+        <v>4.708259777888901e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.283005894656468e-10</v>
+        <v>6.283005894656488e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.901283041409728e-10</v>
+        <v>4.901283041409767e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.801260049472666e-10</v>
+        <v>6.801260049472659e-10</v>
       </c>
       <c r="F3" t="n">
         <v>5.259464532338456e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.781078909811562e-10</v>
+        <v>4.781078909811653e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.163919718688148e-10</v>
+        <v>5.163919718688162e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.702112845520169e-10</v>
+        <v>4.702112845520135e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.654043753540551e-10</v>
+        <v>8.654043753540536e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.853516013547942e-10</v>
+        <v>8.853516013547966e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.513434872296221e-10</v>
+        <v>5.513434872296237e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.676992116156262e-10</v>
+        <v>4.676992116156286e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.655387841652226e-10</v>
+        <v>4.655387841652221e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.98408252190317e-10</v>
+        <v>4.984082521903195e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.66459129638285e-10</v>
+        <v>4.664591296382838e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.664591296382849e-10</v>
+        <v>4.66459129638284e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.791199170636509e-10</v>
+        <v>4.791199170636499e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.415720599306404e-10</v>
+        <v>5.415720599306429e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.668569670033923e-10</v>
+        <v>4.668569670033933e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.920066987423079e-10</v>
+        <v>4.920066987423111e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.637951297431812e-10</v>
+        <v>4.637951297431831e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.937595403314298e-10</v>
+        <v>5.937595403314325e-10</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.815528573891113e-09</v>
+        <v>1.815528573891116e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.734936752250428e-09</v>
+        <v>1.734936752250416e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.306215242082485e-09</v>
+        <v>2.306215242082484e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.734936783492054e-09</v>
+        <v>1.734936783492042e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.734936783492054e-09</v>
+        <v>1.734936783492042e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.037868304409947e-09</v>
+        <v>2.037868304410289e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>3.317830314701814e-09</v>
+        <v>3.317830314701791e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.734932429834657e-09</v>
+        <v>1.734932429834646e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.356085660371159e-09</v>
+        <v>2.356085660371165e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.705251787033315e-09</v>
+        <v>1.705251787033319e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.982110814457966e-09</v>
+        <v>1.982110814458022e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.597058293023211e-10</v>
+        <v>5.59705829302319e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.581477865165744e-10</v>
+        <v>5.581477865165763e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.912189080776065e-10</v>
+        <v>5.912189080776045e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.546127758927025e-10</v>
+        <v>5.546127758927012e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.59029559210149e-10</v>
+        <v>5.590295592101511e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.957175408414876e-10</v>
+        <v>8.957175408415132e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.556712848774885e-10</v>
+        <v>9.556712848774926e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.588635846900884e-10</v>
+        <v>5.588635846900852e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.06537382466447e-10</v>
+        <v>9.065373824664447e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5541901728412e-10</v>
+        <v>5.554190172841204e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.866017600841479e-10</v>
+        <v>6.866017600841477e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.236620752088378e-09</v>
+        <v>1.23662075208838e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.235782829891912e-09</v>
+        <v>1.235782829891914e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.267299753392805e-09</v>
+        <v>1.267299753392808e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.235885390673016e-09</v>
+        <v>1.235885390673015e-09</v>
       </c>
       <c r="F7" t="n">
         <v>1.235885390673015e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.248041457536376e-09</v>
+        <v>1.248041457536403e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.310493600403392e-09</v>
+        <v>1.310493600403394e-09</v>
       </c>
       <c r="I7" t="n">
         <v>1.235778507476144e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.260928239215059e-09</v>
+        <v>1.260928239215062e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.232716670215931e-09</v>
+        <v>1.232716670215934e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.362681080804181e-09</v>
+        <v>1.362681080804184e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.192838240521833e-09</v>
+        <v>1.192838240521839e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.715998047719292e-09</v>
+        <v>1.715998047719298e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.855911209230794e-09</v>
+        <v>1.8559112092308e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.572721486781403e-09</v>
+        <v>1.572721486781404e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.20868178711813e-09</v>
+        <v>1.208681787118131e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.728018018447997e-09</v>
+        <v>1.728018018447996e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.790470161314962e-09</v>
+        <v>1.790470161314968e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.715755068387735e-09</v>
+        <v>1.715755068387738e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.741007733857926e-09</v>
+        <v>1.741007733857931e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.179205064974663e-09</v>
+        <v>1.179205064974666e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.389767789001102e-09</v>
+        <v>2.389767789001107e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.654372359040771e-10</v>
+        <v>9.654372359040916e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.129678206650676e-09</v>
+        <v>1.129678206650686e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.161225373657717e-09</v>
+        <v>1.161225373657727e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.320175791525109e-09</v>
+        <v>1.320175791525125e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.12967809932387e-09</v>
+        <v>1.129678099323878e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.14193683429515e-09</v>
+        <v>1.141936834295172e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.204388977162151e-09</v>
+        <v>1.204388977162166e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.129673884234907e-09</v>
+        <v>1.12967388423492e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.154823615973821e-09</v>
+        <v>1.154823615973833e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.030964773989486e-09</v>
+        <v>1.030964773989498e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.256576457562942e-09</v>
+        <v>1.256576457562956e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.079202332321704e-10</v>
+        <v>5.079202332321715e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.918225059484401e-10</v>
+        <v>5.918225059484408e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.089433594027099e-10</v>
+        <v>5.089433594027104e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.208084809695896e-10</v>
+        <v>6.208084809695899e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.365379234034821e-10</v>
+        <v>5.365379234034832e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.086140467648503e-10</v>
+        <v>5.086140467648502e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.10248163586466e-10</v>
+        <v>5.102481635864665e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.075385400365319e-10</v>
+        <v>5.075385400365323e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.17605035690605e-10</v>
+        <v>7.176050356906087e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.517185135349234e-10</v>
+        <v>7.517185135349249e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.114005533291938e-10</v>
+        <v>5.114005533291944e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.38065283054869e-10</v>
+        <v>4.380652830548688e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.760890527014793e-10</v>
+        <v>5.7608905270148e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.453160875128955e-10</v>
+        <v>4.453160875128967e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.228647748939107e-10</v>
+        <v>6.228647748939128e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.837492986725748e-10</v>
+        <v>4.837492986725754e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.430253055497128e-10</v>
+        <v>4.430253055497125e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.639595569673039e-10</v>
+        <v>4.639595569673043e-10</v>
       </c>
       <c r="I3" t="n">
         <v>4.352515971964956e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.01395861245561e-10</v>
+        <v>8.013958612455652e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.433726159290205e-10</v>
+        <v>8.433726159290204e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.638753133984822e-10</v>
+        <v>4.638753133984826e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.275338103591452e-10</v>
+        <v>4.275338103591454e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.214740837733472e-10</v>
+        <v>4.214740837733474e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.390904911166795e-10</v>
+        <v>4.390904911166805e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.224153513886389e-10</v>
+        <v>4.224153513886391e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.224153513886387e-10</v>
+        <v>4.224153513886393e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.353206351815975e-10</v>
+        <v>4.353206351815979e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.706678573775008e-10</v>
+        <v>4.706678573775015e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.231082488173222e-10</v>
+        <v>4.231082488173229e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.627311325072251e-10</v>
+        <v>4.627311325072258e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.335201069801021e-10</v>
+        <v>4.335201069801025e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.679876126447164e-10</v>
+        <v>4.679876126447172e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.423647043981997e-09</v>
+        <v>1.423647043981982e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.292229446265528e-09</v>
+        <v>1.292229446265527e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.613630147513432e-09</v>
+        <v>1.613630147513431e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.292229483234795e-09</v>
+        <v>1.292229483234794e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.292229483234796e-09</v>
+        <v>1.292229483234794e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.576360193350949e-09</v>
+        <v>1.576360193350945e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.31193904661371e-09</v>
+        <v>2.311939046613719e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.292225205835508e-09</v>
+        <v>1.292225205835509e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.151210694673271e-09</v>
+        <v>2.151210694673275e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.517931218069198e-09</v>
+        <v>1.517931218069192e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.383390811555883e-09</v>
+        <v>2.383390811555882e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.67100217406579e-10</v>
+        <v>8.671002174065782e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.237528890939233e-10</v>
+        <v>5.237528890939254e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.782527150237286e-10</v>
+        <v>8.782527150237316e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.201745490153726e-10</v>
+        <v>5.201745490153734e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.247072123489764e-10</v>
+        <v>5.247072123489774e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.748870422290308e-10</v>
+        <v>8.748870422290318e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.725459638063395e-10</v>
+        <v>5.725459638063399e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.626746558647552e-10</v>
+        <v>8.626746558647546e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.006182482042471e-10</v>
+        <v>9.006182482042484e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.350458284959155e-10</v>
+        <v>5.350458284959157e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.698388979047721e-10</v>
+        <v>5.698388979047724e-10</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.227368914906125e-09</v>
+        <v>1.227368914906126e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.222947593794321e-09</v>
+        <v>1.222947593794322e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.238893689670074e-09</v>
+        <v>1.238893689670076e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.222989366403696e-09</v>
+        <v>1.222989366403698e-09</v>
       </c>
       <c r="F7" t="n">
         <v>1.222989366403698e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.235155739728576e-09</v>
+        <v>1.235155739728577e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.270502961924479e-09</v>
+        <v>1.270502961924482e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.222943353364302e-09</v>
+        <v>1.222943353364304e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.262566237054204e-09</v>
+        <v>1.262566237054207e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.23335521152708e-09</v>
+        <v>1.233355211527082e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.267822717191697e-09</v>
+        <v>1.267822717191698e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6302,34 +6302,34 @@
         <v>1.166774738593047e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.69417999960322e-09</v>
+        <v>1.694179999603224e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.820213039588762e-09</v>
+        <v>1.820213039588765e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.548752740024757e-09</v>
+        <v>1.548752740024759e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.179249620649985e-09</v>
+        <v>1.179249620649986e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.70620371929948e-09</v>
+        <v>1.706203719299481e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.741550941495348e-09</v>
+        <v>1.741550941495354e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.693991332935203e-09</v>
+        <v>1.693991332935204e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.733718699612404e-09</v>
+        <v>1.73371869961241e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.162885509217453e-09</v>
+        <v>1.162885509217451e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.294215383842026e-09</v>
+        <v>2.294215383842032e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6339,34 +6339,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.715830291059461e-10</v>
+        <v>9.715830291059469e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.144579371072847e-09</v>
+        <v>1.144579371072849e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.160557591223541e-09</v>
+        <v>1.160557591223542e-09</v>
       </c>
       <c r="E9" t="n">
         <v>1.349315663091982e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.144579277160002e-09</v>
+        <v>1.144579277160004e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.156787517007105e-09</v>
+        <v>1.156787517007107e-09</v>
       </c>
       <c r="H9" t="n">
         <v>1.192134739203009e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.14457513064283e-09</v>
+        <v>1.144575130642831e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.184198014332733e-09</v>
+        <v>1.184198014332734e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.052190589853188e-09</v>
+        <v>1.052190589853189e-09</v>
       </c>
       <c r="L9" t="n">
         <v>1.189454494470224e-09</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.030407382897802e-10</v>
+        <v>5.030407382897771e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.79970908927844e-10</v>
+        <v>5.799709089278435e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.017077417407604e-10</v>
+        <v>5.017077417407584e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.068380239290654e-10</v>
+        <v>6.068380239290662e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.288676176476454e-10</v>
+        <v>5.288676176476422e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.023461442155777e-10</v>
+        <v>5.02346144215579e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.008363530172576e-10</v>
+        <v>5.008363530172571e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.020581179895758e-10</v>
+        <v>5.020581179895734e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>6.967562081900002e-10</v>
+        <v>6.967562081899978e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.404962812888385e-10</v>
+        <v>7.404962812888395e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.023914619307609e-10</v>
+        <v>5.023914619307605e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.41999234203335e-10</v>
+        <v>4.419992342033329e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.65170172365816e-10</v>
+        <v>5.651701723658149e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.325180610348685e-10</v>
+        <v>4.325180610348667e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.084892679542644e-10</v>
+        <v>6.08489267954267e-10</v>
       </c>
       <c r="F3" t="n">
         <v>4.797733068364407e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.370667157270878e-10</v>
+        <v>4.370667157270897e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.357279872592179e-10</v>
+        <v>4.357279872592172e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.348903151589152e-10</v>
+        <v>4.34890315158916e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>7.757129724151602e-10</v>
+        <v>7.757129724151545e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.31974290903169e-10</v>
+        <v>8.319742909031667e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.385079873158463e-10</v>
+        <v>4.38507987315846e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.313430800215617e-10</v>
+        <v>4.31343080021562e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.187686620515186e-10</v>
+        <v>4.187686620515188e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.162862707916759e-10</v>
+        <v>4.162862707916762e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.196224465977827e-10</v>
+        <v>4.196224465977823e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.196224465977829e-10</v>
+        <v>4.196224465977823e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.234483757719891e-10</v>
+        <v>4.234483757719863e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.235367392853954e-10</v>
+        <v>4.235367392853957e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.201382296140023e-10</v>
+        <v>4.20138229614002e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.599988266344139e-10</v>
+        <v>4.599988266344135e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.273156903997933e-10</v>
+        <v>4.273156903997938e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.256257728048418e-10</v>
+        <v>4.256257728048421e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6578,34 +6578,34 @@
         <v>1.573105796193857e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.32699314626664e-09</v>
+        <v>1.326993146266638e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.32363821993459e-09</v>
+        <v>1.323638219934589e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.326993180780898e-09</v>
+        <v>1.326993180780893e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.326993180780898e-09</v>
+        <v>1.326993180780893e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.447161268354551e-09</v>
+        <v>1.447161268354522e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.525457481350749e-09</v>
+        <v>1.525457481350748e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.32699094553043e-09</v>
+        <v>1.326990945530429e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.096712625601213e-09</v>
+        <v>2.09671262560121e-09</v>
       </c>
       <c r="K5" t="n">
         <v>1.484966564499677e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.687671223747659e-09</v>
+        <v>1.68767122374766e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6618,34 +6618,34 @@
         <v>8.405735298999204e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.154095364753491e-10</v>
+        <v>5.15409536475346e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.119253810231156e-10</v>
+        <v>5.119253810231153e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.120411226849388e-10</v>
+        <v>5.120411226849382e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.161017625526806e-10</v>
+        <v>5.161017625526799e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.326788256503415e-10</v>
+        <v>8.326788256503442e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.305015455429496e-10</v>
+        <v>8.305015455429509e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.293686794923589e-10</v>
+        <v>8.293686794923592e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.652090599531066e-10</v>
+        <v>5.652090599531069e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.233088488416436e-10</v>
+        <v>5.233088488416437e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.215764142094146e-10</v>
+        <v>5.215764142094145e-10</v>
       </c>
     </row>
     <row r="7">
@@ -6655,22 +6655,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.166555248977799e-09</v>
+        <v>1.1665552489778e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.155352599306449e-09</v>
+        <v>1.155352599306448e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.15146889126669e-09</v>
+        <v>1.151468891266689e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.155402295133794e-09</v>
+        <v>1.155402295133793e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.155402295133794e-09</v>
+        <v>1.155402295133793e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.158660544728228e-09</v>
+        <v>1.158660544728224e-09</v>
       </c>
       <c r="H7" t="n">
         <v>1.158748908241633e-09</v>
@@ -6679,13 +6679,13 @@
         <v>1.155350398570239e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.19521099559065e-09</v>
+        <v>1.195210995590651e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.16252785935603e-09</v>
+        <v>1.162527859356032e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.16083794176108e-09</v>
+        <v>1.160837941761081e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.097158678241402e-09</v>
+        <v>1.097158678241401e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.565567774962154e-09</v>
+        <v>1.565567774962155e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.660948376653174e-09</v>
+        <v>1.660948376653173e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.43442047284804e-09</v>
+        <v>1.434420472848039e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.101200600079932e-09</v>
+        <v>1.101200600079931e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.568696934129466e-09</v>
+        <v>1.568696934129463e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.568785297642864e-09</v>
+        <v>1.568785297642863e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.565386787971477e-09</v>
+        <v>1.565386787971478e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.605341607364621e-09</v>
+        <v>1.60534160736462e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.084225575239298e-09</v>
+        <v>1.084225575239297e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.071682147611908e-09</v>
+        <v>2.071682147611907e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.066034689152456e-10</v>
+        <v>9.066034689152437e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.051376502844674e-09</v>
+        <v>1.051376502844671e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.047522550530946e-09</v>
+        <v>1.047522550530943e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.231369223791055e-09</v>
+        <v>1.231369223791052e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.05137643130337e-09</v>
+        <v>1.051376431303368e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.05468444826645e-09</v>
+        <v>1.054684448266446e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.05477281177986e-09</v>
+        <v>1.054772811779856e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.051374302108464e-09</v>
+        <v>1.051374302108462e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.091234899128877e-09</v>
+        <v>1.091234899128873e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.681789264185646e-10</v>
+        <v>9.68178926418563e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.056861845299305e-09</v>
+        <v>1.056861845299302e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.04062320827111e-10</v>
+        <v>5.040623208271128e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.793489475842616e-10</v>
+        <v>5.793489475842624e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.025048139230937e-10</v>
+        <v>5.025048139230968e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.059871184887026e-10</v>
+        <v>6.059871184887045e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.287247287214702e-10</v>
+        <v>5.287247287214685e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.023409612837098e-10</v>
+        <v>5.023409612837095e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.001721517728209e-10</v>
+        <v>5.001721517728211e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.022230130347252e-10</v>
+        <v>5.022230130347266e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.008030097630796e-10</v>
+        <v>7.008030097630807e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.393645093560258e-10</v>
+        <v>7.39364509356029e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.028411880717033e-10</v>
+        <v>5.028411880717028e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.5090432811913e-10</v>
+        <v>4.509043281191298e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.666822422201461e-10</v>
+        <v>5.666822422201475e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.398289257262774e-10</v>
+        <v>4.398289257262786e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.096463158089306e-10</v>
+        <v>6.096463158089317e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.820990539469816e-10</v>
+        <v>4.820990539469842e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.387022103541361e-10</v>
+        <v>4.387022103541363e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.327096918138337e-10</v>
+        <v>4.327096918138358e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.377240895600064e-10</v>
+        <v>4.377240895600083e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.140337890467112e-10</v>
+        <v>8.140337890467136e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.310035744878615e-10</v>
+        <v>8.310035744878642e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.434257783014305e-10</v>
+        <v>4.434257783014316e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.463319673056769e-10</v>
+        <v>4.463319673056775e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.240831144037729e-10</v>
+        <v>4.240831144037744e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.287392103362218e-10</v>
+        <v>4.287392103362225e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.249455963140215e-10</v>
+        <v>4.249455963140225e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.249455963140216e-10</v>
+        <v>4.249455963140225e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.268397993092345e-10</v>
+        <v>4.268397993092352e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.194920805820936e-10</v>
+        <v>4.194920805820948e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.254529367543095e-10</v>
+        <v>4.254529367543108e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.252688566638078e-10</v>
+        <v>5.252688566638087e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.292366470506514e-10</v>
+        <v>4.29236647050652e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.341212402597212e-10</v>
+        <v>4.341212402597221e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.799993222714909e-09</v>
+        <v>1.799993222714911e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.404967381216884e-09</v>
+        <v>1.404967381216891e-09</v>
       </c>
       <c r="D5" t="n">
         <v>1.509877257152013e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.404967416010109e-09</v>
+        <v>1.404967416010116e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.404967416010109e-09</v>
+        <v>1.404967416010116e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.49922724633066e-09</v>
+        <v>1.499227246330733e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.46944591045652e-09</v>
+        <v>1.469445910456522e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.404965613884287e-09</v>
+        <v>1.404965613884295e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>3.212787590466559e-09</v>
+        <v>3.212787590466575e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.494187784545343e-09</v>
+        <v>1.494187784545348e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.77857699850358e-09</v>
+        <v>1.778576998503582e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.430102334831506e-10</v>
+        <v>5.430102334831513e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.214229418125835e-10</v>
+        <v>5.214229418125863e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.252921549697299e-10</v>
+        <v>5.252921549697303e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.179819838619107e-10</v>
+        <v>5.179819838619132e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.221242533061891e-10</v>
+        <v>5.221242533061911e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.23518065486709e-10</v>
+        <v>5.235180654867094e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.272794291465982e-10</v>
+        <v>8.272794291466017e-10</v>
       </c>
       <c r="I6" t="n">
         <v>5.221312029317837e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>6.315466804749153e-10</v>
+        <v>6.315466804749188e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.25818473443772e-10</v>
+        <v>5.258184734437709e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.307915506118048e-10</v>
+        <v>5.307915506118054e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.179723634850723e-09</v>
+        <v>1.179723634850726e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.158846371631953e-09</v>
+        <v>1.158846371631954e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.162101388749741e-09</v>
+        <v>1.162101388749743e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.158894327361769e-09</v>
+        <v>1.15889432736177e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.158894327361769e-09</v>
+        <v>1.15889432736177e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.160231466854283e-09</v>
+        <v>1.160231466854285e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.152883748127141e-09</v>
+        <v>1.152883748127144e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.158844604299359e-09</v>
+        <v>1.15884460429936e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.258660524208855e-09</v>
+        <v>1.258660524208858e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.162628314595697e-09</v>
+        <v>1.162628314595704e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.167512907804769e-09</v>
+        <v>1.167512907804773e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7091,34 +7091,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.106575840276246e-09</v>
+        <v>1.10657584027625e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.561821295207196e-09</v>
+        <v>1.561821295207199e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.663620016318889e-09</v>
+        <v>1.663620016318893e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.431627820349041e-09</v>
+        <v>1.431627820349044e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.100831555245666e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.563030027939687e-09</v>
+        <v>1.563030027939688e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.55568230921256e-09</v>
+        <v>1.555682309212559e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.561643165384762e-09</v>
+        <v>1.561643165384761e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.661552622446539e-09</v>
+        <v>1.661552622446546e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.08063957210934e-09</v>
+        <v>1.080639572109341e-09</v>
       </c>
       <c r="L8" t="n">
         <v>2.067477235415007e-09</v>
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.048444171640092e-10</v>
+        <v>9.048444171640127e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.035334441656469e-09</v>
+        <v>1.035334441656473e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.03861915537704e-09</v>
+        <v>1.038619155377046e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.21000917950913e-09</v>
+        <v>1.210009179509135e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.035334376446427e-09</v>
+        <v>1.03533437644643e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.036719536878801e-09</v>
+        <v>1.036719536878809e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.029371818151659e-09</v>
+        <v>1.029371818151661e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.035332674323877e-09</v>
+        <v>1.035332674323884e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.135148594233375e-09</v>
+        <v>1.135148594233381e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.478554526192966e-10</v>
+        <v>9.478554526192995e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.044000977829285e-09</v>
+        <v>1.044000977829295e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.205573819045657e-10</v>
+        <v>5.205573819045606e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>6.083612573827135e-10</v>
+        <v>6.083612573827138e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.247644787169756e-10</v>
+        <v>5.247644787169709e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.392157631032299e-10</v>
+        <v>6.392157631032293e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.494469214583003e-10</v>
+        <v>5.494469214583e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.219041066268333e-10</v>
+        <v>5.219041066268285e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.291573728649325e-10</v>
+        <v>5.291573728649321e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.18730901688959e-10</v>
+        <v>5.18730901688954e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.415123172914378e-10</v>
+        <v>7.415123172914385e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.685916791508547e-10</v>
+        <v>7.685916791508607e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.321601469688772e-10</v>
+        <v>5.321601469688771e-10</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.603450786434501e-10</v>
+        <v>4.60345078643449e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.969794905172364e-10</v>
+        <v>5.969794905172368e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.902179839280732e-10</v>
+        <v>4.902179839280734e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.467874091052137e-10</v>
+        <v>6.467874091052147e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.985960193522903e-10</v>
+        <v>4.985960193522931e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.699836437864266e-10</v>
+        <v>4.699836437864279e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.307754651824941e-10</v>
+        <v>5.307754651824949e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.47264770057319e-10</v>
+        <v>4.472647700573178e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.324505758375366e-10</v>
+        <v>8.324505758375342e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.683241643824767e-10</v>
+        <v>8.683241643824727e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.440484650202901e-10</v>
+        <v>5.440484650202908e-10</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.577637651878232e-10</v>
+        <v>4.577637651878225e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.347856337620447e-10</v>
+        <v>4.347856337620449e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.052848590441573e-10</v>
+        <v>5.052848590441574e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.357848514527088e-10</v>
+        <v>4.357848514527093e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.357848514527089e-10</v>
+        <v>4.35784851452709e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.729138214004832e-10</v>
+        <v>4.729138214004852e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.712689120016473e-10</v>
+        <v>5.712689120016492e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.369397139491392e-10</v>
+        <v>4.369397139491394e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.72600566247337e-10</v>
+        <v>4.726005662473366e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.547389875769508e-10</v>
+        <v>4.547389875769503e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.88850216485471e-10</v>
+        <v>5.888502164854701e-10</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.805446129608729e-09</v>
+        <v>1.805446129608728e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.390354899792565e-09</v>
+        <v>1.390354899792524e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.618682040774353e-09</v>
+        <v>2.618682040774363e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.39035494551054e-09</v>
+        <v>1.390354945510522e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.39035494551054e-09</v>
+        <v>1.390354945510522e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.107982651343971e-09</v>
+        <v>2.107982651343982e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.04100546360863e-09</v>
+        <v>4.041005463608665e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.390345188275987e-09</v>
+        <v>1.39034518827597e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.181903670447524e-09</v>
+        <v>2.181903670447516e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.760627376496709e-09</v>
+        <v>1.76062737649671e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.994829972709163e-09</v>
+        <v>1.994829972709188e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7407,34 +7407,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.581981950700767e-10</v>
+        <v>5.58198195070077e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.358069630427927e-10</v>
+        <v>5.358069630427921e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>6.071872427230285e-10</v>
+        <v>6.071872427230283e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.321788256134595e-10</v>
+        <v>5.321788256134598e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.373276243913525e-10</v>
+        <v>5.373276243913523e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.170685699440138e-10</v>
+        <v>9.17068569944015e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>1.013535033164346e-09</v>
+        <v>1.013535033164347e-09</v>
       </c>
       <c r="I6" t="n">
         <v>8.810944624926675e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.151460076352505e-10</v>
+        <v>9.151460076352506e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.54833783756687e-10</v>
+        <v>5.548337837566877e-10</v>
       </c>
       <c r="L6" t="n">
         <v>6.902000285948343e-10</v>
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.271404615894382e-09</v>
+        <v>1.271404615894383e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.25059027617228e-09</v>
+        <v>1.250590276172281e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.318893680077386e-09</v>
+        <v>1.318893680077387e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2505656337002e-09</v>
+        <v>1.250565633700201e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2505656337002e-09</v>
+        <v>1.250565633700201e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.286554672107045e-09</v>
+        <v>1.286554672107047e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.38490976270821e-09</v>
+        <v>1.384909762708211e-09</v>
       </c>
       <c r="I7" t="n">
         <v>1.2505805646557e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.286241416953896e-09</v>
+        <v>1.286241416953898e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.268379838283511e-09</v>
+        <v>1.268379838283514e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.402491067192031e-09</v>
+        <v>1.402491067192032e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.222075540524938e-09</v>
+        <v>1.222075540524939e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.751625671794546e-09</v>
+        <v>1.751625671794542e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.933932202035208e-09</v>
+        <v>1.933932202035205e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.60111846424068e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.218707377028252e-09</v>
+        <v>1.218707377028251e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.787465364137075e-09</v>
+        <v>1.787465364137072e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.885820454738218e-09</v>
+        <v>1.885820454738219e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.75149125668573e-09</v>
+        <v>1.751491256685728e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.787260246939098e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.208829776735177e-09</v>
+        <v>1.208829776735178e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.478173206640511e-09</v>
+        <v>2.478173206640509e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7530,34 +7530,34 @@
         <v>1.024325934349065e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.188316541584647e-09</v>
+        <v>1.188316541584649e-09</v>
       </c>
       <c r="D9" t="n">
         <v>1.256652186819839e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.401577569899599e-09</v>
+        <v>1.401577569899602e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.188316428080498e-09</v>
+        <v>1.188316428080497e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.224280937519414e-09</v>
+        <v>1.224280937519416e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.32263602812058e-09</v>
+        <v>1.322636028120577e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.18830683006807e-09</v>
+        <v>1.188306830068068e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.223967682366261e-09</v>
+        <v>1.223967682366265e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.099029480665594e-09</v>
+        <v>1.099029480665593e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.340217332604397e-09</v>
+        <v>1.340217332604399e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.129913486377052e-10</v>
+        <v>5.129913486377046e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.990313963087131e-10</v>
+        <v>5.990313963087141e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.174549228103437e-10</v>
+        <v>5.174549228103434e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.286575113397267e-10</v>
+        <v>6.286575113397282e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.424860670502525e-10</v>
+        <v>5.424860670502519e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.148491909515258e-10</v>
+        <v>5.148491909515251e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.13339067990868e-10</v>
+        <v>5.133390679908672e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.128909035444515e-10</v>
+        <v>5.128909035444512e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>7.272837986538202e-10</v>
+        <v>7.2728379865382e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>7.575674043764682e-10</v>
+        <v>7.575674043764677e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.216376104977894e-10</v>
+        <v>5.216376104977898e-10</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.429199190858063e-10</v>
+        <v>4.429199190858066e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.860042911111655e-10</v>
+        <v>5.860042911111658e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.745401425899426e-10</v>
+        <v>4.74540142589942e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.338284616167097e-10</v>
+        <v>6.338284616167104e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.91575220477797e-10</v>
+        <v>4.915752204777964e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.561387426949276e-10</v>
+        <v>4.561387426949275e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.549573624995391e-10</v>
+        <v>4.549573624995393e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.420940965449146e-10</v>
+        <v>4.420940965449148e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>8.145793299395391e-10</v>
+        <v>8.145793299395414e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>8.469675431137283e-10</v>
+        <v>8.469675431137287e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.054569925450648e-10</v>
+        <v>5.054569925450644e-10</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.271487386801881e-10</v>
+        <v>4.271487386801894e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.241670281305918e-10</v>
+        <v>4.24167028130592e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.775668623057121e-10</v>
+        <v>4.775668623057119e-10</v>
       </c>
       <c r="E4" t="n">
+        <v>4.250710399260332e-10</v>
+      </c>
+      <c r="F4" t="n">
         <v>4.25071039926033e-10</v>
       </c>
-      <c r="F4" t="n">
-        <v>4.250710399260326e-10</v>
-      </c>
       <c r="G4" t="n">
-        <v>4.48079097569355e-10</v>
+        <v>4.480790975693551e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.483760303838718e-10</v>
+        <v>4.483760303838723e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.25868287156949e-10</v>
+        <v>4.258682871569492e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.638418658546784e-10</v>
+        <v>4.638418658546792e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.278856600866221e-10</v>
+        <v>4.27885660086623e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.253735275135043e-10</v>
+        <v>5.253735275135052e-10</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.369831786069333e-09</v>
+        <v>1.369831786069331e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.293169775769829e-09</v>
+        <v>1.293169775769833e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.138984912427566e-09</v>
+        <v>2.138984912427562e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.293169815333556e-09</v>
+        <v>1.293169815333557e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.293169815333556e-09</v>
+        <v>1.293169815333557e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.719848205624224e-09</v>
+        <v>1.719848205624213e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.826379314238955e-09</v>
+        <v>1.826379314238957e-09</v>
       </c>
       <c r="I5" t="n">
         <v>1.293163241471173e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.074837605069707e-09</v>
+        <v>2.0748376050697e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.368425750581006e-09</v>
+        <v>1.368425750581005e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>3.378293942536025e-09</v>
+        <v>3.378293942536017e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.390256423356986e-10</v>
+        <v>8.390256423356985e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.183941427065024e-10</v>
+        <v>5.183941427064988e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.72312036234103e-10</v>
+        <v>5.72312036234104e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.15005163876086e-10</v>
+        <v>5.150051638760869e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.19477622847461e-10</v>
+        <v>5.194776228474627e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.599560012248671e-10</v>
+        <v>8.599560012248643e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.579436537656796e-10</v>
+        <v>8.579436537656777e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.377451908124564e-10</v>
+        <v>8.377451908124591e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.668615907476386e-10</v>
+        <v>5.668615907476415e-10</v>
       </c>
       <c r="K6" t="n">
         <v>5.209964626121306e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.195404192373086e-10</v>
+        <v>6.195404192373083e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7849,13 +7849,13 @@
         <v>1.177086806977574e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.228749081579104e-09</v>
+        <v>1.228749081579105e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.177106098928702e-09</v>
+        <v>1.177106098928704e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.177106098928702e-09</v>
+        <v>1.177106098928704e-09</v>
       </c>
       <c r="G7" t="n">
         <v>1.199291083091322e-09</v>
@@ -7867,13 +7867,13 @@
         <v>1.177080272678916e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.215053851376645e-09</v>
+        <v>1.215053851376646e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.179097645608589e-09</v>
+        <v>1.17909764560859e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.276585513035471e-09</v>
+        <v>1.276585513035472e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.122959578408212e-09</v>
+        <v>1.122959578408214e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.623341831332291e-09</v>
+        <v>1.623341831332296e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.778869242654424e-09</v>
+        <v>1.778869242654426e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.486161442414928e-09</v>
+        <v>1.486161442414932e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.13761177737524e-09</v>
+        <v>1.137611777375243e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.645391799752556e-09</v>
+        <v>1.64539179975256e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.645688732567042e-09</v>
+        <v>1.645688732567047e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.62318098934015e-09</v>
+        <v>1.623180989340154e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.661253127587614e-09</v>
+        <v>1.661253127587619e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.114380845243098e-09</v>
+        <v>1.1143808452431e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.246546859993595e-09</v>
+        <v>2.246546859993603e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.217689736338658e-10</v>
+        <v>9.217689736338656e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.08313502926978e-09</v>
+        <v>1.083135029269774e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.134827283740238e-09</v>
+        <v>1.134827283740233e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.270818195966479e-09</v>
+        <v>1.270818195966474e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.083134951927973e-09</v>
+        <v>1.08313495192797e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.105339305383524e-09</v>
+        <v>1.105339305383521e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.105636238198042e-09</v>
+        <v>1.105636238198038e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.083128494971118e-09</v>
+        <v>1.083128494971116e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.121102073668848e-09</v>
+        <v>1.121102073668843e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>9.909117187368764e-10</v>
+        <v>9.909117187368688e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>1.182633735327676e-09</v>
+        <v>1.182633735327671e-09</v>
       </c>
     </row>
   </sheetData>
